--- a/INFORME EXCESOS DE VELOCIDAD.xlsx
+++ b/INFORME EXCESOS DE VELOCIDAD.xlsx
@@ -222,8 +222,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SpeedingFleetsSummaryTable_1" displayName="SpeedingFleetsSummaryTable_1" ref="A5:I12" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A5:I12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SpeedingFleetsSummaryTable_1" displayName="SpeedingFleetsSummaryTable_1" ref="A5:I15" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A5:I15"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Alias"/>
     <tableColumn id="2" name="Excesos" dataDxfId="0"/>
@@ -240,8 +240,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SpeedingFleetsDetailTable_1" displayName="SpeedingFleetsDetailTable_1" ref="A5:O25" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A5:O25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SpeedingFleetsDetailTable_1" displayName="SpeedingFleetsDetailTable_1" ref="A5:O66" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A5:O66"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Alias"/>
     <tableColumn id="2" name="Conductor"/>
@@ -264,8 +264,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SpeedingFleetsDataTable_1" displayName="SpeedingFleetsDataTable_1" ref="A5:H47" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A5:H47"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SpeedingFleetsDataTable_1" displayName="SpeedingFleetsDataTable_1" ref="A5:H164" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A5:H164"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Alias"/>
     <tableColumn id="2" name="Secuencial" dataDxfId="0"/>
@@ -569,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.710625" customWidth="1" style="7" min="1" max="1"/>
@@ -593,7 +593,7 @@
     <row r="3" ht="25" customHeight="1" s="8">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Desde : 2026/07/13 00:00:00 Hasta: 2026/07/25 23:59:59</t>
+          <t>Desde : 2026/07/13 00:00:00 Hasta: 2026/08/02 23:59:59</t>
         </is>
       </c>
     </row>
@@ -647,26 +647,26 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>GC RXDL-59 OPERACIONES</t>
+          <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>0.0001388888888888889</v>
+        <v>0.0006944444444444445</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>0.0001388888888888889</v>
+        <v>0.0006944444444444445</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>100.6</v>
+        <v>102.1</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>100.6</v>
+        <v>102.1</v>
       </c>
       <c r="H6" s="12" t="n">
         <v>0</v>
@@ -678,26 +678,26 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B7" s="12" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>0.001388888888888889</v>
+        <v>0.0009722222222222222</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>0.0006944444444444445</v>
+        <v>0.0004861111111111111</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>101.1</v>
+        <v>103.1</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>100.9</v>
+        <v>102</v>
       </c>
       <c r="H7" s="12" t="n">
         <v>0</v>
@@ -709,26 +709,26 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>0.002777777777777778</v>
+        <v>0.0006944444444444445</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>0.000925925925925926</v>
+        <v>0.0006944444444444445</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>6.8</v>
+        <v>1.6</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>104.4</v>
+        <v>102</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>103.1</v>
+        <v>102</v>
       </c>
       <c r="H8" s="12" t="n">
         <v>0</v>
@@ -740,20 +740,20 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>GV PEUGEOT THJY-73 J PONCE</t>
+          <t>GLP SHLC-75 L FONSECA</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>0.0002777777777777778</v>
+        <v>0.0002430555555555555</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>0.0002777777777777778</v>
+        <v>0.0002430555555555555</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F9" s="12" t="n">
         <v>100.2</v>
@@ -771,26 +771,26 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GV SHLC-74 B MIRANDA</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>0.002233796296296296</v>
+        <v>0.0006944444444444445</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>0.000279224537037037</v>
+        <v>0.0006944444444444445</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>109.3</v>
+        <v>102.9</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>102.5</v>
+        <v>102.9</v>
       </c>
       <c r="H10" s="12" t="n">
         <v>0</v>
@@ -802,26 +802,26 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>GLP SHDV-51 J REBOLLEDO</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>0.000462962962962963</v>
+        <v>0.04327546296296296</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>0.000462962962962963</v>
+        <v>0.001352361111111111</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>1</v>
+        <v>108.8</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>101.3</v>
+        <v>114.5</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>101.3</v>
+        <v>106.4</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>0</v>
@@ -833,31 +833,124 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>GC TSVS-89 M AEDO</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
         <v>4</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>0.002268518518518519</v>
+        <v>0.001319444444444444</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>0.0005671296296296297</v>
+        <v>0.0003298611111111111</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>5.4</v>
+        <v>3.1</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>106.4</v>
+        <v>106.1</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>102.6</v>
+        <v>104.2</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 RXDL-61 OPERACIONES</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>0.005844907407407407</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>0.0004496064814814814</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>109</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>GLP SKDX-44 V VIAL</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>0.0006712962962962962</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>0.0003356481481481481</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>141.7</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>141.7</v>
+      </c>
+      <c r="H14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>0.002141203703703704</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>0.0005353009259259259</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -882,7 +975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O86"/>
+  <dimension ref="A1:O108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.710625" customWidth="1" style="7" min="1" max="1"/>
@@ -910,7 +1003,7 @@
     <row r="3" ht="25" customHeight="1" s="8">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Desde : 2026/07/13 00:00:00 Hasta: 2026/07/19 23:59:58</t>
+          <t>Desde : 2026/07/20 00:00:00 Hasta: 2026/07/26 23:59:58</t>
         </is>
       </c>
     </row>
@@ -998,7 +1091,6 @@
           <t>GLP SHDV-51 J REBOLLEDO</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>1</v>
       </c>
@@ -1057,7 +1149,6 @@
           <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>1</v>
       </c>
@@ -1116,7 +1207,6 @@
           <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>2</v>
       </c>
@@ -1175,7 +1265,6 @@
           <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>3</v>
       </c>
@@ -1234,7 +1323,6 @@
           <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>1</v>
       </c>
@@ -1293,7 +1381,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>1</v>
       </c>
@@ -1352,7 +1439,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>1</v>
       </c>
@@ -1411,7 +1497,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>2</v>
       </c>
@@ -1470,7 +1555,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>3</v>
       </c>
@@ -1529,7 +1613,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>1</v>
       </c>
@@ -1588,7 +1671,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>2</v>
       </c>
@@ -1647,7 +1729,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>3</v>
       </c>
@@ -1706,7 +1787,6 @@
           <t>GC RXDL-59 OPERACIONES</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>1</v>
       </c>
@@ -1765,7 +1845,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>4</v>
       </c>
@@ -1824,7 +1903,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>4</v>
       </c>
@@ -1883,7 +1961,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>5</v>
       </c>
@@ -1942,7 +2019,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>6</v>
       </c>
@@ -2001,7 +2077,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>7</v>
       </c>
@@ -2060,7 +2135,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>8</v>
       </c>
@@ -2119,7 +2193,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>2</v>
       </c>
@@ -2178,7 +2251,6 @@
           <t>GLP SHLC-75 L FONSECA</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>1</v>
       </c>
@@ -2237,7 +2309,6 @@
           <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>1</v>
       </c>
@@ -2296,7 +2367,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>1</v>
       </c>
@@ -2355,7 +2425,6 @@
           <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>2</v>
       </c>
@@ -2414,7 +2483,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>1</v>
       </c>
@@ -2473,7 +2541,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>2</v>
       </c>
@@ -2534,7 +2601,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>3</v>
       </c>
@@ -2593,7 +2659,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>4</v>
       </c>
@@ -2652,7 +2717,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>5</v>
       </c>
@@ -2711,7 +2775,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>6</v>
       </c>
@@ -2770,7 +2833,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>7</v>
       </c>
@@ -2829,7 +2891,6 @@
           <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
         <v>1</v>
       </c>
@@ -2888,7 +2949,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
         <v>8</v>
       </c>
@@ -2947,7 +3007,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
         <v>9</v>
       </c>
@@ -3006,7 +3065,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
         <v>10</v>
       </c>
@@ -3065,7 +3123,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
         <v>11</v>
       </c>
@@ -3124,7 +3181,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
         <v>12</v>
       </c>
@@ -3183,7 +3239,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
         <v>13</v>
       </c>
@@ -3242,7 +3297,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
         <v>14</v>
       </c>
@@ -3301,7 +3355,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
         <v>15</v>
       </c>
@@ -3360,7 +3413,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
         <v>16</v>
       </c>
@@ -3419,7 +3471,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
         <v>17</v>
       </c>
@@ -3480,7 +3531,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
         <v>18</v>
       </c>
@@ -3539,7 +3589,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
         <v>19</v>
       </c>
@@ -3600,7 +3649,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
         <v>20</v>
       </c>
@@ -3659,7 +3707,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
         <v>21</v>
       </c>
@@ -3720,7 +3767,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
         <v>22</v>
       </c>
@@ -3779,7 +3825,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
         <v>23</v>
       </c>
@@ -3840,7 +3885,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
         <v>24</v>
       </c>
@@ -3899,7 +3943,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
         <v>25</v>
       </c>
@@ -3958,7 +4001,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
         <v>26</v>
       </c>
@@ -4019,7 +4061,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
         <v>27</v>
       </c>
@@ -4078,7 +4119,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
         <v>28</v>
       </c>
@@ -4139,7 +4179,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
         <v>29</v>
       </c>
@@ -4198,7 +4237,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
         <v>30</v>
       </c>
@@ -4257,7 +4295,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
         <v>31</v>
       </c>
@@ -4316,7 +4353,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
         <v>32</v>
       </c>
@@ -4375,7 +4411,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
         <v>1</v>
       </c>
@@ -4434,7 +4469,6 @@
           <t>GLP DF6 RXDL-61 OPERACIONES</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
         <v>1</v>
       </c>
@@ -4493,7 +4527,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
         <v>2</v>
       </c>
@@ -4552,7 +4585,6 @@
           <t>GV SHLC-74 B MIRANDA</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
         <v>1</v>
       </c>
@@ -4611,7 +4643,6 @@
           <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
         <v>1</v>
       </c>
@@ -4672,7 +4703,6 @@
           <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
         <v>2</v>
       </c>
@@ -4731,7 +4761,6 @@
           <t>GLP DF6 RXDL-61 OPERACIONES</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
         <v>2</v>
       </c>
@@ -4790,7 +4819,6 @@
           <t>GLP DF6 RXDL-61 OPERACIONES</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
         <v>3</v>
       </c>
@@ -4849,7 +4877,6 @@
           <t>GLP DF6 RXDL-61 OPERACIONES</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
         <v>4</v>
       </c>
@@ -4908,7 +4935,6 @@
           <t>GLP DF6 RXDL-61 OPERACIONES</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
         <v>5</v>
       </c>
@@ -4967,7 +4993,6 @@
           <t>GLP DF6 RXDL-61 OPERACIONES</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
         <v>6</v>
       </c>
@@ -5026,7 +5051,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
         <v>1</v>
       </c>
@@ -5085,7 +5109,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
         <v>2</v>
       </c>
@@ -5144,7 +5167,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
         <v>3</v>
       </c>
@@ -5203,7 +5225,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
         <v>4</v>
       </c>
@@ -5262,7 +5283,6 @@
           <t>GLP DF6 RXDL-61 OPERACIONES</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
         <v>7</v>
       </c>
@@ -5321,7 +5341,6 @@
           <t>GLP DF6 RXDL-61 OPERACIONES</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
         <v>8</v>
       </c>
@@ -5380,7 +5399,6 @@
           <t>GLP DF6 RXDL-61 OPERACIONES</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
         <v>9</v>
       </c>
@@ -5439,7 +5457,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
         <v>3</v>
       </c>
@@ -5498,7 +5515,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
         <v>4</v>
       </c>
@@ -5557,7 +5573,6 @@
           <t>GLP DF6 RXDL-61 OPERACIONES</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
         <v>10</v>
       </c>
@@ -5616,7 +5631,6 @@
           <t>GLP DF6 RXDL-61 OPERACIONES</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
         <v>11</v>
       </c>
@@ -5677,7 +5691,6 @@
           <t>GLP DF6 RXDL-61 OPERACIONES</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
         <v>12</v>
       </c>
@@ -5736,7 +5749,6 @@
           <t>GLP DF6 RXDL-61 OPERACIONES</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
         <v>13</v>
       </c>
@@ -5786,6 +5798,1304 @@
         <v>0</v>
       </c>
       <c r="O86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026/07/27 06:25:04</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>-33.067327,-71.387599</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2026/07/27 06:26:04</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-33.068846,-71.370499</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J87" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L87" t="n">
+        <v>104</v>
+      </c>
+      <c r="M87" t="n">
+        <v>104</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="n">
+        <v>2</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026/07/27 06:32:04</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>-33.016759,-71.31988</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2026/07/27 06:33:04</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-33.004069,-71.328408</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J88" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L88" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="M88" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="n">
+        <v>3</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026/07/27 06:43:04</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>-32.911064,-71.269813</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2026/07/27 06:44:04</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-32.903617,-71.254498</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J89" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K89" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L89" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="M89" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="n">
+        <v>4</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026/07/27 07:46:04</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>-32.572429,-71.289271</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2026/07/27 07:47:04</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-32.569254,-71.276721</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="J90" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L90" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="M90" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="n">
+        <v>5</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026/07/27 07:50:04</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>-32.549855,-71.268268</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2026/07/27 07:53:04</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-32.506255,-71.259684</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J91" s="14" t="n">
+        <v>0.002083333333333333</v>
+      </c>
+      <c r="K91" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L91" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="M91" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026/07/28 02:11:25</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>-32.944023,-71.513376</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2026/07/28 02:12:25</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-32.935778,-71.513703</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="J92" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L92" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="M92" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026/07/28 15:58:20</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>-32.733776,-71.436634</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2026/07/28 15:58:42</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>-32.736051,-71.431128</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Ruta F-20, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J93" s="14" t="n">
+        <v>0.0002546296296296296</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L93" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="M93" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>GV TDKV-88 L CORDERO</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026/07/30 17:56:03</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>-33.10693,-71.550214</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2026/07/30 17:56:09</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>-33.107497,-71.5518</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J94" s="14" t="n">
+        <v>6.944444444444444e-05</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L94" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="M94" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026/07/30 18:54:20</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>-32.897768,-71.449538</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2026/07/30 18:55:20</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-32.906604,-71.440511</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Ruta F-190, Quillota, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J95" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L95" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="M95" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>GV SHLC-74 B MIRANDA</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026/07/31 07:36:59</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>-33.158797,-71.546799</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2026/07/31 07:37:59</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>-33.149438,-71.558461</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J96" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L96" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="M96" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="n">
+        <v>2</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026/07/31 13:08:39</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>-33.219324,-71.471926</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Ruta F-190, Quillota, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2026/07/31 13:09:39</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>-33.231962,-71.464083</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J97" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L97" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="M97" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>GC MAXUS PCRF-25 TERRENO</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026/07/31 14:57:40</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-32.577562,-71.309168</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2026/07/31 14:58:40</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>-32.583363,-71.323384</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="J98" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K98" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L98" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="M98" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="n">
+        <v>6</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026/07/31 19:07:11</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>-32.870929,-71.229809</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>2026/07/31 19:09:11</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-32.898972,-71.239656</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J99" s="14" t="n">
+        <v>0.001388888888888889</v>
+      </c>
+      <c r="K99" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L99" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="M99" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="n">
+        <v>7</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026/07/31 19:10:11</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>-32.904194,-71.25627</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2026/07/31 19:12:55</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-32.933783,-71.288593</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J100" s="14" t="n">
+        <v>0.001898148148148148</v>
+      </c>
+      <c r="K100" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L100" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="M100" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>GLP SKDX-44 V VIAL</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026/08/01 06:30:23</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>-33.102452,-71.54806</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2026/08/01 06:30:48</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-33.096687,-71.546062</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>s/n, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="J101" s="14" t="n">
+        <v>0.0002893518518518518</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L101" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="M101" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>GLP SKDX-44 V VIAL</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="n">
+        <v>2</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026/08/01 06:46:24</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>-32.967111,-71.503823</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>s/n, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2026/08/01 06:47:14</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-32.957174,-71.510191</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J102" s="14" t="n">
+        <v>0.0005787037037037037</v>
+      </c>
+      <c r="K102" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L102" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="M102" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>GLP SKDX-44 V VIAL</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="n">
+        <v>3</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026/08/01 06:50:24</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>-32.989287,-71.500906</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2026/08/01 06:51:02</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-32.998137,-71.50228</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Camino Internacional, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J103" s="14" t="n">
+        <v>0.0004398148148148148</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L103" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="M103" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>GLP SKDX-44 V VIAL</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="n">
+        <v>4</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026/08/01 09:40:00</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>-33.013677,-71.500475</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Camino Internacional, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2026/08/01 09:40:16</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-33.017375,-71.500179</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Avenida Rubén Hurtado, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="J104" s="14" t="n">
+        <v>0.0001851851851851852</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L104" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="M104" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>GLP SKDX-44 V VIAL</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="n">
+        <v>5</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026/08/01 11:31:13</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>-33.059472,-71.645814</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Avenida Rubén Hurtado, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2026/08/01 11:31:21</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-33.060679,-71.644303</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="J105" s="14" t="n">
+        <v>9.259259259259259e-05</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L105" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="M105" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>GLP SKDX-44 V VIAL</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="n">
+        <v>6</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026/08/01 11:31:50</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>-33.06623,-71.64223</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2026/08/01 11:32:53</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-33.072407,-71.627597</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="J106" s="14" t="n">
+        <v>0.0007291666666666667</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L106" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="M106" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>GLP SKDX-44 V VIAL</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="n">
+        <v>7</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026/08/02 12:14:56</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>-33.09045,-71.541794</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2026/08/02 12:15:30</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-33.096963,-71.546855</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J107" s="14" t="n">
+        <v>0.0003935185185185185</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1</v>
+      </c>
+      <c r="L107" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="M107" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>GV TDLD-98 J PACHECHO</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="n">
+        <v>1</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026/08/02 14:32:36</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>-33.16243,-71.539564</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>2026/08/02 14:33:36</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-33.15517,-71.553769</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J108" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K108" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L108" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="M108" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5810,7 +7120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.710625" customWidth="1" style="7" min="1" max="1"/>
@@ -5836,7 +7146,7 @@
     <row r="3" ht="25" customHeight="1" s="8">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Desde : 2026/07/13 00:00:00 Hasta: 2026/07/19 23:59:58</t>
+          <t>Desde : 2026/07/20 00:00:00 Hasta: 2026/07/26 23:59:58</t>
         </is>
       </c>
     </row>
@@ -5885,7 +7195,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>GC RXDL-59 OPERACIONES</t>
+          <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
@@ -5893,33 +7203,33 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>2026/07/15 18:07:41</t>
+          <t>2026/07/22 09:27:12</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>-32.845538,-71.10364</t>
+          <t>-33.07762,-71.564593</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Hijuelas, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F6" s="12" t="n">
-        <v>100.6</v>
+        <v>102.1</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>164798.6</v>
+        <v>60300.6</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>295.8</v>
+        <v>170.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>GC RXDL-59 OPERACIONES</t>
+          <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
       <c r="B7" s="12" t="n">
@@ -5927,33 +7237,33 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>2026/07/15 18:07:53</t>
+          <t>2026/07/22 09:28:12</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>-32.845953,-71.100303</t>
+          <t>-33.08851,-71.556912</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Hijuelas, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F7" s="12" t="n">
-        <v>98.5</v>
+        <v>72</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>164798.9</v>
+        <v>60302</v>
       </c>
       <c r="H7" s="12" t="n">
-        <v>297.4</v>
+        <v>236.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
@@ -5961,33 +7271,33 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>2026/07/14 07:44:50</t>
+          <t>2026/07/21 11:32:34</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>-33.165059,-71.534739</t>
+          <t>-33.284147,-71.41146</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta F-852, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F8" s="12" t="n">
-        <v>101.1</v>
+        <v>100.9</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>184847.4</v>
+        <v>75326.10000000001</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>353.7</v>
+        <v>267.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
@@ -5995,33 +7305,33 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>2026/07/14 07:45:50</t>
+          <t>2026/07/21 11:32:59</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>-33.172368,-71.520485</t>
+          <t>-33.279333,-71.41388</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta F-852, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F9" s="12" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>184848.9</v>
+        <v>75326.7</v>
       </c>
       <c r="H9" s="12" t="n">
-        <v>343.9</v>
+        <v>306.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
@@ -6029,33 +7339,33 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>2026/07/17 17:21:41</t>
+          <t>2026/07/22 07:56:42</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>-33.198929,-71.490981</t>
+          <t>-33.225503,-71.468722</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F10" s="12" t="n">
-        <v>100.8</v>
+        <v>103.1</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>185489.8</v>
+        <v>75546.8</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>377.5</v>
+        <v>328.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B11" s="12" t="n">
@@ -6063,33 +7373,33 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>2026/07/17 17:22:41</t>
+          <t>2026/07/22 07:57:41</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>-33.187224,-71.500346</t>
+          <t>-33.237146,-71.459055</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>93.90000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>185491.3</v>
+        <v>75548.39999999999</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>352.5</v>
+        <v>324.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
@@ -6097,33 +7407,33 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>2026/07/13 08:42:08</t>
+          <t>2026/07/21 18:30:06</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>-33.12888,-71.561959</t>
+          <t>-33.17968,-71.506531</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>104.4</v>
+        <v>102</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>51165.7</v>
+        <v>186090.6</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>333.5</v>
+        <v>345.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B13" s="12" t="n">
@@ -6131,148 +7441,148 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>2026/07/13 08:43:08</t>
+          <t>2026/07/21 18:31:06</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>-33.144288,-71.56111</t>
+          <t>-33.172153,-71.520549</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>90.09999999999999</v>
+        <v>91</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>51167.4</v>
+        <v>186092.2</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>331.1</v>
+        <v>341.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
+          <t>GLP SHLC-75 L FONSECA</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>2026/07/13 08:44:08</t>
+          <t>2026/07/20 14:20:36</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>-33.156109,-71.552273</t>
+          <t>-33.106749,-71.563552</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>101.7</v>
+        <v>100.2</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>51169</v>
+        <v>95113.3</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>364.6</v>
+        <v>356</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
+          <t>GLP SHLC-75 L FONSECA</t>
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>2026/07/13 08:45:08</t>
+          <t>2026/07/20 14:20:57</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>-33.164064,-71.536687</t>
+          <t>-33.106017,-71.558066</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>97.3</v>
+        <v>67.7</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>51170.7</v>
+        <v>95113.8</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>363.3</v>
+        <v>358.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
+          <t>GV SHLC-74 B MIRANDA</t>
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>2026/07/13 08:50:08</t>
+          <t>2026/07/22 17:03:05</t>
         </is>
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>-33.213661,-71.475503</t>
+          <t>-33.218405,-71.47239</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>103.4</v>
+        <v>102.9</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>51178.8</v>
+        <v>120412.2</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>342.5</v>
+        <v>332.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
+          <t>GV SHLC-74 B MIRANDA</t>
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>2026/07/13 08:51:08</t>
+          <t>2026/07/22 17:04:05</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>-33.227299,-71.467669</t>
+          <t>-33.231782,-71.464215</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
@@ -6281,53 +7591,53 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>103.1</v>
+        <v>97.2</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>51180.5</v>
+        <v>120413.9</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>330.7</v>
+        <v>338.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>2026/07/13 08:52:08</t>
+          <t>2026/07/22 08:58:27</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>-33.238981,-71.456259</t>
+          <t>-33.205225,-71.484598</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>98.09999999999999</v>
+        <v>102</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>51182.2</v>
+        <v>65138.2</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>305.2</v>
+        <v>401.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>GV PEUGEOT THJY-73 J PONCE</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B19" s="12" t="n">
@@ -6335,33 +7645,33 @@
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>2026/07/13 13:00:42</t>
+          <t>2026/07/22 08:59:27</t>
         </is>
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>-33.099705,-71.547794</t>
+          <t>-33.217675,-71.472802</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>100.2</v>
+        <v>106.6</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>119672.8</v>
+        <v>65140</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>326.5</v>
+        <v>335.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>GV PEUGEOT THJY-73 J PONCE</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B20" s="12" t="n">
@@ -6369,33 +7679,33 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>2026/07/13 13:01:06</t>
+          <t>2026/07/22 09:00:26</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>-33.094204,-71.54823</t>
+          <t>-33.23198,-71.464046</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>95.5</v>
+        <v>106.3</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>119673.4</v>
+        <v>65141.8</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>288.6</v>
+        <v>341.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B21" s="12" t="n">
@@ -6403,33 +7713,33 @@
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>2026/07/15 17:25:01</t>
+          <t>2026/07/22 09:01:26</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>-33.058362,-71.649256</t>
+          <t>-33.243273,-71.450439</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+          <t>s/n, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>101.9</v>
+        <v>110</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>258039.8</v>
+        <v>65143.6</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>304.1</v>
+        <v>276.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B22" s="12" t="n">
@@ -6437,101 +7747,101 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>2026/07/15 17:25:19</t>
+          <t>2026/07/22 09:02:26</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>-33.059146,-71.654077</t>
+          <t>-33.256881,-71.439776</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>81.59999999999999</v>
+        <v>106.4</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>258040.3</v>
+        <v>65145.4</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>272.5</v>
+        <v>273.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>2026/07/15 18:01:06</t>
+          <t>2026/07/22 09:03:27</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>-33.095062,-71.598051</t>
+          <t>-33.271995,-71.431471</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>101.7</v>
+        <v>106.9</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>258055.7</v>
+        <v>65147.2</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>432</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>2026/07/15 18:01:10</t>
+          <t>2026/07/22 09:04:26</t>
         </is>
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>-33.094727,-71.596901</t>
+          <t>-33.285196,-71.425764</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>102.4</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>258055.8</v>
+        <v>65148.8</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>432.9</v>
+        <v>336.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B25" s="12" t="n">
@@ -6539,33 +7849,33 @@
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>2026/07/15 18:01:33</t>
+          <t>2026/07/22 09:05:28</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>-33.094594,-71.59094</t>
+          <t>-33.299233,-71.416588</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>84.5</v>
+        <v>105.6</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>258056.4</v>
+        <v>65150.6</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>440.9</v>
+        <v>256.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B26" s="12" t="n">
@@ -6573,33 +7883,33 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>2026/07/15 18:04:10</t>
+          <t>2026/07/22 09:06:28</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>-33.10572,-71.559885</t>
+          <t>-33.312372,-71.404842</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>100.6</v>
+        <v>108.8</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>258060.3</v>
+        <v>65152.5</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>346</v>
+        <v>260.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B27" s="12" t="n">
@@ -6607,33 +7917,33 @@
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>2026/07/15 18:04:20</t>
+          <t>2026/07/22 09:07:28</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>-33.106413,-71.557354</t>
+          <t>-33.324524,-71.3921</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>77.2</v>
+        <v>108.7</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>258060.5</v>
+        <v>65154.3</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>344</v>
+        <v>271.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B28" s="12" t="n">
@@ -6641,33 +7951,33 @@
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>2026/07/15 21:43:31</t>
+          <t>2026/07/22 09:08:29</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>-32.992951,-71.501164</t>
+          <t>-33.335276,-71.378202</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Camino Internacional, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>102.3</v>
+        <v>108.3</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>258132</v>
+        <v>65156.1</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>142.4</v>
+        <v>265.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B29" s="12" t="n">
@@ -6675,639 +7985,4617 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>2026/07/15 21:43:53</t>
+          <t>2026/07/22 09:09:29</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>-32.998213,-71.502356</t>
+          <t>-33.343029,-71.360996</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Ruta 64, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>86.7</v>
+        <v>108.5</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>258132.6</v>
+        <v>65157.9</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>156.7</v>
+        <v>273</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B30" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>2026/07/15 21:52:30</t>
+          <t>2026/07/22 09:10:29</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>-33.058841,-71.530245</t>
+          <t>-33.350755,-71.343674</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>101</v>
+        <v>109.8</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>258144.7</v>
+        <v>65159.8</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>265.4</v>
+        <v>281.7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B31" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>2026/07/15 21:53:09</t>
+          <t>2026/07/22 09:11:29</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>-33.066816,-71.533635</t>
+          <t>-33.358468,-71.326486</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>91.59999999999999</v>
+        <v>108.4</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>258145.7</v>
+        <v>65161.6</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>305.5</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>2026/07/15 22:30:23</t>
+          <t>2026/07/22 09:12:29</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>-33.058737,-71.646769</t>
+          <t>-33.366253,-71.309257</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>102.5</v>
+        <v>108.9</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>258175.8</v>
+        <v>65163.4</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>314.3</v>
+        <v>307.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>2026/07/15 22:30:49</t>
+          <t>2026/07/22 09:13:29</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>-33.062339,-71.641619</t>
+          <t>-33.374795,-71.292789</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>94.5</v>
+        <v>103.8</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>258176.5</v>
+        <v>65165.2</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>355.6</v>
+        <v>329.9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>2026/07/15 22:34:51</t>
+          <t>2026/07/22 09:14:29</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>-33.091601,-71.606396</t>
+          <t>-33.382592,-71.278129</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>109.3</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>258182</v>
+        <v>65166.9</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>432.6</v>
+        <v>400</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>2026/07/15 22:35:28</t>
+          <t>2026/07/22 09:18:29</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>-33.094922,-71.597433</t>
+          <t>-33.403175,-71.216164</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>87.3</v>
+        <v>110.8</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>258183</v>
+        <v>65173.1</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>438.7</v>
+        <v>262.3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>2026/07/15 22:52:43</t>
+          <t>2026/07/22 09:19:29</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>-33.107062,-71.568951</t>
+          <t>-33.40527,-71.196932</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>100.6</v>
+        <v>105.4</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>258196.6</v>
+        <v>65174.9</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>369.4</v>
+        <v>240.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B37" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2026/07/15 22:52:57</t>
+          <t>2026/07/22 09:20:29</t>
         </is>
       </c>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>-33.105882,-71.572602</t>
+          <t>-33.408414,-71.17798</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>88.3</v>
+        <v>100.4</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>258196.9</v>
+        <v>65176.7</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>365.7</v>
+        <v>209.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>GLP SHDV-51 J REBOLLEDO</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>2026/07/13 07:37:39</t>
+          <t>2026/07/22 09:21:29</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>-33.062896,-71.45301</t>
+          <t>-33.412095,-71.159082</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>Autopista Troncal Sur, Quilpué, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>101.3</v>
+        <v>102.5</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>95751.7</v>
+        <v>65178.5</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>182.7</v>
+        <v>196</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>GLP SHDV-51 J REBOLLEDO</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B39" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>2026/07/13 07:38:19</t>
+          <t>2026/07/22 09:22:29</t>
         </is>
       </c>
       <c r="D39" s="15" t="inlineStr">
         <is>
-          <t>-33.06113,-71.463575</t>
+          <t>-33.409931,-71.140659</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Autopista Troncal Sur, Quilpué, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>95.59999999999999</v>
+        <v>105.5</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>95752.7</v>
+        <v>65180.3</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>144.5</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>GC TSVS-89 M AEDO</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B40" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>2026/07/15 07:28:34</t>
+          <t>2026/07/22 09:23:29</t>
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>-32.719794,-71.203983</t>
+          <t>-33.407447,-71.122999</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>100.1</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>112572.3</v>
+        <v>65182.1</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>227.3</v>
+        <v>189.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>GC TSVS-89 M AEDO</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B41" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>2026/07/15 07:29:34</t>
+          <t>2026/07/22 09:24:10</t>
         </is>
       </c>
       <c r="D41" s="15" t="inlineStr">
         <is>
-          <t>-32.70528,-71.206092</t>
+          <t>-33.40112,-71.115029</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>96.2</v>
+        <v>109.6</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>112573.9</v>
+        <v>65183.1</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>234.9</v>
+        <v>191.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>GC TSVS-89 M AEDO</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B42" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>2026/07/15 17:06:01</t>
+          <t>2026/07/22 09:24:29</t>
         </is>
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>-32.621476,-71.228795</t>
+          <t>-33.401131,-71.108913</t>
         </is>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>101.4</v>
+        <v>109.6</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>112747.9</v>
+        <v>65183.7</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>369</v>
+        <v>185.9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>GC TSVS-89 M AEDO</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B43" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>2026/07/15 17:06:17</t>
+          <t>2026/07/22 09:25:29</t>
         </is>
       </c>
       <c r="D43" s="15" t="inlineStr">
         <is>
-          <t>-32.625211,-71.230095</t>
+          <t>-33.404203,-71.089858</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>97.09999999999999</v>
+        <v>108.5</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>112748.4</v>
+        <v>65185.5</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>352.3</v>
+        <v>181.9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>GC TSVS-89 M AEDO</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B44" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>2026/07/15 17:07:17</t>
+          <t>2026/07/22 09:26:29</t>
         </is>
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>-32.639763,-71.232692</t>
+          <t>-33.4079,-71.070976</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>106.4</v>
+        <v>111.5</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>112750</v>
+        <v>65187.3</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>307.8</v>
+        <v>187.6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>GC TSVS-89 M AEDO</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B45" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>2026/07/15 17:08:17</t>
+          <t>2026/07/22 09:27:29</t>
         </is>
       </c>
       <c r="D45" s="15" t="inlineStr">
         <is>
-          <t>-32.652491,-71.223793</t>
+          <t>-33.414364,-71.053484</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>98.3</v>
+        <v>109.1</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>112751.7</v>
+        <v>65189.1</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>256.7</v>
+        <v>179.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>GC TSVS-89 M AEDO</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B46" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>2026/07/15 18:36:45</t>
+          <t>2026/07/22 09:28:29</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>-33.051309,-71.331856</t>
+          <t>-33.425893,-71.03943</t>
         </is>
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>102.5</v>
+        <v>110.9</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>112814.1</v>
+        <v>65190.9</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>203.9</v>
+        <v>187.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 09:29:29</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="inlineStr">
+        <is>
+          <t>-33.437414,-71.025349</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>65192.8</v>
+      </c>
+      <c r="H47" s="12" t="n">
+        <v>195.5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 09:30:15</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>-33.442193,-71.012405</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="n">
+        <v>101</v>
+      </c>
+      <c r="G48" s="12" t="n">
+        <v>65194.1</v>
+      </c>
+      <c r="H48" s="12" t="n">
+        <v>237.1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 09:30:29</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t>-33.440741,-71.008548</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="G49" s="12" t="n">
+        <v>65194.5</v>
+      </c>
+      <c r="H49" s="12" t="n">
+        <v>247.9</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 09:30:44</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>-33.44006,-71.00426</t>
+        </is>
+      </c>
+      <c r="E50" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G50" s="12" t="n">
+        <v>65194.9</v>
+      </c>
+      <c r="H50" s="12" t="n">
+        <v>267.4</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 09:32:29</t>
+        </is>
+      </c>
+      <c r="D51" s="15" t="inlineStr">
+        <is>
+          <t>-33.446799,-70.981751</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="inlineStr">
+        <is>
+          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>65197.5</v>
+      </c>
+      <c r="H51" s="12" t="n">
+        <v>391.1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 09:32:42</t>
+        </is>
+      </c>
+      <c r="D52" s="15" t="inlineStr">
+        <is>
+          <t>-33.449648,-70.980172</t>
+        </is>
+      </c>
+      <c r="E52" s="12" t="inlineStr">
+        <is>
+          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>65197.8</v>
+      </c>
+      <c r="H52" s="12" t="n">
+        <v>409.6</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 09:33:29</t>
+        </is>
+      </c>
+      <c r="D53" s="15" t="inlineStr">
+        <is>
+          <t>-33.456411,-70.96902</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="inlineStr">
+        <is>
+          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="G53" s="12" t="n">
+        <v>65199.1</v>
+      </c>
+      <c r="H53" s="12" t="n">
+        <v>468.9</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 09:34:31</t>
+        </is>
+      </c>
+      <c r="D54" s="15" t="inlineStr">
+        <is>
+          <t>-33.456411,-70.96902</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="inlineStr">
+        <is>
+          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="G54" s="12" t="n">
+        <v>65199.7</v>
+      </c>
+      <c r="H54" s="12" t="n">
+        <v>468.9</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 09:35:31</t>
+        </is>
+      </c>
+      <c r="D55" s="15" t="inlineStr">
+        <is>
+          <t>-33.456411,-70.96902</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="G55" s="12" t="n">
+        <v>65199.7</v>
+      </c>
+      <c r="H55" s="12" t="n">
+        <v>468.9</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B56" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 09:35:45</t>
+        </is>
+      </c>
+      <c r="D56" s="15" t="inlineStr">
+        <is>
+          <t>-33.458044,-70.931695</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="G56" s="12" t="n">
+        <v>65202.7</v>
+      </c>
+      <c r="H56" s="12" t="n">
+        <v>530.1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 09:36:29</t>
+        </is>
+      </c>
+      <c r="D57" s="15" t="inlineStr">
+        <is>
+          <t>-33.457597,-70.917386</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="G57" s="12" t="n">
+        <v>65204</v>
+      </c>
+      <c r="H57" s="12" t="n">
+        <v>508.4</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 09:37:29</t>
+        </is>
+      </c>
+      <c r="D58" s="15" t="inlineStr">
+        <is>
+          <t>-33.456615,-70.898224</t>
+        </is>
+      </c>
+      <c r="E58" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F58" s="12" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="G58" s="12" t="n">
+        <v>65205.8</v>
+      </c>
+      <c r="H58" s="12" t="n">
+        <v>483.4</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 09:38:29</t>
+        </is>
+      </c>
+      <c r="D59" s="15" t="inlineStr">
+        <is>
+          <t>-33.451481,-70.879731</t>
+        </is>
+      </c>
+      <c r="E59" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F59" s="12" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="G59" s="12" t="n">
+        <v>65207.7</v>
+      </c>
+      <c r="H59" s="12" t="n">
+        <v>465.6</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 09:39:29</t>
+        </is>
+      </c>
+      <c r="D60" s="15" t="inlineStr">
+        <is>
+          <t>-33.446593,-70.861109</t>
+        </is>
+      </c>
+      <c r="E60" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F60" s="12" t="n">
+        <v>108</v>
+      </c>
+      <c r="G60" s="12" t="n">
+        <v>65209.5</v>
+      </c>
+      <c r="H60" s="12" t="n">
+        <v>461.5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B61" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 09:40:29</t>
+        </is>
+      </c>
+      <c r="D61" s="15" t="inlineStr">
+        <is>
+          <t>-33.442227,-70.844696</t>
+        </is>
+      </c>
+      <c r="E61" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F61" s="12" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="G61" s="12" t="n">
+        <v>65211.1</v>
+      </c>
+      <c r="H61" s="12" t="n">
+        <v>468.5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="C62" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 09:44:29</t>
+        </is>
+      </c>
+      <c r="D62" s="15" t="inlineStr">
+        <is>
+          <t>-33.424598,-70.798787</t>
+        </is>
+      </c>
+      <c r="E62" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Costanera Norte, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F62" s="12" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="G62" s="12" t="n">
+        <v>65216.9</v>
+      </c>
+      <c r="H62" s="12" t="n">
+        <v>468.6</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B63" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="C63" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 09:45:27</t>
+        </is>
+      </c>
+      <c r="D63" s="15" t="inlineStr">
+        <is>
+          <t>-33.416012,-70.786191</t>
+        </is>
+      </c>
+      <c r="E63" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Costanera Norte, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F63" s="12" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="G63" s="12" t="n">
+        <v>65218.4</v>
+      </c>
+      <c r="H63" s="12" t="n">
+        <v>468.4</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B64" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 09:45:29</t>
+        </is>
+      </c>
+      <c r="D64" s="15" t="inlineStr">
+        <is>
+          <t>-33.415985,-70.785594</t>
+        </is>
+      </c>
+      <c r="E64" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Costanera Norte, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F64" s="12" t="n">
+        <v>101</v>
+      </c>
+      <c r="G64" s="12" t="n">
+        <v>65218.5</v>
+      </c>
+      <c r="H64" s="12" t="n">
+        <v>466.8</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 09:46:29</t>
+        </is>
+      </c>
+      <c r="D65" s="15" t="inlineStr">
+        <is>
+          <t>-33.412913,-70.768448</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Costanera Norte, Renca, Santiago, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F65" s="12" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="G65" s="12" t="n">
+        <v>65220.2</v>
+      </c>
+      <c r="H65" s="12" t="n">
+        <v>478.2</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="C66" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 09:47:29</t>
+        </is>
+      </c>
+      <c r="D66" s="15" t="inlineStr">
+        <is>
+          <t>-33.411607,-70.750867</t>
+        </is>
+      </c>
+      <c r="E66" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Costanera Norte, Renca, Santiago, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F66" s="12" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="G66" s="12" t="n">
+        <v>65221.8</v>
+      </c>
+      <c r="H66" s="12" t="n">
+        <v>483.7</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 09:48:29</t>
+        </is>
+      </c>
+      <c r="D67" s="15" t="inlineStr">
+        <is>
+          <t>-33.411833,-70.731852</t>
+        </is>
+      </c>
+      <c r="E67" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Costanera Norte, Renca, Santiago, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F67" s="12" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="G67" s="12" t="n">
+        <v>65223.6</v>
+      </c>
+      <c r="H67" s="12" t="n">
+        <v>491.6</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B68" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="C68" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:02:44</t>
+        </is>
+      </c>
+      <c r="D68" s="15" t="inlineStr">
+        <is>
+          <t>-33.419429,-70.793301</t>
+        </is>
+      </c>
+      <c r="E68" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Costanera Norte, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F68" s="12" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="G68" s="12" t="n">
+        <v>65238</v>
+      </c>
+      <c r="H68" s="12" t="n">
+        <v>477.9</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:03:44</t>
+        </is>
+      </c>
+      <c r="D69" s="15" t="inlineStr">
+        <is>
+          <t>-33.429227,-70.807823</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Costanera Norte, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F69" s="12" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="G69" s="12" t="n">
+        <v>65239.8</v>
+      </c>
+      <c r="H69" s="12" t="n">
+        <v>465.1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B70" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="C70" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:04:35</t>
+        </is>
+      </c>
+      <c r="D70" s="15" t="inlineStr">
+        <is>
+          <t>-33.438924,-70.81374</t>
+        </is>
+      </c>
+      <c r="E70" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Costanera Norte, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F70" s="12" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="G70" s="12" t="n">
+        <v>65241</v>
+      </c>
+      <c r="H70" s="12" t="n">
+        <v>466.9</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:06:44</t>
+        </is>
+      </c>
+      <c r="D71" s="15" t="inlineStr">
+        <is>
+          <t>-33.442559,-70.846133</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="inlineStr">
+        <is>
+          <t>Camino A Valparaíso, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F71" s="12" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="G71" s="12" t="n">
+        <v>65244.1</v>
+      </c>
+      <c r="H71" s="12" t="n">
+        <v>467.2</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B72" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="C72" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:07:44</t>
+        </is>
+      </c>
+      <c r="D72" s="15" t="inlineStr">
+        <is>
+          <t>-33.447081,-70.86318</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="inlineStr">
+        <is>
+          <t>Camino A Valparaíso, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F72" s="12" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="G72" s="12" t="n">
+        <v>65245.8</v>
+      </c>
+      <c r="H72" s="12" t="n">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B73" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:08:44</t>
+        </is>
+      </c>
+      <c r="D73" s="15" t="inlineStr">
+        <is>
+          <t>-33.45144,-70.879801</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F73" s="12" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="G73" s="12" t="n">
+        <v>65247.4</v>
+      </c>
+      <c r="H73" s="12" t="n">
+        <v>466.1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B74" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="C74" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:09:44</t>
+        </is>
+      </c>
+      <c r="D74" s="15" t="inlineStr">
+        <is>
+          <t>-33.45618,-70.896875</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F74" s="12" t="n">
+        <v>98</v>
+      </c>
+      <c r="G74" s="12" t="n">
+        <v>65249.1</v>
+      </c>
+      <c r="H74" s="12" t="n">
+        <v>481.8</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:13:44</t>
+        </is>
+      </c>
+      <c r="D75" s="15" t="inlineStr">
+        <is>
+          <t>-33.45651,-70.968755</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F75" s="12" t="n">
+        <v>108</v>
+      </c>
+      <c r="G75" s="12" t="n">
+        <v>65255.9</v>
+      </c>
+      <c r="H75" s="12" t="n">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B76" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="C76" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:14:42</t>
+        </is>
+      </c>
+      <c r="D76" s="15" t="inlineStr">
+        <is>
+          <t>-33.446769,-70.981665</t>
+        </is>
+      </c>
+      <c r="E76" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F76" s="12" t="n">
+        <v>101</v>
+      </c>
+      <c r="G76" s="12" t="n">
+        <v>65257.5</v>
+      </c>
+      <c r="H76" s="12" t="n">
+        <v>390.1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:14:44</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="inlineStr">
+        <is>
+          <t>-33.446256,-70.981656</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F77" s="12" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="G77" s="12" t="n">
+        <v>65257.6</v>
+      </c>
+      <c r="H77" s="12" t="n">
+        <v>388.7</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B78" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:14:58</t>
+        </is>
+      </c>
+      <c r="D78" s="15" t="inlineStr">
+        <is>
+          <t>-33.443085,-70.983097</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="inlineStr">
+        <is>
+          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F78" s="12" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="G78" s="12" t="n">
+        <v>65258</v>
+      </c>
+      <c r="H78" s="12" t="n">
+        <v>372.9</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:16:44</t>
+        </is>
+      </c>
+      <c r="D79" s="15" t="inlineStr">
+        <is>
+          <t>-33.442058,-71.011834</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F79" s="12" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="G79" s="12" t="n">
+        <v>65260.9</v>
+      </c>
+      <c r="H79" s="12" t="n">
+        <v>238.1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C80" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:17:25</t>
+        </is>
+      </c>
+      <c r="D80" s="15" t="inlineStr">
+        <is>
+          <t>-33.438093,-71.023991</t>
+        </is>
+      </c>
+      <c r="E80" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F80" s="12" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="G80" s="12" t="n">
+        <v>65262.1</v>
+      </c>
+      <c r="H80" s="12" t="n">
+        <v>194.2</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B81" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:17:44</t>
+        </is>
+      </c>
+      <c r="D81" s="15" t="inlineStr">
+        <is>
+          <t>-33.434804,-71.028527</t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="inlineStr">
+        <is>
+          <t>s/n, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F81" s="12" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="G81" s="12" t="n">
+        <v>65262.7</v>
+      </c>
+      <c r="H81" s="12" t="n">
+        <v>193.8</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B82" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:18:44</t>
+        </is>
+      </c>
+      <c r="D82" s="15" t="inlineStr">
+        <is>
+          <t>-33.42387,-71.041797</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F82" s="12" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="G82" s="12" t="n">
+        <v>65264.4</v>
+      </c>
+      <c r="H82" s="12" t="n">
+        <v>183.4</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B83" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:19:44</t>
+        </is>
+      </c>
+      <c r="D83" s="15" t="inlineStr">
+        <is>
+          <t>-33.412894,-71.055501</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="inlineStr">
+        <is>
+          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F83" s="12" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="G83" s="12" t="n">
+        <v>65266.2</v>
+      </c>
+      <c r="H83" s="12" t="n">
+        <v>183.7</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B84" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:20:44</t>
+        </is>
+      </c>
+      <c r="D84" s="15" t="inlineStr">
+        <is>
+          <t>-33.407271,-71.073586</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="inlineStr">
+        <is>
+          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>65268</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>188.2</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B85" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:21:44</t>
+        </is>
+      </c>
+      <c r="D85" s="15" t="inlineStr">
+        <is>
+          <t>-33.403508,-71.092758</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="inlineStr">
+        <is>
+          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F85" s="12" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="G85" s="12" t="n">
+        <v>65269.8</v>
+      </c>
+      <c r="H85" s="12" t="n">
+        <v>182.8</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B86" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="C86" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:22:44</t>
+        </is>
+      </c>
+      <c r="D86" s="15" t="inlineStr">
+        <is>
+          <t>-33.401012,-71.111695</t>
+        </is>
+      </c>
+      <c r="E86" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F86" s="12" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="G86" s="12" t="n">
+        <v>65271.6</v>
+      </c>
+      <c r="H86" s="12" t="n">
+        <v>187.8</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B87" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="C87" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:23:09</t>
+        </is>
+      </c>
+      <c r="D87" s="15" t="inlineStr">
+        <is>
+          <t>-33.402891,-71.119196</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F87" s="12" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="G87" s="12" t="n">
+        <v>65272.3</v>
+      </c>
+      <c r="H87" s="12" t="n">
+        <v>199.6</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B88" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:23:44</t>
+        </is>
+      </c>
+      <c r="D88" s="15" t="inlineStr">
+        <is>
+          <t>-33.409251,-71.127083</t>
+        </is>
+      </c>
+      <c r="E88" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F88" s="12" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="G88" s="12" t="n">
+        <v>65273.4</v>
+      </c>
+      <c r="H88" s="12" t="n">
+        <v>191.6</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B89" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="C89" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:24:44</t>
+        </is>
+      </c>
+      <c r="D89" s="15" t="inlineStr">
+        <is>
+          <t>-33.411612,-71.145894</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F89" s="12" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="G89" s="12" t="n">
+        <v>65275.2</v>
+      </c>
+      <c r="H89" s="12" t="n">
+        <v>194.8</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B90" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="C90" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:25:44</t>
+        </is>
+      </c>
+      <c r="D90" s="15" t="inlineStr">
+        <is>
+          <t>-33.410945,-71.164731</t>
+        </is>
+      </c>
+      <c r="E90" s="12" t="inlineStr">
+        <is>
+          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F90" s="12" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="G90" s="12" t="n">
+        <v>65277.1</v>
+      </c>
+      <c r="H90" s="12" t="n">
+        <v>201.5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B91" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="C91" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:26:44</t>
+        </is>
+      </c>
+      <c r="D91" s="15" t="inlineStr">
+        <is>
+          <t>-33.407166,-71.183775</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="inlineStr">
+        <is>
+          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F91" s="12" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="G91" s="12" t="n">
+        <v>65278.9</v>
+      </c>
+      <c r="H91" s="12" t="n">
+        <v>218.2</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B92" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="C92" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:27:44</t>
+        </is>
+      </c>
+      <c r="D92" s="15" t="inlineStr">
+        <is>
+          <t>-33.405465,-71.202733</t>
+        </is>
+      </c>
+      <c r="E92" s="12" t="inlineStr">
+        <is>
+          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F92" s="12" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="G92" s="12" t="n">
+        <v>65280.7</v>
+      </c>
+      <c r="H92" s="12" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B93" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:28:44</t>
+        </is>
+      </c>
+      <c r="D93" s="15" t="inlineStr">
+        <is>
+          <t>-33.401162,-71.221267</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="inlineStr">
+        <is>
+          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F93" s="12" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="G93" s="12" t="n">
+        <v>65282.5</v>
+      </c>
+      <c r="H93" s="12" t="n">
+        <v>271.2</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B94" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:29:44</t>
+        </is>
+      </c>
+      <c r="D94" s="15" t="inlineStr">
+        <is>
+          <t>-33.395823,-71.237249</t>
+        </is>
+      </c>
+      <c r="E94" s="12" t="inlineStr">
+        <is>
+          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F94" s="12" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="G94" s="12" t="n">
+        <v>65284.1</v>
+      </c>
+      <c r="H94" s="12" t="n">
+        <v>334.2</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B95" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="C95" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:30:44</t>
+        </is>
+      </c>
+      <c r="D95" s="15" t="inlineStr">
+        <is>
+          <t>-33.39194,-71.252428</t>
+        </is>
+      </c>
+      <c r="E95" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F95" s="12" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="G95" s="12" t="n">
+        <v>65285.6</v>
+      </c>
+      <c r="H95" s="12" t="n">
+        <v>420.2</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B96" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:32:44</t>
+        </is>
+      </c>
+      <c r="D96" s="15" t="inlineStr">
+        <is>
+          <t>-33.378054,-71.283</t>
+        </is>
+      </c>
+      <c r="E96" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F96" s="12" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="G96" s="12" t="n">
+        <v>65288.8</v>
+      </c>
+      <c r="H96" s="12" t="n">
+        <v>358.8</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B97" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="C97" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:33:44</t>
+        </is>
+      </c>
+      <c r="D97" s="15" t="inlineStr">
+        <is>
+          <t>-33.370564,-71.300398</t>
+        </is>
+      </c>
+      <c r="E97" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F97" s="12" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="G97" s="12" t="n">
+        <v>65290.7</v>
+      </c>
+      <c r="H97" s="12" t="n">
+        <v>309.9</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B98" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="C98" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:34:44</t>
+        </is>
+      </c>
+      <c r="D98" s="15" t="inlineStr">
+        <is>
+          <t>-33.362495,-71.317435</t>
+        </is>
+      </c>
+      <c r="E98" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F98" s="12" t="n">
+        <v>105</v>
+      </c>
+      <c r="G98" s="12" t="n">
+        <v>65292.5</v>
+      </c>
+      <c r="H98" s="12" t="n">
+        <v>302.8</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B99" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="C99" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:35:44</t>
+        </is>
+      </c>
+      <c r="D99" s="15" t="inlineStr">
+        <is>
+          <t>-33.354711,-71.334664</t>
+        </is>
+      </c>
+      <c r="E99" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F99" s="12" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="G99" s="12" t="n">
+        <v>65294.3</v>
+      </c>
+      <c r="H99" s="12" t="n">
+        <v>288.5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B100" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="C100" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:36:44</t>
+        </is>
+      </c>
+      <c r="D100" s="15" t="inlineStr">
+        <is>
+          <t>-33.346987,-71.351864</t>
+        </is>
+      </c>
+      <c r="E100" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F100" s="12" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="G100" s="12" t="n">
+        <v>65296.1</v>
+      </c>
+      <c r="H100" s="12" t="n">
+        <v>278.2</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B101" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:37:44</t>
+        </is>
+      </c>
+      <c r="D101" s="15" t="inlineStr">
+        <is>
+          <t>-33.339269,-71.36912</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F101" s="12" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="G101" s="12" t="n">
+        <v>65297.9</v>
+      </c>
+      <c r="H101" s="12" t="n">
+        <v>270.6</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B102" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="C102" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:38:44</t>
+        </is>
+      </c>
+      <c r="D102" s="15" t="inlineStr">
+        <is>
+          <t>-33.331501,-71.38635</t>
+        </is>
+      </c>
+      <c r="E102" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F102" s="12" t="n">
+        <v>109</v>
+      </c>
+      <c r="G102" s="12" t="n">
+        <v>65299.8</v>
+      </c>
+      <c r="H102" s="12" t="n">
+        <v>264.2</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:39:44</t>
+        </is>
+      </c>
+      <c r="D103" s="15" t="inlineStr">
+        <is>
+          <t>-33.318513,-71.397761</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F103" s="12" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="G103" s="12" t="n">
+        <v>65301.6</v>
+      </c>
+      <c r="H103" s="12" t="n">
+        <v>265.6</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B104" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 11:40:44</t>
+        </is>
+      </c>
+      <c r="D104" s="15" t="inlineStr">
+        <is>
+          <t>-33.306928,-71.409003</t>
+        </is>
+      </c>
+      <c r="E104" s="12" t="inlineStr">
+        <is>
+          <t>s/n, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F104" s="12" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="G104" s="12" t="n">
+        <v>65303.2</v>
+      </c>
+      <c r="H104" s="12" t="n">
+        <v>264.2</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 12:06:08</t>
+        </is>
+      </c>
+      <c r="D105" s="15" t="inlineStr">
+        <is>
+          <t>-33.224113,-71.469302</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F105" s="12" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="G105" s="12" t="n">
+        <v>65314.8</v>
+      </c>
+      <c r="H105" s="12" t="n">
+        <v>326.5</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B106" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="C106" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 12:07:08</t>
+        </is>
+      </c>
+      <c r="D106" s="15" t="inlineStr">
+        <is>
+          <t>-33.210556,-71.478677</t>
+        </is>
+      </c>
+      <c r="E106" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F106" s="12" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="G106" s="12" t="n">
+        <v>65316.6</v>
+      </c>
+      <c r="H106" s="12" t="n">
+        <v>365.5</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B107" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="C107" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 12:08:08</t>
+        </is>
+      </c>
+      <c r="D107" s="15" t="inlineStr">
+        <is>
+          <t>-33.198961,-71.490969</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F107" s="12" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="G107" s="12" t="n">
+        <v>65318.3</v>
+      </c>
+      <c r="H107" s="12" t="n">
+        <v>376.3</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B108" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="C108" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 12:09:08</t>
+        </is>
+      </c>
+      <c r="D108" s="15" t="inlineStr">
+        <is>
+          <t>-33.185309,-71.501905</t>
+        </is>
+      </c>
+      <c r="E108" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F108" s="12" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="G108" s="12" t="n">
+        <v>65320.1</v>
+      </c>
+      <c r="H108" s="12" t="n">
+        <v>351.2</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 12:10:08</t>
+        </is>
+      </c>
+      <c r="D109" s="15" t="inlineStr">
+        <is>
+          <t>-33.174444,-71.51614</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F109" s="12" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="G109" s="12" t="n">
+        <v>65322</v>
+      </c>
+      <c r="H109" s="12" t="n">
+        <v>348.7</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B110" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="C110" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 12:11:08</t>
+        </is>
+      </c>
+      <c r="D110" s="15" t="inlineStr">
+        <is>
+          <t>-33.166486,-71.531748</t>
+        </is>
+      </c>
+      <c r="E110" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F110" s="12" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="G110" s="12" t="n">
+        <v>65323.7</v>
+      </c>
+      <c r="H110" s="12" t="n">
+        <v>349.1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B111" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 12:12:08</t>
+        </is>
+      </c>
+      <c r="D111" s="15" t="inlineStr">
+        <is>
+          <t>-33.159788,-71.544855</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F111" s="12" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="G111" s="12" t="n">
+        <v>65325.1</v>
+      </c>
+      <c r="H111" s="12" t="n">
+        <v>368.7</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B112" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="C112" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 12:13:08</t>
+        </is>
+      </c>
+      <c r="D112" s="15" t="inlineStr">
+        <is>
+          <t>-33.14935,-71.55852</t>
+        </is>
+      </c>
+      <c r="E112" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F112" s="12" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="G112" s="12" t="n">
+        <v>65326.9</v>
+      </c>
+      <c r="H112" s="12" t="n">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B113" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="C113" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 12:14:08</t>
+        </is>
+      </c>
+      <c r="D113" s="15" t="inlineStr">
+        <is>
+          <t>-33.133708,-71.562403</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F113" s="12" t="n">
+        <v>104</v>
+      </c>
+      <c r="G113" s="12" t="n">
+        <v>65328.7</v>
+      </c>
+      <c r="H113" s="12" t="n">
+        <v>324.6</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B114" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="C114" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 12:15:08</t>
+        </is>
+      </c>
+      <c r="D114" s="15" t="inlineStr">
+        <is>
+          <t>-33.11785,-71.560635</t>
+        </is>
+      </c>
+      <c r="E114" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F114" s="12" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="G114" s="12" t="n">
+        <v>65330.5</v>
+      </c>
+      <c r="H114" s="12" t="n">
+        <v>338.9</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B115" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C115" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 14:08:42</t>
+        </is>
+      </c>
+      <c r="D115" s="15" t="inlineStr">
+        <is>
+          <t>-33.107,-71.569879</t>
+        </is>
+      </c>
+      <c r="E115" s="12" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="F115" s="12" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="G115" s="12" t="n">
+        <v>260780.3</v>
+      </c>
+      <c r="H115" s="12" t="n">
+        <v>367.9</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B116" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C116" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 14:08:46</t>
+        </is>
+      </c>
+      <c r="D116" s="15" t="inlineStr">
+        <is>
+          <t>-33.107137,-71.568647</t>
+        </is>
+      </c>
+      <c r="E116" s="12" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="F116" s="12" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="G116" s="12" t="n">
+        <v>260780.4</v>
+      </c>
+      <c r="H116" s="12" t="n">
+        <v>368.1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B117" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 14:09:27</t>
+        </is>
+      </c>
+      <c r="D117" s="15" t="inlineStr">
+        <is>
+          <t>-33.106817,-71.556895</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="F117" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="G117" s="12" t="n">
+        <v>260781.6</v>
+      </c>
+      <c r="H117" s="12" t="n">
+        <v>349.4</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B118" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C118" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 14:47:45</t>
+        </is>
+      </c>
+      <c r="D118" s="15" t="inlineStr">
+        <is>
+          <t>-33.115854,-71.560497</t>
+        </is>
+      </c>
+      <c r="E118" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F118" s="12" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="G118" s="12" t="n">
+        <v>260816.5</v>
+      </c>
+      <c r="H118" s="12" t="n">
+        <v>339.4</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B119" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 14:48:14</t>
+        </is>
+      </c>
+      <c r="D119" s="15" t="inlineStr">
+        <is>
+          <t>-33.121168,-71.561407</t>
+        </is>
+      </c>
+      <c r="E119" s="12" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F119" s="12" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="G119" s="12" t="n">
+        <v>260817.1</v>
+      </c>
+      <c r="H119" s="12" t="n">
+        <v>352.1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B120" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C120" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/24 20:27:40</t>
+        </is>
+      </c>
+      <c r="D120" s="15" t="inlineStr">
+        <is>
+          <t>-33.106894,-71.550205</t>
+        </is>
+      </c>
+      <c r="E120" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F120" s="12" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="G120" s="12" t="n">
+        <v>261242.2</v>
+      </c>
+      <c r="H120" s="12" t="n">
+        <v>352.2</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B121" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/24 20:27:48</t>
+        </is>
+      </c>
+      <c r="D121" s="15" t="inlineStr">
+        <is>
+          <t>-33.10767,-71.55247</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F121" s="12" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="G121" s="12" t="n">
+        <v>261242.5</v>
+      </c>
+      <c r="H121" s="12" t="n">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B122" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C122" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/24 20:28:16</t>
+        </is>
+      </c>
+      <c r="D122" s="15" t="inlineStr">
+        <is>
+          <t>-33.111025,-71.559678</t>
+        </is>
+      </c>
+      <c r="E122" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F122" s="12" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="G122" s="12" t="n">
+        <v>261243.2</v>
+      </c>
+      <c r="H122" s="12" t="n">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B123" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C123" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/24 20:28:48</t>
+        </is>
+      </c>
+      <c r="D123" s="15" t="inlineStr">
+        <is>
+          <t>-33.118716,-71.56082</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F123" s="12" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="G123" s="12" t="n">
+        <v>261244.1</v>
+      </c>
+      <c r="H123" s="12" t="n">
+        <v>343.8</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 RXDL-61 OPERACIONES</t>
+        </is>
+      </c>
+      <c r="B124" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C124" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 14:19:11</t>
+        </is>
+      </c>
+      <c r="D124" s="15" t="inlineStr">
+        <is>
+          <t>-33.078618,-71.626482</t>
+        </is>
+      </c>
+      <c r="E124" s="12" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="F124" s="12" t="n">
+        <v>109</v>
+      </c>
+      <c r="G124" s="12" t="n">
+        <v>174133</v>
+      </c>
+      <c r="H124" s="12" t="n">
+        <v>452.6</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 RXDL-61 OPERACIONES</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C125" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/22 14:20:10</t>
+        </is>
+      </c>
+      <c r="D125" s="15" t="inlineStr">
+        <is>
+          <t>-33.067049,-71.633956</t>
+        </is>
+      </c>
+      <c r="E125" s="12" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="F125" s="12" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="G125" s="12" t="n">
+        <v>174134.6</v>
+      </c>
+      <c r="H125" s="12" t="n">
+        <v>433.3</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 RXDL-61 OPERACIONES</t>
+        </is>
+      </c>
+      <c r="B126" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C126" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/23 09:31:40</t>
+        </is>
+      </c>
+      <c r="D126" s="15" t="inlineStr">
+        <is>
+          <t>-32.983884,-71.500411</t>
+        </is>
+      </c>
+      <c r="E126" s="12" t="inlineStr">
+        <is>
+          <t>Camino Internacional Valparaíso - Mendoza, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F126" s="12" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="G126" s="12" t="n">
+        <v>174523.8</v>
+      </c>
+      <c r="H126" s="12" t="n">
+        <v>122.9</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 RXDL-61 OPERACIONES</t>
+        </is>
+      </c>
+      <c r="B127" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C127" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/23 09:32:40</t>
+        </is>
+      </c>
+      <c r="D127" s="15" t="inlineStr">
+        <is>
+          <t>-32.996284,-71.501418</t>
+        </is>
+      </c>
+      <c r="E127" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 64, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="F127" s="12" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="G127" s="12" t="n">
+        <v>174525.2</v>
+      </c>
+      <c r="H127" s="12" t="n">
+        <v>140.1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 RXDL-61 OPERACIONES</t>
+        </is>
+      </c>
+      <c r="B128" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C128" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/23 10:03:32</t>
+        </is>
+      </c>
+      <c r="D128" s="15" t="inlineStr">
+        <is>
+          <t>-33.088351,-71.542177</t>
+        </is>
+      </c>
+      <c r="E128" s="12" t="inlineStr">
+        <is>
+          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="F128" s="12" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="G128" s="12" t="n">
+        <v>174563.5</v>
+      </c>
+      <c r="H128" s="12" t="n">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 RXDL-61 OPERACIONES</t>
+        </is>
+      </c>
+      <c r="B129" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C129" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/23 10:03:44</t>
+        </is>
+      </c>
+      <c r="D129" s="15" t="inlineStr">
+        <is>
+          <t>-33.085761,-71.544134</t>
+        </is>
+      </c>
+      <c r="E129" s="12" t="inlineStr">
+        <is>
+          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F129" s="12" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="G129" s="12" t="n">
+        <v>174563.8</v>
+      </c>
+      <c r="H129" s="12" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 RXDL-61 OPERACIONES</t>
+        </is>
+      </c>
+      <c r="B130" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C130" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/23 10:04:19</t>
+        </is>
+      </c>
+      <c r="D130" s="15" t="inlineStr">
+        <is>
+          <t>-33.078217,-71.546978</t>
+        </is>
+      </c>
+      <c r="E130" s="12" t="inlineStr">
+        <is>
+          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F130" s="12" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="G130" s="12" t="n">
+        <v>174564.7</v>
+      </c>
+      <c r="H130" s="12" t="n">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 RXDL-61 OPERACIONES</t>
+        </is>
+      </c>
+      <c r="B131" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C131" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/23 10:06:00</t>
+        </is>
+      </c>
+      <c r="D131" s="15" t="inlineStr">
+        <is>
+          <t>-33.065183,-71.531366</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="inlineStr">
+        <is>
+          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F131" s="12" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="G131" s="12" t="n">
+        <v>174566.9</v>
+      </c>
+      <c r="H131" s="12" t="n">
+        <v>295.5</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 RXDL-61 OPERACIONES</t>
+        </is>
+      </c>
+      <c r="B132" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C132" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/23 10:06:13</t>
+        </is>
+      </c>
+      <c r="D132" s="15" t="inlineStr">
+        <is>
+          <t>-33.062309,-71.530029</t>
+        </is>
+      </c>
+      <c r="E132" s="12" t="inlineStr">
+        <is>
+          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F132" s="12" t="n">
+        <v>98</v>
+      </c>
+      <c r="G132" s="12" t="n">
+        <v>174567.3</v>
+      </c>
+      <c r="H132" s="12" t="n">
+        <v>278.3</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 RXDL-61 OPERACIONES</t>
+        </is>
+      </c>
+      <c r="B133" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C133" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/23 10:13:01</t>
+        </is>
+      </c>
+      <c r="D133" s="15" t="inlineStr">
+        <is>
+          <t>-33.01484,-71.499892</t>
+        </is>
+      </c>
+      <c r="E133" s="12" t="inlineStr">
+        <is>
+          <t>Camino Internacional Valparaíso - Mendoza, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F133" s="12" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="G133" s="12" t="n">
+        <v>174576.8</v>
+      </c>
+      <c r="H133" s="12" t="n">
+        <v>235.2</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 RXDL-61 OPERACIONES</t>
+        </is>
+      </c>
+      <c r="B134" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C134" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/23 10:13:44</t>
+        </is>
+      </c>
+      <c r="D134" s="15" t="inlineStr">
+        <is>
+          <t>-33.00551,-71.508908</t>
+        </is>
+      </c>
+      <c r="E134" s="12" t="inlineStr">
+        <is>
+          <t>Camino Internacional Valparaíso - Mendoza, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F134" s="12" t="n">
+        <v>103</v>
+      </c>
+      <c r="G134" s="12" t="n">
+        <v>174578.1</v>
+      </c>
+      <c r="H134" s="12" t="n">
+        <v>204.9</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 RXDL-61 OPERACIONES</t>
+        </is>
+      </c>
+      <c r="B135" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C135" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/23 10:13:56</t>
+        </is>
+      </c>
+      <c r="D135" s="15" t="inlineStr">
+        <is>
+          <t>-33.002751,-71.510215</t>
+        </is>
+      </c>
+      <c r="E135" s="12" t="inlineStr">
+        <is>
+          <t>Avenida Carlos Ibáñez del Campo, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="F135" s="12" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="G135" s="12" t="n">
+        <v>174578.4</v>
+      </c>
+      <c r="H135" s="12" t="n">
+        <v>200.8</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 RXDL-61 OPERACIONES</t>
+        </is>
+      </c>
+      <c r="B136" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C136" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/23 10:18:44</t>
+        </is>
+      </c>
+      <c r="D136" s="15" t="inlineStr">
+        <is>
+          <t>-32.949168,-71.510894</t>
+        </is>
+      </c>
+      <c r="E136" s="12" t="inlineStr">
+        <is>
+          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="F136" s="12" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="G136" s="12" t="n">
+        <v>174585.7</v>
+      </c>
+      <c r="H136" s="12" t="n">
+        <v>151.7</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 RXDL-61 OPERACIONES</t>
+        </is>
+      </c>
+      <c r="B137" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C137" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/23 10:19:44</t>
+        </is>
+      </c>
+      <c r="D137" s="15" t="inlineStr">
+        <is>
+          <t>-32.933913,-71.513453</t>
+        </is>
+      </c>
+      <c r="E137" s="12" t="inlineStr">
+        <is>
+          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="F137" s="12" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="G137" s="12" t="n">
+        <v>174587.4</v>
+      </c>
+      <c r="H137" s="12" t="n">
+        <v>71.59999999999999</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 RXDL-61 OPERACIONES</t>
+        </is>
+      </c>
+      <c r="B138" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C138" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/24 20:12:46</t>
+        </is>
+      </c>
+      <c r="D138" s="15" t="inlineStr">
+        <is>
+          <t>-32.981829,-71.500282</t>
+        </is>
+      </c>
+      <c r="E138" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 64, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F138" s="12" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="G138" s="12" t="n">
+        <v>175199.2</v>
+      </c>
+      <c r="H138" s="12" t="n">
+        <v>123.4</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 RXDL-61 OPERACIONES</t>
+        </is>
+      </c>
+      <c r="B139" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C139" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/24 20:13:47</t>
+        </is>
+      </c>
+      <c r="D139" s="15" t="inlineStr">
+        <is>
+          <t>-32.9948,-71.501299</t>
+        </is>
+      </c>
+      <c r="E139" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 64, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F139" s="12" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="G139" s="12" t="n">
+        <v>175200.7</v>
+      </c>
+      <c r="H139" s="12" t="n">
+        <v>138.7</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 RXDL-61 OPERACIONES</t>
+        </is>
+      </c>
+      <c r="B140" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C140" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/24 20:24:48</t>
+        </is>
+      </c>
+      <c r="D140" s="15" t="inlineStr">
+        <is>
+          <t>-33.075325,-71.544371</t>
+        </is>
+      </c>
+      <c r="E140" s="12" t="inlineStr">
+        <is>
+          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F140" s="12" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="G140" s="12" t="n">
+        <v>175215.7</v>
+      </c>
+      <c r="H140" s="12" t="n">
+        <v>343.2</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 RXDL-61 OPERACIONES</t>
+        </is>
+      </c>
+      <c r="B141" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C141" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/24 20:25:12</t>
+        </is>
+      </c>
+      <c r="D141" s="15" t="inlineStr">
+        <is>
+          <t>-33.078418,-71.548691</t>
+        </is>
+      </c>
+      <c r="E141" s="12" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F141" s="12" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="G141" s="12" t="n">
+        <v>175216.2</v>
+      </c>
+      <c r="H141" s="12" t="n">
+        <v>321.2</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 RXDL-61 OPERACIONES</t>
+        </is>
+      </c>
+      <c r="B142" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="C142" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/24 20:26:12</t>
+        </is>
+      </c>
+      <c r="D142" s="15" t="inlineStr">
+        <is>
+          <t>-33.090191,-71.541746</t>
+        </is>
+      </c>
+      <c r="E142" s="12" t="inlineStr">
+        <is>
+          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="F142" s="12" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="G142" s="12" t="n">
+        <v>175217.7</v>
+      </c>
+      <c r="H142" s="12" t="n">
+        <v>320.6</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 RXDL-61 OPERACIONES</t>
+        </is>
+      </c>
+      <c r="B143" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="C143" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/24 20:26:32</t>
+        </is>
+      </c>
+      <c r="D143" s="15" t="inlineStr">
+        <is>
+          <t>-33.094784,-71.543372</t>
+        </is>
+      </c>
+      <c r="E143" s="12" t="inlineStr">
+        <is>
+          <t>Vía Las Palmas, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="F143" s="12" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="G143" s="12" t="n">
+        <v>175218.3</v>
+      </c>
+      <c r="H143" s="12" t="n">
+        <v>313.6</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 RXDL-61 OPERACIONES</t>
+        </is>
+      </c>
+      <c r="B144" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="C144" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/24 20:26:50</t>
+        </is>
+      </c>
+      <c r="D144" s="15" t="inlineStr">
+        <is>
+          <t>-33.097308,-71.547427</t>
+        </is>
+      </c>
+      <c r="E144" s="12" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="F144" s="12" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="G144" s="12" t="n">
+        <v>175218.8</v>
+      </c>
+      <c r="H144" s="12" t="n">
+        <v>319.2</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 RXDL-61 OPERACIONES</t>
+        </is>
+      </c>
+      <c r="B145" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C145" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/24 20:28:16</t>
+        </is>
+      </c>
+      <c r="D145" s="15" t="inlineStr">
+        <is>
+          <t>-33.111189,-71.559772</t>
+        </is>
+      </c>
+      <c r="E145" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F145" s="12" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="G145" s="12" t="n">
+        <v>175221</v>
+      </c>
+      <c r="H145" s="12" t="n">
+        <v>345.3</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 RXDL-61 OPERACIONES</t>
+        </is>
+      </c>
+      <c r="B146" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C146" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/24 20:28:49</t>
+        </is>
+      </c>
+      <c r="D146" s="15" t="inlineStr">
+        <is>
+          <t>-33.119619,-71.560914</t>
+        </is>
+      </c>
+      <c r="E146" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F146" s="12" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="G146" s="12" t="n">
+        <v>175221.9</v>
+      </c>
+      <c r="H146" s="12" t="n">
+        <v>347.4</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 RXDL-61 OPERACIONES</t>
+        </is>
+      </c>
+      <c r="B147" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C147" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/24 20:56:46</t>
+        </is>
+      </c>
+      <c r="D147" s="15" t="inlineStr">
+        <is>
+          <t>-33.079385,-71.626351</t>
+        </is>
+      </c>
+      <c r="E147" s="12" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="F147" s="12" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="G147" s="12" t="n">
+        <v>175236.5</v>
+      </c>
+      <c r="H147" s="12" t="n">
+        <v>460.8</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 RXDL-61 OPERACIONES</t>
+        </is>
+      </c>
+      <c r="B148" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="C148" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/24 20:57:46</t>
+        </is>
+      </c>
+      <c r="D148" s="15" t="inlineStr">
+        <is>
+          <t>-33.06751,-71.633245</t>
+        </is>
+      </c>
+      <c r="E148" s="12" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="F148" s="12" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="G148" s="12" t="n">
+        <v>175238.1</v>
+      </c>
+      <c r="H148" s="12" t="n">
+        <v>436.3</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 RXDL-61 OPERACIONES</t>
+        </is>
+      </c>
+      <c r="B149" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="C149" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/24 20:58:04</t>
+        </is>
+      </c>
+      <c r="D149" s="15" t="inlineStr">
+        <is>
+          <t>-33.066265,-71.637746</t>
+        </is>
+      </c>
+      <c r="E149" s="12" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="F149" s="12" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="G149" s="12" t="n">
+        <v>175238.5</v>
+      </c>
+      <c r="H149" s="12" t="n">
+        <v>415.3</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 RXDL-61 OPERACIONES</t>
+        </is>
+      </c>
+      <c r="B150" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="C150" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/25 21:08:17</t>
+        </is>
+      </c>
+      <c r="D150" s="15" t="inlineStr">
+        <is>
+          <t>-33.066598,-71.635033</t>
+        </is>
+      </c>
+      <c r="E150" s="12" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="F150" s="12" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="G150" s="12" t="n">
+        <v>175669.8</v>
+      </c>
+      <c r="H150" s="12" t="n">
+        <v>431.4</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 RXDL-61 OPERACIONES</t>
+        </is>
+      </c>
+      <c r="B151" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="C151" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/25 21:08:54</t>
+        </is>
+      </c>
+      <c r="D151" s="15" t="inlineStr">
+        <is>
+          <t>-33.072071,-71.62779</t>
+        </is>
+      </c>
+      <c r="E151" s="12" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="F151" s="12" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="G151" s="12" t="n">
+        <v>175670.8</v>
+      </c>
+      <c r="H151" s="12" t="n">
+        <v>431.3</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="7" t="inlineStr">
+        <is>
+          <t>GLP SKDX-44 V VIAL</t>
+        </is>
+      </c>
+      <c r="B152" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C152" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/23 07:47:11</t>
+        </is>
+      </c>
+      <c r="D152" s="15" t="inlineStr">
+        <is>
+          <t>-33.028376,-71.652639</t>
+        </is>
+      </c>
+      <c r="E152" s="12" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora Costero, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F152" s="12" t="n">
+        <v>141.7</v>
+      </c>
+      <c r="G152" s="12" t="n">
+        <v>145184.4</v>
+      </c>
+      <c r="H152" s="12" t="n">
+        <v>91.59999999999999</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="7" t="inlineStr">
+        <is>
+          <t>GLP SKDX-44 V VIAL</t>
+        </is>
+      </c>
+      <c r="B153" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C153" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/23 07:47:11</t>
+        </is>
+      </c>
+      <c r="D153" s="15" t="inlineStr">
+        <is>
+          <t>-33.028376,-71.652639</t>
+        </is>
+      </c>
+      <c r="E153" s="12" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora Costero, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F153" s="12" t="n">
+        <v>141.7</v>
+      </c>
+      <c r="G153" s="12" t="n">
+        <v>145184.4</v>
+      </c>
+      <c r="H153" s="12" t="n">
+        <v>91.59999999999999</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="7" t="inlineStr">
+        <is>
+          <t>GLP SKDX-44 V VIAL</t>
+        </is>
+      </c>
+      <c r="B154" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C154" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/23 07:47:58</t>
+        </is>
+      </c>
+      <c r="D154" s="15" t="inlineStr">
+        <is>
+          <t>-33.028376,-71.652639</t>
+        </is>
+      </c>
+      <c r="E154" s="12" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora Costero, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F154" s="12" t="n">
+        <v>141.7</v>
+      </c>
+      <c r="G154" s="12" t="n">
+        <v>145184.5</v>
+      </c>
+      <c r="H154" s="12" t="n">
+        <v>91.59999999999999</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="7" t="inlineStr">
+        <is>
+          <t>GLP SKDX-44 V VIAL</t>
+        </is>
+      </c>
+      <c r="B155" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C155" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/23 07:48:56</t>
+        </is>
+      </c>
+      <c r="D155" s="15" t="inlineStr">
+        <is>
+          <t>-33.032598,-71.629362</t>
+        </is>
+      </c>
+      <c r="E155" s="12" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F155" s="12" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="G155" s="12" t="n">
+        <v>145186.8</v>
+      </c>
+      <c r="H155" s="12" t="n">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="7" t="inlineStr">
+        <is>
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B47" s="12" t="n">
+      <c r="B156" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C156" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/24 19:07:17</t>
+        </is>
+      </c>
+      <c r="D156" s="15" t="inlineStr">
+        <is>
+          <t>-32.97347,-71.302447</t>
+        </is>
+      </c>
+      <c r="E156" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F156" s="12" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="G156" s="12" t="n">
+        <v>115202.5</v>
+      </c>
+      <c r="H156" s="12" t="n">
+        <v>75.40000000000001</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B157" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C157" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/24 19:07:59</t>
+        </is>
+      </c>
+      <c r="D157" s="15" t="inlineStr">
+        <is>
+          <t>-32.981261,-71.310045</t>
+        </is>
+      </c>
+      <c r="E157" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F157" s="12" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="G157" s="12" t="n">
+        <v>115203.6</v>
+      </c>
+      <c r="H157" s="12" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B158" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C158" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/24 19:08:30</t>
+        </is>
+      </c>
+      <c r="D158" s="15" t="inlineStr">
+        <is>
+          <t>-32.984069,-71.317887</t>
+        </is>
+      </c>
+      <c r="E158" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F158" s="12" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="G158" s="12" t="n">
+        <v>115204.4</v>
+      </c>
+      <c r="H158" s="12" t="n">
+        <v>77.2</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B159" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C159" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/24 19:08:46</t>
+        </is>
+      </c>
+      <c r="D159" s="15" t="inlineStr">
+        <is>
+          <t>-32.986648,-71.321198</t>
+        </is>
+      </c>
+      <c r="E159" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F159" s="12" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="G159" s="12" t="n">
+        <v>115204.9</v>
+      </c>
+      <c r="H159" s="12" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B160" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C160" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/24 19:09:11</t>
+        </is>
+      </c>
+      <c r="D160" s="15" t="inlineStr">
+        <is>
+          <t>-32.989576,-71.327162</t>
+        </is>
+      </c>
+      <c r="E160" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F160" s="12" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="G160" s="12" t="n">
+        <v>115205.5</v>
+      </c>
+      <c r="H160" s="12" t="n">
+        <v>74.40000000000001</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B161" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C161" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/24 19:09:16</t>
+        </is>
+      </c>
+      <c r="D161" s="15" t="inlineStr">
+        <is>
+          <t>-32.990725,-71.327755</t>
+        </is>
+      </c>
+      <c r="E161" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F161" s="12" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="G161" s="12" t="n">
+        <v>115205.7</v>
+      </c>
+      <c r="H161" s="12" t="n">
+        <v>75.09999999999999</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B162" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C162" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/24 19:10:18</t>
+        </is>
+      </c>
+      <c r="D162" s="15" t="inlineStr">
+        <is>
+          <t>-33.005592,-71.328105</t>
+        </is>
+      </c>
+      <c r="E162" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F162" s="12" t="n">
+        <v>99</v>
+      </c>
+      <c r="G162" s="12" t="n">
+        <v>115207.4</v>
+      </c>
+      <c r="H162" s="12" t="n">
+        <v>95.90000000000001</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B163" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="C47" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/15 18:37:45</t>
-        </is>
-      </c>
-      <c r="D47" s="15" t="inlineStr">
-        <is>
-          <t>-33.061073,-71.344216</t>
-        </is>
-      </c>
-      <c r="E47" s="12" t="inlineStr">
+      <c r="C163" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/24 19:14:19</t>
+        </is>
+      </c>
+      <c r="D163" s="15" t="inlineStr">
+        <is>
+          <t>-33.054475,-71.335471</t>
+        </is>
+      </c>
+      <c r="E163" s="12" t="inlineStr">
         <is>
           <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
-      <c r="F47" s="12" t="n">
-        <v>91.3</v>
-      </c>
-      <c r="G47" s="12" t="n">
-        <v>112815.7</v>
-      </c>
-      <c r="H47" s="12" t="n">
-        <v>193</v>
+      <c r="F163" s="12" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="G163" s="12" t="n">
+        <v>115213.9</v>
+      </c>
+      <c r="H163" s="12" t="n">
+        <v>183.1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B164" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C164" s="12" t="inlineStr">
+        <is>
+          <t>2026/07/24 19:15:19</t>
+        </is>
+      </c>
+      <c r="D164" s="15" t="inlineStr">
+        <is>
+          <t>-33.063683,-71.34876</t>
+        </is>
+      </c>
+      <c r="E164" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F164" s="12" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="G164" s="12" t="n">
+        <v>115215.5</v>
+      </c>
+      <c r="H164" s="12" t="n">
+        <v>204.1</v>
       </c>
     </row>
   </sheetData>
@@ -7359,12 +12647,129 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId159"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="default" paperSize="1" scale="100" pageOrder="downThenOver" blackAndWhite="0" draft="0" errors="displayed"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId43"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId160"/>
   </tableParts>
 </worksheet>
 </file>
--- a/INFORME EXCESOS DE VELOCIDAD.xlsx
+++ b/INFORME EXCESOS DE VELOCIDAD.xlsx
@@ -5807,7 +5807,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
         <v>1</v>
       </c>
@@ -5866,7 +5865,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
         <v>2</v>
       </c>
@@ -5925,7 +5923,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
         <v>3</v>
       </c>
@@ -5984,7 +5981,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
         <v>4</v>
       </c>
@@ -6043,7 +6039,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
         <v>5</v>
       </c>
@@ -6102,7 +6097,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
         <v>1</v>
       </c>
@@ -6161,7 +6155,6 @@
           <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
         <v>1</v>
       </c>
@@ -6220,7 +6213,6 @@
           <t>GV TDKV-88 L CORDERO</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
         <v>1</v>
       </c>
@@ -6279,7 +6271,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
         <v>1</v>
       </c>
@@ -6338,7 +6329,6 @@
           <t>GV SHLC-74 B MIRANDA</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
         <v>1</v>
       </c>
@@ -6397,7 +6387,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
         <v>2</v>
       </c>
@@ -6456,7 +6445,6 @@
           <t>GC MAXUS PCRF-25 TERRENO</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
         <v>1</v>
       </c>
@@ -6515,7 +6503,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
         <v>6</v>
       </c>
@@ -6574,7 +6561,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
         <v>7</v>
       </c>
@@ -6633,7 +6619,6 @@
           <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
         <v>1</v>
       </c>
@@ -6692,7 +6677,6 @@
           <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
         <v>2</v>
       </c>
@@ -6751,7 +6735,6 @@
           <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
         <v>3</v>
       </c>
@@ -6810,7 +6793,6 @@
           <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr"/>
       <c r="C104" t="n">
         <v>4</v>
       </c>
@@ -6869,7 +6851,6 @@
           <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
         <v>5</v>
       </c>
@@ -6928,7 +6909,6 @@
           <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr"/>
       <c r="C106" t="n">
         <v>6</v>
       </c>
@@ -6987,7 +6967,6 @@
           <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
         <v>7</v>
       </c>
@@ -7046,7 +7025,6 @@
           <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr"/>
       <c r="C108" t="n">
         <v>1</v>
       </c>

--- a/INFORME EXCESOS DE VELOCIDAD.xlsx
+++ b/INFORME EXCESOS DE VELOCIDAD.xlsx
@@ -222,8 +222,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SpeedingFleetsSummaryTable_1" displayName="SpeedingFleetsSummaryTable_1" ref="A5:I15" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A5:I15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SpeedingFleetsSummaryTable_1" displayName="SpeedingFleetsSummaryTable_1" ref="A5:I14" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A5:I14"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Alias"/>
     <tableColumn id="2" name="Excesos" dataDxfId="0"/>
@@ -240,8 +240,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SpeedingFleetsDetailTable_1" displayName="SpeedingFleetsDetailTable_1" ref="A5:O66" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A5:O66"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SpeedingFleetsDetailTable_1" displayName="SpeedingFleetsDetailTable_1" ref="A5:O27" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A5:O27"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Alias"/>
     <tableColumn id="2" name="Conductor"/>
@@ -264,8 +264,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SpeedingFleetsDataTable_1" displayName="SpeedingFleetsDataTable_1" ref="A5:H164" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A5:H164"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SpeedingFleetsDataTable_1" displayName="SpeedingFleetsDataTable_1" ref="A5:H59" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A5:H59"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Alias"/>
     <tableColumn id="2" name="Secuencial" dataDxfId="0"/>
@@ -569,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.710625" customWidth="1" style="7" min="1" max="1"/>
@@ -593,7 +593,7 @@
     <row r="3" ht="25" customHeight="1" s="8">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Desde : 2026/07/13 00:00:00 Hasta: 2026/08/02 23:59:59</t>
+          <t>Desde : 2026/07/13 00:00:00 Hasta: 2026/08/08 23:59:59</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>GLP SSZD-71  J VALLEJOS</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
@@ -660,13 +660,13 @@
         <v>0.0006944444444444445</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>102.1</v>
+        <v>100.1</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>102.1</v>
+        <v>100.1</v>
       </c>
       <c r="H6" s="12" t="n">
         <v>0</v>
@@ -678,26 +678,26 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>GV TDLD-98 J PACHECHO</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B7" s="12" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>0.0009722222222222222</v>
+        <v>0.001388888888888889</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>0.0004861111111111111</v>
+        <v>0.0006944444444444445</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>103.1</v>
+        <v>104.7</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>102</v>
+        <v>104.4</v>
       </c>
       <c r="H7" s="12" t="n">
         <v>0</v>
@@ -709,26 +709,26 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GV TDKV-88 L CORDERO</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>0.0006944444444444445</v>
+        <v>6.944444444444444e-05</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>0.0006944444444444445</v>
+        <v>6.944444444444444e-05</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>102</v>
+        <v>101.3</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>102</v>
+        <v>101.3</v>
       </c>
       <c r="H8" s="12" t="n">
         <v>0</v>
@@ -740,26 +740,26 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>GLP SHLC-75 L FONSECA</t>
+          <t>GV SHLC-74 B MIRANDA</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>0.0002430555555555555</v>
+        <v>0.0006944444444444445</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>0.0002430555555555555</v>
+        <v>0.0006944444444444445</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>100.2</v>
+        <v>100.5</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>100.2</v>
+        <v>100.5</v>
       </c>
       <c r="H9" s="12" t="n">
         <v>0</v>
@@ -771,26 +771,26 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>GV SHLC-74 B MIRANDA</t>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>0.0006944444444444445</v>
+        <v>0.0002546296296296296</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>0.0006944444444444445</v>
+        <v>0.0002546296296296296</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>102.9</v>
+        <v>100.1</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>102.9</v>
+        <v>100.1</v>
       </c>
       <c r="H10" s="12" t="n">
         <v>0</v>
@@ -802,26 +802,26 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>0.04327546296296296</v>
+        <v>0.0006944444444444445</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>0.001352361111111111</v>
+        <v>0.0006944444444444445</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>108.8</v>
+        <v>0.9</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>114.5</v>
+        <v>100.8</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>106.4</v>
+        <v>100.8</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>0</v>
@@ -833,26 +833,26 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>0.001319444444444444</v>
+        <v>0.002708333333333333</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>0.0003298611111111111</v>
+        <v>0.0003869097222222222</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>3.1</v>
+        <v>6.3</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>106.1</v>
+        <v>103.6</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>104.2</v>
+        <v>101.7</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>0</v>
@@ -864,26 +864,26 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 RXDL-61 OPERACIONES</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>0.005844907407407407</v>
+        <v>0.008148148148148147</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>0.0004496064814814814</v>
+        <v>0.001164016203703704</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>13.3</v>
+        <v>19</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>103.6</v>
+        <v>101.7</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>0</v>
@@ -895,62 +895,31 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>GLP SKDX-44 V VIAL</t>
+          <t>GC MAXUS PCRF-25 TERRENO</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>0.0006712962962962962</v>
+        <v>0.0006944444444444445</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>0.0003356481481481481</v>
+        <v>0.0006944444444444445</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>141.7</v>
+        <v>100.4</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>141.7</v>
+        <v>100.4</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="C15" s="13" t="n">
-        <v>0.002141203703703704</v>
-      </c>
-      <c r="D15" s="13" t="n">
-        <v>0.0005353009259259259</v>
-      </c>
-      <c r="E15" s="12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="F15" s="12" t="n">
-        <v>106.7</v>
-      </c>
-      <c r="G15" s="12" t="n">
-        <v>102.2</v>
-      </c>
-      <c r="H15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -975,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O108"/>
+  <dimension ref="A1:O123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.710625" customWidth="1" style="7" min="1" max="1"/>
@@ -1003,7 +972,7 @@
     <row r="3" ht="25" customHeight="1" s="8">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Desde : 2026/07/20 00:00:00 Hasta: 2026/07/26 23:59:58</t>
+          <t>Desde : 2026/07/27 00:00:00 Hasta: 2026/08/02 23:59:58</t>
         </is>
       </c>
     </row>
@@ -7074,6 +7043,891 @@
         <v>0</v>
       </c>
       <c r="O108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026/08/03 06:01:10</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>-33.063154,-71.469437</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2026/08/03 06:02:10</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-33.061893,-71.457259</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>s/n, Quilpué, Marga Marga, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="J109" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K109" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L109" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="M109" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>GLP SSZD-71  J VALLEJOS</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026/08/05 12:23:39</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>-33.080686,-71.561833</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>2026/08/05 12:24:39</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-33.070089,-71.574806</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J110" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K110" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L110" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="M110" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>GV TDLD-98 J PACHECHO</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026/08/05 14:23:46</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>-33.163504,-71.537483</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>2026/08/05 14:24:46</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>-33.156097,-71.552015</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J111" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L111" t="n">
+        <v>101</v>
+      </c>
+      <c r="M111" t="n">
+        <v>101</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>GV SHLC-74 B MIRANDA</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026/08/05 16:09:19</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>-32.786803,-71.431676</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>2026/08/05 16:10:19</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>-32.797308,-71.44036</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Ruta F-190, Quintero, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="J112" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K112" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L112" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="M112" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="N112" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>JAC  LYTS-17 G GALEA</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026/08/06 07:52:03</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>-32.680652,-71.425247</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>2026/08/06 07:53:03</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>-32.670624,-71.425352</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Ruta E-30-F, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J113" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K113" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L113" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="M113" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="N113" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>GV SHLC-74 B MIRANDA</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
+      <c r="C114" t="n">
+        <v>2</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026/08/06 09:46:47</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>-33.205819,-71.48396</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Ruta F-190, Quintero, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>2026/08/06 09:47:47</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>-33.216959,-71.473175</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J114" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K114" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L114" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="M114" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>GLP SSZD-71  J VALLEJOS</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="n">
+        <v>2</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026/08/06 12:13:09</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>-33.059575,-71.530514</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>2026/08/06 12:13:48</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>-33.066788,-71.533562</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J115" s="14" t="n">
+        <v>0.0004513888888888889</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L115" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="M115" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>GV TDLD-98 J PACHECHO</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
+      <c r="C116" t="n">
+        <v>2</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026/08/06 14:22:56</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>-33.231385,-71.464327</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>2026/08/06 14:23:56</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>-33.219271,-71.471768</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J116" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K116" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L116" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="M116" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>GV TM5 RXXG-15 E CABANILLA</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="n">
+        <v>1</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026/08/07 07:01:46</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>-33.275515,-71.429868</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>2026/08/07 07:02:46</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>-33.262462,-71.43552</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J117" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K117" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L117" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="M117" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>GV TM5 RXXG-15 E CABANILLA</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" t="n">
+        <v>2</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026/08/07 07:14:46</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>-33.143468,-71.561375</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>2026/08/07 07:15:46</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>-33.130053,-71.561948</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J118" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K118" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L118" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="M118" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>GLP SSZD-71  J VALLEJOS</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="n">
+        <v>3</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026/08/07 12:07:15</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>-33.094897,-71.600273</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>2026/08/07 12:08:15</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>-33.089443,-71.614598</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="J119" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L119" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="M119" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" t="n">
+        <v>2</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026/08/07 18:21:12</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>-32.924007,-71.28105</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>s/n, Quilpué, Marga Marga, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>2026/08/07 18:22:01</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>-32.933575,-71.288625</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J120" s="14" t="n">
+        <v>0.0005671296296296297</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L120" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="M120" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="n">
+        <v>3</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026/08/07 18:36:12</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>-33.06936,-71.36277</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>2026/08/07 18:38:12</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>-33.066117,-71.397749</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J121" s="14" t="n">
+        <v>0.001388888888888889</v>
+      </c>
+      <c r="K121" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L121" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="M121" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>GV TDLD-98 J PACHECHO</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="n">
+        <v>3</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2026/08/08 01:32:10</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>-33.234063,-71.462269</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>2026/08/08 01:33:10</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>-33.244036,-71.449798</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J122" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L122" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="M122" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>GV TDLD-98 J PACHECHO</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="n">
+        <v>4</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2026/08/08 14:19:07</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>-33.232909,-71.463096</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>2026/08/08 14:20:07</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-33.219807,-71.471478</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J123" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K123" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L123" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="M123" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7098,7 +7952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H164"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.710625" customWidth="1" style="7" min="1" max="1"/>
@@ -7124,7 +7978,7 @@
     <row r="3" ht="25" customHeight="1" s="8">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Desde : 2026/07/20 00:00:00 Hasta: 2026/07/26 23:59:58</t>
+          <t>Desde : 2026/07/27 00:00:00 Hasta: 2026/08/02 23:59:58</t>
         </is>
       </c>
     </row>
@@ -7173,7 +8027,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>GLP SSZD-71  J VALLEJOS</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
@@ -7181,33 +8035,33 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:27:12</t>
+          <t>2026/08/02 14:32:36</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>-33.07762,-71.564593</t>
+          <t>-33.16243,-71.539564</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F6" s="12" t="n">
-        <v>102.1</v>
+        <v>100.1</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>60300.6</v>
+        <v>77880.5</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>170.1</v>
+        <v>360.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>GLP SSZD-71  J VALLEJOS</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B7" s="12" t="n">
@@ -7215,33 +8069,33 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:28:12</t>
+          <t>2026/08/02 14:33:36</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>-33.08851,-71.556912</t>
+          <t>-33.15517,-71.553769</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F7" s="12" t="n">
-        <v>72</v>
+        <v>91.2</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>60302</v>
+        <v>77882.10000000001</v>
       </c>
       <c r="H7" s="12" t="n">
-        <v>236.4</v>
+        <v>356.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>GV TDLD-98 J PACHECHO</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
@@ -7249,33 +8103,33 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>2026/07/21 11:32:34</t>
+          <t>2026/07/30 18:54:20</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>-33.284147,-71.41146</t>
+          <t>-32.897768,-71.449538</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-852, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta F-190, Quillota, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F8" s="12" t="n">
-        <v>100.9</v>
+        <v>104.7</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>75326.10000000001</v>
+        <v>187456</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>267.5</v>
+        <v>125.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>GV TDLD-98 J PACHECHO</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
@@ -7283,33 +8137,33 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>2026/07/21 11:32:59</t>
+          <t>2026/07/30 18:55:20</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>-33.279333,-71.41388</t>
+          <t>-32.906604,-71.440511</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-852, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta F-190, Quillota, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F9" s="12" t="n">
-        <v>81</v>
+        <v>76.7</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>75326.7</v>
+        <v>187457.3</v>
       </c>
       <c r="H9" s="12" t="n">
-        <v>306.6</v>
+        <v>124.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>GV TDLD-98 J PACHECHO</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
@@ -7317,33 +8171,33 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 07:56:42</t>
+          <t>2026/07/31 13:08:39</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>-33.225503,-71.468722</t>
+          <t>-33.219324,-71.471926</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F10" s="12" t="n">
-        <v>103.1</v>
+        <v>104.1</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>75546.8</v>
+        <v>187526.8</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>328.4</v>
+        <v>330.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>GV TDLD-98 J PACHECHO</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B11" s="12" t="n">
@@ -7351,12 +8205,12 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 07:57:41</t>
+          <t>2026/07/31 13:09:39</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>-33.237146,-71.459055</t>
+          <t>-33.231962,-71.464083</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -7365,19 +8219,19 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>94.09999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>75548.39999999999</v>
+        <v>187528.4</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>324.8</v>
+        <v>337.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GV TDKV-88 L CORDERO</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
@@ -7385,33 +8239,33 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>2026/07/21 18:30:06</t>
+          <t>2026/07/30 17:56:03</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>-33.17968,-71.506531</t>
+          <t>-33.10693,-71.550214</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>102</v>
+        <v>101.3</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>186090.6</v>
+        <v>76539</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>345.2</v>
+        <v>351.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GV TDKV-88 L CORDERO</t>
         </is>
       </c>
       <c r="B13" s="12" t="n">
@@ -7419,33 +8273,33 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>2026/07/21 18:31:06</t>
+          <t>2026/07/30 17:56:09</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>-33.172153,-71.520549</t>
+          <t>-33.107497,-71.5518</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>91</v>
+        <v>93.2</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>186092.2</v>
+        <v>76539.2</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>341.7</v>
+        <v>347.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>GLP SHLC-75 L FONSECA</t>
+          <t>GV SHLC-74 B MIRANDA</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
@@ -7453,33 +8307,33 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>2026/07/20 14:20:36</t>
+          <t>2026/07/31 07:36:59</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>-33.106749,-71.563552</t>
+          <t>-33.158797,-71.546799</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>100.2</v>
+        <v>100.5</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>95113.3</v>
+        <v>122625.2</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>356</v>
+        <v>369.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>GLP SHLC-75 L FONSECA</t>
+          <t>GV SHLC-74 B MIRANDA</t>
         </is>
       </c>
       <c r="B15" s="12" t="n">
@@ -7487,33 +8341,33 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>2026/07/20 14:20:57</t>
+          <t>2026/07/31 07:37:59</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>-33.106017,-71.558066</t>
+          <t>-33.149438,-71.558461</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>67.7</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>95113.8</v>
+        <v>122626.7</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>358.4</v>
+        <v>344.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>GV SHLC-74 B MIRANDA</t>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
       <c r="B16" s="12" t="n">
@@ -7521,33 +8375,33 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 17:03:05</t>
+          <t>2026/07/28 15:58:20</t>
         </is>
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>-33.218405,-71.47239</t>
+          <t>-32.733776,-71.436634</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta F-20, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>102.9</v>
+        <v>100.1</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>120412.2</v>
+        <v>122447.9</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>332.3</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>GV SHLC-74 B MIRANDA</t>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
       <c r="B17" s="12" t="n">
@@ -7555,33 +8409,33 @@
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 17:04:05</t>
+          <t>2026/07/28 15:58:42</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>-33.231782,-71.464215</t>
+          <t>-32.736051,-71.431128</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta F-20, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>97.2</v>
+        <v>93</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>120413.9</v>
+        <v>122448.5</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>338.4</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B18" s="12" t="n">
@@ -7589,33 +8443,33 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 08:58:27</t>
+          <t>2026/07/28 02:11:25</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>-33.205225,-71.484598</t>
+          <t>-32.944023,-71.513376</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>102</v>
+        <v>100.8</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>65138.2</v>
+        <v>261970.6</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>401.1</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B19" s="12" t="n">
@@ -7623,33 +8477,33 @@
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 08:59:27</t>
+          <t>2026/07/28 02:12:25</t>
         </is>
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>-33.217675,-71.472802</t>
+          <t>-32.935778,-71.513703</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>106.6</v>
+        <v>0</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>65140</v>
+        <v>261971.5</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>335.5</v>
+        <v>84.90000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
       <c r="B20" s="12" t="n">
@@ -7657,33 +8511,33 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:00:26</t>
+          <t>2026/08/01 06:30:23</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>-33.23198,-71.464046</t>
+          <t>-33.102452,-71.54806</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>106.3</v>
+        <v>102.1</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>65141.8</v>
+        <v>147132</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>341.6</v>
+        <v>345.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
       <c r="B21" s="12" t="n">
@@ -7691,475 +8545,475 @@
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:01:26</t>
+          <t>2026/08/01 06:30:48</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>-33.243273,-71.450439</t>
+          <t>-33.096687,-71.546062</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>s/n, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>s/n, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>110</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>65143.6</v>
+        <v>147132.7</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>276.1</v>
+        <v>310.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:02:26</t>
+          <t>2026/08/01 06:46:24</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>-33.256881,-71.439776</t>
+          <t>-32.967111,-71.503823</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta E-30-F, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>106.4</v>
+        <v>102.6</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>65145.4</v>
+        <v>147153.7</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>273.8</v>
+        <v>159.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:03:27</t>
+          <t>2026/08/01 06:47:14</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>-33.271995,-71.431471</t>
+          <t>-32.957174,-71.510191</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>106.9</v>
+        <v>88.8</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>65147.2</v>
+        <v>147155</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>284</v>
+        <v>171.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:04:26</t>
+          <t>2026/08/01 06:50:24</t>
         </is>
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>-33.285196,-71.425764</t>
+          <t>-32.989287,-71.500906</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Camino Internacional, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>88.40000000000001</v>
+        <v>103.1</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>65148.8</v>
+        <v>147159.5</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>336.1</v>
+        <v>136.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:05:28</t>
+          <t>2026/08/01 06:51:02</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>-33.299233,-71.416588</t>
+          <t>-32.998137,-71.50228</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Camino Internacional, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>105.6</v>
+        <v>80</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>65150.6</v>
+        <v>147160.4</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>256.9</v>
+        <v>153.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:06:28</t>
+          <t>2026/08/01 09:40:00</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>-33.312372,-71.404842</t>
+          <t>-33.013677,-71.500475</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Avenida Carlos Ibáñez del Campo, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>108.8</v>
+        <v>100.4</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>65152.5</v>
+        <v>147253.8</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>260.1</v>
+        <v>249.7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:07:28</t>
+          <t>2026/08/01 09:40:16</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>-33.324524,-71.3921</t>
+          <t>-33.017375,-71.500179</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Avenida Rubén Hurtado, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>108.7</v>
+        <v>93.3</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>65154.3</v>
+        <v>147254.2</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>271.4</v>
+        <v>240.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:08:29</t>
+          <t>2026/08/01 11:31:13</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>-33.335276,-71.378202</t>
+          <t>-33.059472,-71.645814</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>108.3</v>
+        <v>100.6</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>65156.1</v>
+        <v>147292.5</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>265.8</v>
+        <v>322.9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
       <c r="B29" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:09:29</t>
+          <t>2026/08/01 11:31:21</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>-33.343029,-71.360996</t>
+          <t>-33.060679,-71.644303</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>108.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>65157.9</v>
+        <v>147292.8</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>273</v>
+        <v>335.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
       <c r="B30" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:10:29</t>
+          <t>2026/08/01 11:31:50</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>-33.350755,-71.343674</t>
+          <t>-33.06623,-71.64223</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>109.8</v>
+        <v>101.2</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>65159.8</v>
+        <v>147293.5</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>281.7</v>
+        <v>386.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
       <c r="B31" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:11:29</t>
+          <t>2026/08/01 11:31:55</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>-33.358468,-71.326486</t>
+          <t>-33.067011,-71.641101</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>108.4</v>
+        <v>100.6</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>65161.6</v>
+        <v>147293.7</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>296</v>
+        <v>395.6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:12:29</t>
+          <t>2026/08/01 11:32:00</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>-33.366253,-71.309257</t>
+          <t>-33.066878,-71.63965</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>108.9</v>
+        <v>101.8</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>65163.4</v>
+        <v>147293.8</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>307.7</v>
+        <v>404.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:13:29</t>
+          <t>2026/08/01 11:32:04</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>-33.374795,-71.292789</t>
+          <t>-33.066455,-71.638545</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>103.8</v>
+        <v>103.6</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>65165.2</v>
+        <v>147294</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>329.9</v>
+        <v>410.7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:14:29</t>
+          <t>2026/08/01 11:32:17</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>-33.382592,-71.278129</t>
+          <t>-33.066758,-71.634562</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>95.59999999999999</v>
+        <v>101</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>65166.9</v>
+        <v>147294.3</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>400</v>
+        <v>432.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
       <c r="B35" s="12" t="n">
@@ -8167,4413 +9021,843 @@
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:18:29</t>
+          <t>2026/08/01 11:32:53</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>-33.403175,-71.216164</t>
+          <t>-33.072407,-71.627597</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>110.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>65173.1</v>
+        <v>147295.2</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>262.3</v>
+        <v>431.9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:19:29</t>
+          <t>2026/08/02 12:14:56</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>-33.40527,-71.196932</t>
+          <t>-33.09045,-71.541794</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>105.4</v>
+        <v>102.2</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>65174.9</v>
+        <v>147585.4</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>240.2</v>
+        <v>321.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
       <c r="B37" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:20:29</t>
+          <t>2026/08/02 12:15:15</t>
         </is>
       </c>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>-33.408414,-71.17798</t>
+          <t>-33.094806,-71.543443</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+          <t>Vía Las Palmas, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>100.4</v>
+        <v>100.3</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>65176.7</v>
+        <v>147586</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>209.4</v>
+        <v>318.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:21:29</t>
+          <t>2026/08/02 12:15:30</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>-33.412095,-71.159082</t>
+          <t>-33.096963,-71.546855</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>102.5</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>65178.5</v>
+        <v>147586.4</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>196</v>
+        <v>321.6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B39" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:22:29</t>
+          <t>2026/07/27 06:25:04</t>
         </is>
       </c>
       <c r="D39" s="15" t="inlineStr">
         <is>
-          <t>-33.409931,-71.140659</t>
+          <t>-33.067327,-71.387599</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>105.5</v>
+        <v>104</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>65180.3</v>
+        <v>115264</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>191.6</v>
+        <v>171</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B40" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:23:29</t>
+          <t>2026/07/27 06:26:04</t>
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>-33.407447,-71.122999</t>
+          <t>-33.068846,-71.370499</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>90.09999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>65182.1</v>
+        <v>115265.6</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>189.8</v>
+        <v>176.9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B41" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:24:10</t>
+          <t>2026/07/27 06:32:04</t>
         </is>
       </c>
       <c r="D41" s="15" t="inlineStr">
         <is>
-          <t>-33.40112,-71.115029</t>
+          <t>-33.016759,-71.31988</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>109.6</v>
+        <v>100.2</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>65183.1</v>
+        <v>115274.5</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>191.5</v>
+        <v>108.7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B42" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:24:29</t>
+          <t>2026/07/27 06:33:04</t>
         </is>
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>-33.401131,-71.108913</t>
+          <t>-33.004069,-71.328408</t>
         </is>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>109.6</v>
+        <v>88.7</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>65183.7</v>
+        <v>115276.1</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>185.9</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B43" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:25:29</t>
+          <t>2026/07/27 06:43:04</t>
         </is>
       </c>
       <c r="D43" s="15" t="inlineStr">
         <is>
-          <t>-33.404203,-71.089858</t>
+          <t>-32.911064,-71.269813</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>108.5</v>
+        <v>100.4</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>65185.5</v>
+        <v>115289.1</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>181.9</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B44" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:26:29</t>
+          <t>2026/07/27 06:44:04</t>
         </is>
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>-33.4079,-71.070976</t>
+          <t>-32.903617,-71.254498</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>111.5</v>
+        <v>96.2</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>65187.3</v>
+        <v>115290.8</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>187.6</v>
+        <v>105.4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B45" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:27:29</t>
+          <t>2026/07/27 07:46:04</t>
         </is>
       </c>
       <c r="D45" s="15" t="inlineStr">
         <is>
-          <t>-33.414364,-71.053484</t>
+          <t>-32.572429,-71.289271</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>109.1</v>
+        <v>101.5</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>65189.1</v>
+        <v>115358.6</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>179.8</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B46" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:28:29</t>
+          <t>2026/07/27 07:47:04</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>-33.425893,-71.03943</t>
+          <t>-32.569254,-71.276721</t>
         </is>
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>110.9</v>
+        <v>20.4</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>65190.9</v>
+        <v>115359.8</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>187.5</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B47" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:29:29</t>
+          <t>2026/07/27 07:50:04</t>
         </is>
       </c>
       <c r="D47" s="15" t="inlineStr">
         <is>
-          <t>-33.437414,-71.025349</t>
+          <t>-32.549855,-71.268268</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>108.6</v>
+        <v>103.1</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>65192.8</v>
+        <v>115363.5</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>195.5</v>
+        <v>107.9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B48" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:30:15</t>
+          <t>2026/07/27 07:51:04</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>-33.442193,-71.012405</t>
+          <t>-32.534791,-71.264781</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>65194.1</v>
+        <v>115365.2</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>237.1</v>
+        <v>114.7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B49" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:30:29</t>
+          <t>2026/07/27 07:52:04</t>
         </is>
       </c>
       <c r="D49" s="15" t="inlineStr">
         <is>
-          <t>-33.440741,-71.008548</t>
+          <t>-32.519725,-71.261213</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>102.8</v>
+        <v>100.7</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>65194.5</v>
+        <v>115366.9</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>247.9</v>
+        <v>101.1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B50" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:30:44</t>
+          <t>2026/07/27 07:53:04</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>-33.44006,-71.00426</t>
+          <t>-32.506255,-71.259684</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>95.59999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>65194.9</v>
+        <v>115368.4</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>267.4</v>
+        <v>77.7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B51" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:32:29</t>
+          <t>2026/07/31 19:07:11</t>
         </is>
       </c>
       <c r="D51" s="15" t="inlineStr">
         <is>
-          <t>-33.446799,-70.981751</t>
+          <t>-32.870929,-71.229809</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>100.3</v>
+        <v>101.9</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>65197.5</v>
+        <v>116983.2</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>391.1</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B52" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:32:42</t>
+          <t>2026/07/31 19:08:11</t>
         </is>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>-33.449648,-70.980172</t>
+          <t>-32.885976,-71.232073</t>
         </is>
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>98.3</v>
+        <v>102.4</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>65197.8</v>
+        <v>116984.9</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>409.6</v>
+        <v>117.9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B53" s="12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:33:29</t>
+          <t>2026/07/31 19:09:11</t>
         </is>
       </c>
       <c r="D53" s="15" t="inlineStr">
         <is>
-          <t>-33.456411,-70.96902</t>
+          <t>-32.898972,-71.239656</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>100.6</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>65199.1</v>
+        <v>116986.6</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>468.9</v>
+        <v>109</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B54" s="12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:34:31</t>
+          <t>2026/07/31 19:10:11</t>
         </is>
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>-33.456411,-70.96902</t>
+          <t>-32.904194,-71.25627</t>
         </is>
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>100.6</v>
+        <v>100.9</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>65199.7</v>
+        <v>116988.3</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>468.9</v>
+        <v>100.9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B55" s="12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:35:31</t>
+          <t>2026/07/31 19:11:11</t>
         </is>
       </c>
       <c r="D55" s="15" t="inlineStr">
         <is>
-          <t>-33.456411,-70.96902</t>
+          <t>-32.912396,-71.271115</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>100.6</v>
+        <v>102.5</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>65199.7</v>
+        <v>116990</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>468.9</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B56" s="12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:35:45</t>
+          <t>2026/07/31 19:12:11</t>
         </is>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>-33.458044,-70.931695</t>
+          <t>-32.924905,-71.281892</t>
         </is>
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:100, VMaxPes:90</t>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>104.3</v>
+        <v>100.7</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>65202.7</v>
+        <v>116991.7</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>530.1</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B57" s="12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:36:29</t>
+          <t>2026/07/31 19:12:55</t>
         </is>
       </c>
       <c r="D57" s="15" t="inlineStr">
         <is>
-          <t>-33.457597,-70.917386</t>
+          <t>-32.933783,-71.288593</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:100, VMaxPes:90</t>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>108.2</v>
+        <v>68.8</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>65204</v>
+        <v>116992.9</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>508.4</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GC MAXUS PCRF-25 TERRENO</t>
         </is>
       </c>
       <c r="B58" s="12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:37:29</t>
+          <t>2026/07/31 14:57:40</t>
         </is>
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>-33.456615,-70.898224</t>
+          <t>-32.577562,-71.309168</t>
         </is>
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>107.4</v>
+        <v>100.4</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>65205.8</v>
+        <v>90949.10000000001</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>483.4</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GC MAXUS PCRF-25 TERRENO</t>
         </is>
       </c>
       <c r="B59" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>2026/07/22 09:38:29</t>
+          <t>2026/07/31 14:58:40</t>
         </is>
       </c>
       <c r="D59" s="15" t="inlineStr">
         <is>
-          <t>-33.451481,-70.879731</t>
+          <t>-32.583363,-71.323384</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>109.7</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>65207.7</v>
+        <v>90950.60000000001</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>465.6</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B60" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="C60" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 09:39:29</t>
-        </is>
-      </c>
-      <c r="D60" s="15" t="inlineStr">
-        <is>
-          <t>-33.446593,-70.861109</t>
-        </is>
-      </c>
-      <c r="E60" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F60" s="12" t="n">
-        <v>108</v>
-      </c>
-      <c r="G60" s="12" t="n">
-        <v>65209.5</v>
-      </c>
-      <c r="H60" s="12" t="n">
-        <v>461.5</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B61" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="C61" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 09:40:29</t>
-        </is>
-      </c>
-      <c r="D61" s="15" t="inlineStr">
-        <is>
-          <t>-33.442227,-70.844696</t>
-        </is>
-      </c>
-      <c r="E61" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F61" s="12" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="G61" s="12" t="n">
-        <v>65211.1</v>
-      </c>
-      <c r="H61" s="12" t="n">
-        <v>468.5</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B62" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="C62" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 09:44:29</t>
-        </is>
-      </c>
-      <c r="D62" s="15" t="inlineStr">
-        <is>
-          <t>-33.424598,-70.798787</t>
-        </is>
-      </c>
-      <c r="E62" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Costanera Norte, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F62" s="12" t="n">
-        <v>109.4</v>
-      </c>
-      <c r="G62" s="12" t="n">
-        <v>65216.9</v>
-      </c>
-      <c r="H62" s="12" t="n">
-        <v>468.6</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B63" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="C63" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 09:45:27</t>
-        </is>
-      </c>
-      <c r="D63" s="15" t="inlineStr">
-        <is>
-          <t>-33.416012,-70.786191</t>
-        </is>
-      </c>
-      <c r="E63" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Costanera Norte, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F63" s="12" t="n">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="G63" s="12" t="n">
-        <v>65218.4</v>
-      </c>
-      <c r="H63" s="12" t="n">
-        <v>468.4</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B64" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="C64" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 09:45:29</t>
-        </is>
-      </c>
-      <c r="D64" s="15" t="inlineStr">
-        <is>
-          <t>-33.415985,-70.785594</t>
-        </is>
-      </c>
-      <c r="E64" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Costanera Norte, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F64" s="12" t="n">
-        <v>101</v>
-      </c>
-      <c r="G64" s="12" t="n">
-        <v>65218.5</v>
-      </c>
-      <c r="H64" s="12" t="n">
-        <v>466.8</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B65" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="C65" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 09:46:29</t>
-        </is>
-      </c>
-      <c r="D65" s="15" t="inlineStr">
-        <is>
-          <t>-33.412913,-70.768448</t>
-        </is>
-      </c>
-      <c r="E65" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Costanera Norte, Renca, Santiago, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F65" s="12" t="n">
-        <v>106.1</v>
-      </c>
-      <c r="G65" s="12" t="n">
-        <v>65220.2</v>
-      </c>
-      <c r="H65" s="12" t="n">
-        <v>478.2</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B66" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="C66" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 09:47:29</t>
-        </is>
-      </c>
-      <c r="D66" s="15" t="inlineStr">
-        <is>
-          <t>-33.411607,-70.750867</t>
-        </is>
-      </c>
-      <c r="E66" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Costanera Norte, Renca, Santiago, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F66" s="12" t="n">
-        <v>107.5</v>
-      </c>
-      <c r="G66" s="12" t="n">
-        <v>65221.8</v>
-      </c>
-      <c r="H66" s="12" t="n">
-        <v>483.7</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B67" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="C67" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 09:48:29</t>
-        </is>
-      </c>
-      <c r="D67" s="15" t="inlineStr">
-        <is>
-          <t>-33.411833,-70.731852</t>
-        </is>
-      </c>
-      <c r="E67" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Costanera Norte, Renca, Santiago, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F67" s="12" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="G67" s="12" t="n">
-        <v>65223.6</v>
-      </c>
-      <c r="H67" s="12" t="n">
-        <v>491.6</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B68" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="C68" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:02:44</t>
-        </is>
-      </c>
-      <c r="D68" s="15" t="inlineStr">
-        <is>
-          <t>-33.419429,-70.793301</t>
-        </is>
-      </c>
-      <c r="E68" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Costanera Norte, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F68" s="12" t="n">
-        <v>107.7</v>
-      </c>
-      <c r="G68" s="12" t="n">
-        <v>65238</v>
-      </c>
-      <c r="H68" s="12" t="n">
-        <v>477.9</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B69" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="C69" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:03:44</t>
-        </is>
-      </c>
-      <c r="D69" s="15" t="inlineStr">
-        <is>
-          <t>-33.429227,-70.807823</t>
-        </is>
-      </c>
-      <c r="E69" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Costanera Norte, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F69" s="12" t="n">
-        <v>102.3</v>
-      </c>
-      <c r="G69" s="12" t="n">
-        <v>65239.8</v>
-      </c>
-      <c r="H69" s="12" t="n">
-        <v>465.1</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B70" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="C70" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:04:35</t>
-        </is>
-      </c>
-      <c r="D70" s="15" t="inlineStr">
-        <is>
-          <t>-33.438924,-70.81374</t>
-        </is>
-      </c>
-      <c r="E70" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Costanera Norte, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F70" s="12" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="G70" s="12" t="n">
-        <v>65241</v>
-      </c>
-      <c r="H70" s="12" t="n">
-        <v>466.9</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B71" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="C71" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:06:44</t>
-        </is>
-      </c>
-      <c r="D71" s="15" t="inlineStr">
-        <is>
-          <t>-33.442559,-70.846133</t>
-        </is>
-      </c>
-      <c r="E71" s="12" t="inlineStr">
-        <is>
-          <t>Camino A Valparaíso, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F71" s="12" t="n">
-        <v>103.7</v>
-      </c>
-      <c r="G71" s="12" t="n">
-        <v>65244.1</v>
-      </c>
-      <c r="H71" s="12" t="n">
-        <v>467.2</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B72" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="C72" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:07:44</t>
-        </is>
-      </c>
-      <c r="D72" s="15" t="inlineStr">
-        <is>
-          <t>-33.447081,-70.86318</t>
-        </is>
-      </c>
-      <c r="E72" s="12" t="inlineStr">
-        <is>
-          <t>Camino A Valparaíso, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F72" s="12" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="G72" s="12" t="n">
-        <v>65245.8</v>
-      </c>
-      <c r="H72" s="12" t="n">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B73" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="C73" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:08:44</t>
-        </is>
-      </c>
-      <c r="D73" s="15" t="inlineStr">
-        <is>
-          <t>-33.45144,-70.879801</t>
-        </is>
-      </c>
-      <c r="E73" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F73" s="12" t="n">
-        <v>108.5</v>
-      </c>
-      <c r="G73" s="12" t="n">
-        <v>65247.4</v>
-      </c>
-      <c r="H73" s="12" t="n">
-        <v>466.1</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B74" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="C74" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:09:44</t>
-        </is>
-      </c>
-      <c r="D74" s="15" t="inlineStr">
-        <is>
-          <t>-33.45618,-70.896875</t>
-        </is>
-      </c>
-      <c r="E74" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Pudahuel, Santiago, Región Metropolitana de Santiago. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F74" s="12" t="n">
-        <v>98</v>
-      </c>
-      <c r="G74" s="12" t="n">
-        <v>65249.1</v>
-      </c>
-      <c r="H74" s="12" t="n">
-        <v>481.8</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B75" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="C75" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:13:44</t>
-        </is>
-      </c>
-      <c r="D75" s="15" t="inlineStr">
-        <is>
-          <t>-33.45651,-70.968755</t>
-        </is>
-      </c>
-      <c r="E75" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F75" s="12" t="n">
-        <v>108</v>
-      </c>
-      <c r="G75" s="12" t="n">
-        <v>65255.9</v>
-      </c>
-      <c r="H75" s="12" t="n">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B76" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="C76" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:14:42</t>
-        </is>
-      </c>
-      <c r="D76" s="15" t="inlineStr">
-        <is>
-          <t>-33.446769,-70.981665</t>
-        </is>
-      </c>
-      <c r="E76" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F76" s="12" t="n">
-        <v>101</v>
-      </c>
-      <c r="G76" s="12" t="n">
-        <v>65257.5</v>
-      </c>
-      <c r="H76" s="12" t="n">
-        <v>390.1</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B77" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="C77" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:14:44</t>
-        </is>
-      </c>
-      <c r="D77" s="15" t="inlineStr">
-        <is>
-          <t>-33.446256,-70.981656</t>
-        </is>
-      </c>
-      <c r="E77" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F77" s="12" t="n">
-        <v>102.2</v>
-      </c>
-      <c r="G77" s="12" t="n">
-        <v>65257.6</v>
-      </c>
-      <c r="H77" s="12" t="n">
-        <v>388.7</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B78" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="C78" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:14:58</t>
-        </is>
-      </c>
-      <c r="D78" s="15" t="inlineStr">
-        <is>
-          <t>-33.443085,-70.983097</t>
-        </is>
-      </c>
-      <c r="E78" s="12" t="inlineStr">
-        <is>
-          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F78" s="12" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="G78" s="12" t="n">
-        <v>65258</v>
-      </c>
-      <c r="H78" s="12" t="n">
-        <v>372.9</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B79" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="C79" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:16:44</t>
-        </is>
-      </c>
-      <c r="D79" s="15" t="inlineStr">
-        <is>
-          <t>-33.442058,-71.011834</t>
-        </is>
-      </c>
-      <c r="E79" s="12" t="inlineStr">
-        <is>
-          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F79" s="12" t="n">
-        <v>102.9</v>
-      </c>
-      <c r="G79" s="12" t="n">
-        <v>65260.9</v>
-      </c>
-      <c r="H79" s="12" t="n">
-        <v>238.1</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B80" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="C80" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:17:25</t>
-        </is>
-      </c>
-      <c r="D80" s="15" t="inlineStr">
-        <is>
-          <t>-33.438093,-71.023991</t>
-        </is>
-      </c>
-      <c r="E80" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F80" s="12" t="n">
-        <v>104.6</v>
-      </c>
-      <c r="G80" s="12" t="n">
-        <v>65262.1</v>
-      </c>
-      <c r="H80" s="12" t="n">
-        <v>194.2</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B81" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="C81" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:17:44</t>
-        </is>
-      </c>
-      <c r="D81" s="15" t="inlineStr">
-        <is>
-          <t>-33.434804,-71.028527</t>
-        </is>
-      </c>
-      <c r="E81" s="12" t="inlineStr">
-        <is>
-          <t>s/n, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:50, VMaxPes:50</t>
-        </is>
-      </c>
-      <c r="F81" s="12" t="n">
-        <v>105.2</v>
-      </c>
-      <c r="G81" s="12" t="n">
-        <v>65262.7</v>
-      </c>
-      <c r="H81" s="12" t="n">
-        <v>193.8</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B82" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="C82" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:18:44</t>
-        </is>
-      </c>
-      <c r="D82" s="15" t="inlineStr">
-        <is>
-          <t>-33.42387,-71.041797</t>
-        </is>
-      </c>
-      <c r="E82" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F82" s="12" t="n">
-        <v>107.5</v>
-      </c>
-      <c r="G82" s="12" t="n">
-        <v>65264.4</v>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>183.4</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B83" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="C83" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:19:44</t>
-        </is>
-      </c>
-      <c r="D83" s="15" t="inlineStr">
-        <is>
-          <t>-33.412894,-71.055501</t>
-        </is>
-      </c>
-      <c r="E83" s="12" t="inlineStr">
-        <is>
-          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F83" s="12" t="n">
-        <v>108.4</v>
-      </c>
-      <c r="G83" s="12" t="n">
-        <v>65266.2</v>
-      </c>
-      <c r="H83" s="12" t="n">
-        <v>183.7</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B84" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="C84" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:20:44</t>
-        </is>
-      </c>
-      <c r="D84" s="15" t="inlineStr">
-        <is>
-          <t>-33.407271,-71.073586</t>
-        </is>
-      </c>
-      <c r="E84" s="12" t="inlineStr">
-        <is>
-          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F84" s="12" t="n">
-        <v>109.5</v>
-      </c>
-      <c r="G84" s="12" t="n">
-        <v>65268</v>
-      </c>
-      <c r="H84" s="12" t="n">
-        <v>188.2</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B85" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="C85" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:21:44</t>
-        </is>
-      </c>
-      <c r="D85" s="15" t="inlineStr">
-        <is>
-          <t>-33.403508,-71.092758</t>
-        </is>
-      </c>
-      <c r="E85" s="12" t="inlineStr">
-        <is>
-          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F85" s="12" t="n">
-        <v>105.6</v>
-      </c>
-      <c r="G85" s="12" t="n">
-        <v>65269.8</v>
-      </c>
-      <c r="H85" s="12" t="n">
-        <v>182.8</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B86" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="C86" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:22:44</t>
-        </is>
-      </c>
-      <c r="D86" s="15" t="inlineStr">
-        <is>
-          <t>-33.401012,-71.111695</t>
-        </is>
-      </c>
-      <c r="E86" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F86" s="12" t="n">
-        <v>111.2</v>
-      </c>
-      <c r="G86" s="12" t="n">
-        <v>65271.6</v>
-      </c>
-      <c r="H86" s="12" t="n">
-        <v>187.8</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B87" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="C87" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:23:09</t>
-        </is>
-      </c>
-      <c r="D87" s="15" t="inlineStr">
-        <is>
-          <t>-33.402891,-71.119196</t>
-        </is>
-      </c>
-      <c r="E87" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F87" s="12" t="n">
-        <v>111.6</v>
-      </c>
-      <c r="G87" s="12" t="n">
-        <v>65272.3</v>
-      </c>
-      <c r="H87" s="12" t="n">
-        <v>199.6</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B88" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="C88" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:23:44</t>
-        </is>
-      </c>
-      <c r="D88" s="15" t="inlineStr">
-        <is>
-          <t>-33.409251,-71.127083</t>
-        </is>
-      </c>
-      <c r="E88" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F88" s="12" t="n">
-        <v>107.1</v>
-      </c>
-      <c r="G88" s="12" t="n">
-        <v>65273.4</v>
-      </c>
-      <c r="H88" s="12" t="n">
-        <v>191.6</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B89" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="C89" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:24:44</t>
-        </is>
-      </c>
-      <c r="D89" s="15" t="inlineStr">
-        <is>
-          <t>-33.411612,-71.145894</t>
-        </is>
-      </c>
-      <c r="E89" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F89" s="12" t="n">
-        <v>104.6</v>
-      </c>
-      <c r="G89" s="12" t="n">
-        <v>65275.2</v>
-      </c>
-      <c r="H89" s="12" t="n">
-        <v>194.8</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B90" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="C90" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:25:44</t>
-        </is>
-      </c>
-      <c r="D90" s="15" t="inlineStr">
-        <is>
-          <t>-33.410945,-71.164731</t>
-        </is>
-      </c>
-      <c r="E90" s="12" t="inlineStr">
-        <is>
-          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F90" s="12" t="n">
-        <v>108.7</v>
-      </c>
-      <c r="G90" s="12" t="n">
-        <v>65277.1</v>
-      </c>
-      <c r="H90" s="12" t="n">
-        <v>201.5</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B91" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="C91" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:26:44</t>
-        </is>
-      </c>
-      <c r="D91" s="15" t="inlineStr">
-        <is>
-          <t>-33.407166,-71.183775</t>
-        </is>
-      </c>
-      <c r="E91" s="12" t="inlineStr">
-        <is>
-          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F91" s="12" t="n">
-        <v>108.4</v>
-      </c>
-      <c r="G91" s="12" t="n">
-        <v>65278.9</v>
-      </c>
-      <c r="H91" s="12" t="n">
-        <v>218.2</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B92" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="C92" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:27:44</t>
-        </is>
-      </c>
-      <c r="D92" s="15" t="inlineStr">
-        <is>
-          <t>-33.405465,-71.202733</t>
-        </is>
-      </c>
-      <c r="E92" s="12" t="inlineStr">
-        <is>
-          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F92" s="12" t="n">
-        <v>104.3</v>
-      </c>
-      <c r="G92" s="12" t="n">
-        <v>65280.7</v>
-      </c>
-      <c r="H92" s="12" t="n">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B93" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="C93" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:28:44</t>
-        </is>
-      </c>
-      <c r="D93" s="15" t="inlineStr">
-        <is>
-          <t>-33.401162,-71.221267</t>
-        </is>
-      </c>
-      <c r="E93" s="12" t="inlineStr">
-        <is>
-          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F93" s="12" t="n">
-        <v>106.6</v>
-      </c>
-      <c r="G93" s="12" t="n">
-        <v>65282.5</v>
-      </c>
-      <c r="H93" s="12" t="n">
-        <v>271.2</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B94" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="C94" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:29:44</t>
-        </is>
-      </c>
-      <c r="D94" s="15" t="inlineStr">
-        <is>
-          <t>-33.395823,-71.237249</t>
-        </is>
-      </c>
-      <c r="E94" s="12" t="inlineStr">
-        <is>
-          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F94" s="12" t="n">
-        <v>102.4</v>
-      </c>
-      <c r="G94" s="12" t="n">
-        <v>65284.1</v>
-      </c>
-      <c r="H94" s="12" t="n">
-        <v>334.2</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B95" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="C95" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:30:44</t>
-        </is>
-      </c>
-      <c r="D95" s="15" t="inlineStr">
-        <is>
-          <t>-33.39194,-71.252428</t>
-        </is>
-      </c>
-      <c r="E95" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F95" s="12" t="n">
-        <v>84.7</v>
-      </c>
-      <c r="G95" s="12" t="n">
-        <v>65285.6</v>
-      </c>
-      <c r="H95" s="12" t="n">
-        <v>420.2</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B96" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="C96" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:32:44</t>
-        </is>
-      </c>
-      <c r="D96" s="15" t="inlineStr">
-        <is>
-          <t>-33.378054,-71.283</t>
-        </is>
-      </c>
-      <c r="E96" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F96" s="12" t="n">
-        <v>109.7</v>
-      </c>
-      <c r="G96" s="12" t="n">
-        <v>65288.8</v>
-      </c>
-      <c r="H96" s="12" t="n">
-        <v>358.8</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B97" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="C97" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:33:44</t>
-        </is>
-      </c>
-      <c r="D97" s="15" t="inlineStr">
-        <is>
-          <t>-33.370564,-71.300398</t>
-        </is>
-      </c>
-      <c r="E97" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F97" s="12" t="n">
-        <v>110.2</v>
-      </c>
-      <c r="G97" s="12" t="n">
-        <v>65290.7</v>
-      </c>
-      <c r="H97" s="12" t="n">
-        <v>309.9</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B98" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="C98" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:34:44</t>
-        </is>
-      </c>
-      <c r="D98" s="15" t="inlineStr">
-        <is>
-          <t>-33.362495,-71.317435</t>
-        </is>
-      </c>
-      <c r="E98" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F98" s="12" t="n">
-        <v>105</v>
-      </c>
-      <c r="G98" s="12" t="n">
-        <v>65292.5</v>
-      </c>
-      <c r="H98" s="12" t="n">
-        <v>302.8</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B99" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="C99" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:35:44</t>
-        </is>
-      </c>
-      <c r="D99" s="15" t="inlineStr">
-        <is>
-          <t>-33.354711,-71.334664</t>
-        </is>
-      </c>
-      <c r="E99" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F99" s="12" t="n">
-        <v>110.2</v>
-      </c>
-      <c r="G99" s="12" t="n">
-        <v>65294.3</v>
-      </c>
-      <c r="H99" s="12" t="n">
-        <v>288.5</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B100" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="C100" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:36:44</t>
-        </is>
-      </c>
-      <c r="D100" s="15" t="inlineStr">
-        <is>
-          <t>-33.346987,-71.351864</t>
-        </is>
-      </c>
-      <c r="E100" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F100" s="12" t="n">
-        <v>109.6</v>
-      </c>
-      <c r="G100" s="12" t="n">
-        <v>65296.1</v>
-      </c>
-      <c r="H100" s="12" t="n">
-        <v>278.2</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B101" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="C101" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:37:44</t>
-        </is>
-      </c>
-      <c r="D101" s="15" t="inlineStr">
-        <is>
-          <t>-33.339269,-71.36912</t>
-        </is>
-      </c>
-      <c r="E101" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F101" s="12" t="n">
-        <v>108.9</v>
-      </c>
-      <c r="G101" s="12" t="n">
-        <v>65297.9</v>
-      </c>
-      <c r="H101" s="12" t="n">
-        <v>270.6</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B102" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="C102" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:38:44</t>
-        </is>
-      </c>
-      <c r="D102" s="15" t="inlineStr">
-        <is>
-          <t>-33.331501,-71.38635</t>
-        </is>
-      </c>
-      <c r="E102" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F102" s="12" t="n">
-        <v>109</v>
-      </c>
-      <c r="G102" s="12" t="n">
-        <v>65299.8</v>
-      </c>
-      <c r="H102" s="12" t="n">
-        <v>264.2</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B103" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="C103" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:39:44</t>
-        </is>
-      </c>
-      <c r="D103" s="15" t="inlineStr">
-        <is>
-          <t>-33.318513,-71.397761</t>
-        </is>
-      </c>
-      <c r="E103" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F103" s="12" t="n">
-        <v>114.5</v>
-      </c>
-      <c r="G103" s="12" t="n">
-        <v>65301.6</v>
-      </c>
-      <c r="H103" s="12" t="n">
-        <v>265.6</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B104" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="C104" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 11:40:44</t>
-        </is>
-      </c>
-      <c r="D104" s="15" t="inlineStr">
-        <is>
-          <t>-33.306928,-71.409003</t>
-        </is>
-      </c>
-      <c r="E104" s="12" t="inlineStr">
-        <is>
-          <t>s/n, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
-        </is>
-      </c>
-      <c r="F104" s="12" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="G104" s="12" t="n">
-        <v>65303.2</v>
-      </c>
-      <c r="H104" s="12" t="n">
-        <v>264.2</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B105" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="C105" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 12:06:08</t>
-        </is>
-      </c>
-      <c r="D105" s="15" t="inlineStr">
-        <is>
-          <t>-33.224113,-71.469302</t>
-        </is>
-      </c>
-      <c r="E105" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F105" s="12" t="n">
-        <v>103.2</v>
-      </c>
-      <c r="G105" s="12" t="n">
-        <v>65314.8</v>
-      </c>
-      <c r="H105" s="12" t="n">
-        <v>326.5</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B106" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="C106" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 12:07:08</t>
-        </is>
-      </c>
-      <c r="D106" s="15" t="inlineStr">
-        <is>
-          <t>-33.210556,-71.478677</t>
-        </is>
-      </c>
-      <c r="E106" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F106" s="12" t="n">
-        <v>101.9</v>
-      </c>
-      <c r="G106" s="12" t="n">
-        <v>65316.6</v>
-      </c>
-      <c r="H106" s="12" t="n">
-        <v>365.5</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B107" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="C107" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 12:08:08</t>
-        </is>
-      </c>
-      <c r="D107" s="15" t="inlineStr">
-        <is>
-          <t>-33.198961,-71.490969</t>
-        </is>
-      </c>
-      <c r="E107" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F107" s="12" t="n">
-        <v>107.7</v>
-      </c>
-      <c r="G107" s="12" t="n">
-        <v>65318.3</v>
-      </c>
-      <c r="H107" s="12" t="n">
-        <v>376.3</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B108" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="C108" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 12:09:08</t>
-        </is>
-      </c>
-      <c r="D108" s="15" t="inlineStr">
-        <is>
-          <t>-33.185309,-71.501905</t>
-        </is>
-      </c>
-      <c r="E108" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F108" s="12" t="n">
-        <v>109.9</v>
-      </c>
-      <c r="G108" s="12" t="n">
-        <v>65320.1</v>
-      </c>
-      <c r="H108" s="12" t="n">
-        <v>351.2</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B109" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="C109" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 12:10:08</t>
-        </is>
-      </c>
-      <c r="D109" s="15" t="inlineStr">
-        <is>
-          <t>-33.174444,-71.51614</t>
-        </is>
-      </c>
-      <c r="E109" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F109" s="12" t="n">
-        <v>109.9</v>
-      </c>
-      <c r="G109" s="12" t="n">
-        <v>65322</v>
-      </c>
-      <c r="H109" s="12" t="n">
-        <v>348.7</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B110" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="C110" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 12:11:08</t>
-        </is>
-      </c>
-      <c r="D110" s="15" t="inlineStr">
-        <is>
-          <t>-33.166486,-71.531748</t>
-        </is>
-      </c>
-      <c r="E110" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F110" s="12" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="G110" s="12" t="n">
-        <v>65323.7</v>
-      </c>
-      <c r="H110" s="12" t="n">
-        <v>349.1</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B111" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="C111" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 12:12:08</t>
-        </is>
-      </c>
-      <c r="D111" s="15" t="inlineStr">
-        <is>
-          <t>-33.159788,-71.544855</t>
-        </is>
-      </c>
-      <c r="E111" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F111" s="12" t="n">
-        <v>101.4</v>
-      </c>
-      <c r="G111" s="12" t="n">
-        <v>65325.1</v>
-      </c>
-      <c r="H111" s="12" t="n">
-        <v>368.7</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B112" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="C112" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 12:13:08</t>
-        </is>
-      </c>
-      <c r="D112" s="15" t="inlineStr">
-        <is>
-          <t>-33.14935,-71.55852</t>
-        </is>
-      </c>
-      <c r="E112" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F112" s="12" t="n">
-        <v>110.6</v>
-      </c>
-      <c r="G112" s="12" t="n">
-        <v>65326.9</v>
-      </c>
-      <c r="H112" s="12" t="n">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B113" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="C113" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 12:14:08</t>
-        </is>
-      </c>
-      <c r="D113" s="15" t="inlineStr">
-        <is>
-          <t>-33.133708,-71.562403</t>
-        </is>
-      </c>
-      <c r="E113" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F113" s="12" t="n">
-        <v>104</v>
-      </c>
-      <c r="G113" s="12" t="n">
-        <v>65328.7</v>
-      </c>
-      <c r="H113" s="12" t="n">
-        <v>324.6</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="7" t="inlineStr">
-        <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
-        </is>
-      </c>
-      <c r="B114" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="C114" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 12:15:08</t>
-        </is>
-      </c>
-      <c r="D114" s="15" t="inlineStr">
-        <is>
-          <t>-33.11785,-71.560635</t>
-        </is>
-      </c>
-      <c r="E114" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F114" s="12" t="n">
-        <v>84.5</v>
-      </c>
-      <c r="G114" s="12" t="n">
-        <v>65330.5</v>
-      </c>
-      <c r="H114" s="12" t="n">
-        <v>338.9</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
-        </is>
-      </c>
-      <c r="B115" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C115" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 14:08:42</t>
-        </is>
-      </c>
-      <c r="D115" s="15" t="inlineStr">
-        <is>
-          <t>-33.107,-71.569879</t>
-        </is>
-      </c>
-      <c r="E115" s="12" t="inlineStr">
-        <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
-        </is>
-      </c>
-      <c r="F115" s="12" t="n">
-        <v>104.3</v>
-      </c>
-      <c r="G115" s="12" t="n">
-        <v>260780.3</v>
-      </c>
-      <c r="H115" s="12" t="n">
-        <v>367.9</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
-        </is>
-      </c>
-      <c r="B116" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C116" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 14:08:46</t>
-        </is>
-      </c>
-      <c r="D116" s="15" t="inlineStr">
-        <is>
-          <t>-33.107137,-71.568647</t>
-        </is>
-      </c>
-      <c r="E116" s="12" t="inlineStr">
-        <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
-        </is>
-      </c>
-      <c r="F116" s="12" t="n">
-        <v>105.1</v>
-      </c>
-      <c r="G116" s="12" t="n">
-        <v>260780.4</v>
-      </c>
-      <c r="H116" s="12" t="n">
-        <v>368.1</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
-        </is>
-      </c>
-      <c r="B117" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C117" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 14:09:27</t>
-        </is>
-      </c>
-      <c r="D117" s="15" t="inlineStr">
-        <is>
-          <t>-33.106817,-71.556895</t>
-        </is>
-      </c>
-      <c r="E117" s="12" t="inlineStr">
-        <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
-        </is>
-      </c>
-      <c r="F117" s="12" t="n">
-        <v>81</v>
-      </c>
-      <c r="G117" s="12" t="n">
-        <v>260781.6</v>
-      </c>
-      <c r="H117" s="12" t="n">
-        <v>349.4</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
-        </is>
-      </c>
-      <c r="B118" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C118" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 14:47:45</t>
-        </is>
-      </c>
-      <c r="D118" s="15" t="inlineStr">
-        <is>
-          <t>-33.115854,-71.560497</t>
-        </is>
-      </c>
-      <c r="E118" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F118" s="12" t="n">
-        <v>102.5</v>
-      </c>
-      <c r="G118" s="12" t="n">
-        <v>260816.5</v>
-      </c>
-      <c r="H118" s="12" t="n">
-        <v>339.4</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
-        </is>
-      </c>
-      <c r="B119" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C119" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 14:48:14</t>
-        </is>
-      </c>
-      <c r="D119" s="15" t="inlineStr">
-        <is>
-          <t>-33.121168,-71.561407</t>
-        </is>
-      </c>
-      <c r="E119" s="12" t="inlineStr">
-        <is>
-          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
-        </is>
-      </c>
-      <c r="F119" s="12" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="G119" s="12" t="n">
-        <v>260817.1</v>
-      </c>
-      <c r="H119" s="12" t="n">
-        <v>352.1</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
-        </is>
-      </c>
-      <c r="B120" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C120" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/24 20:27:40</t>
-        </is>
-      </c>
-      <c r="D120" s="15" t="inlineStr">
-        <is>
-          <t>-33.106894,-71.550205</t>
-        </is>
-      </c>
-      <c r="E120" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F120" s="12" t="n">
-        <v>106.1</v>
-      </c>
-      <c r="G120" s="12" t="n">
-        <v>261242.2</v>
-      </c>
-      <c r="H120" s="12" t="n">
-        <v>352.2</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
-        </is>
-      </c>
-      <c r="B121" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C121" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/24 20:27:48</t>
-        </is>
-      </c>
-      <c r="D121" s="15" t="inlineStr">
-        <is>
-          <t>-33.10767,-71.55247</t>
-        </is>
-      </c>
-      <c r="E121" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F121" s="12" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="G121" s="12" t="n">
-        <v>261242.5</v>
-      </c>
-      <c r="H121" s="12" t="n">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
-        </is>
-      </c>
-      <c r="B122" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="C122" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/24 20:28:16</t>
-        </is>
-      </c>
-      <c r="D122" s="15" t="inlineStr">
-        <is>
-          <t>-33.111025,-71.559678</t>
-        </is>
-      </c>
-      <c r="E122" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F122" s="12" t="n">
-        <v>103.5</v>
-      </c>
-      <c r="G122" s="12" t="n">
-        <v>261243.2</v>
-      </c>
-      <c r="H122" s="12" t="n">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
-        </is>
-      </c>
-      <c r="B123" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="C123" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/24 20:28:48</t>
-        </is>
-      </c>
-      <c r="D123" s="15" t="inlineStr">
-        <is>
-          <t>-33.118716,-71.56082</t>
-        </is>
-      </c>
-      <c r="E123" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F123" s="12" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="G123" s="12" t="n">
-        <v>261244.1</v>
-      </c>
-      <c r="H123" s="12" t="n">
-        <v>343.8</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 RXDL-61 OPERACIONES</t>
-        </is>
-      </c>
-      <c r="B124" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C124" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 14:19:11</t>
-        </is>
-      </c>
-      <c r="D124" s="15" t="inlineStr">
-        <is>
-          <t>-33.078618,-71.626482</t>
-        </is>
-      </c>
-      <c r="E124" s="12" t="inlineStr">
-        <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
-        </is>
-      </c>
-      <c r="F124" s="12" t="n">
-        <v>109</v>
-      </c>
-      <c r="G124" s="12" t="n">
-        <v>174133</v>
-      </c>
-      <c r="H124" s="12" t="n">
-        <v>452.6</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 RXDL-61 OPERACIONES</t>
-        </is>
-      </c>
-      <c r="B125" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C125" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/22 14:20:10</t>
-        </is>
-      </c>
-      <c r="D125" s="15" t="inlineStr">
-        <is>
-          <t>-33.067049,-71.633956</t>
-        </is>
-      </c>
-      <c r="E125" s="12" t="inlineStr">
-        <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
-        </is>
-      </c>
-      <c r="F125" s="12" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="G125" s="12" t="n">
-        <v>174134.6</v>
-      </c>
-      <c r="H125" s="12" t="n">
-        <v>433.3</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 RXDL-61 OPERACIONES</t>
-        </is>
-      </c>
-      <c r="B126" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C126" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/23 09:31:40</t>
-        </is>
-      </c>
-      <c r="D126" s="15" t="inlineStr">
-        <is>
-          <t>-32.983884,-71.500411</t>
-        </is>
-      </c>
-      <c r="E126" s="12" t="inlineStr">
-        <is>
-          <t>Camino Internacional Valparaíso - Mendoza, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F126" s="12" t="n">
-        <v>100.5</v>
-      </c>
-      <c r="G126" s="12" t="n">
-        <v>174523.8</v>
-      </c>
-      <c r="H126" s="12" t="n">
-        <v>122.9</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 RXDL-61 OPERACIONES</t>
-        </is>
-      </c>
-      <c r="B127" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C127" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/23 09:32:40</t>
-        </is>
-      </c>
-      <c r="D127" s="15" t="inlineStr">
-        <is>
-          <t>-32.996284,-71.501418</t>
-        </is>
-      </c>
-      <c r="E127" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 64, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
-        </is>
-      </c>
-      <c r="F127" s="12" t="n">
-        <v>78.8</v>
-      </c>
-      <c r="G127" s="12" t="n">
-        <v>174525.2</v>
-      </c>
-      <c r="H127" s="12" t="n">
-        <v>140.1</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 RXDL-61 OPERACIONES</t>
-        </is>
-      </c>
-      <c r="B128" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C128" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/23 10:03:32</t>
-        </is>
-      </c>
-      <c r="D128" s="15" t="inlineStr">
-        <is>
-          <t>-33.088351,-71.542177</t>
-        </is>
-      </c>
-      <c r="E128" s="12" t="inlineStr">
-        <is>
-          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
-        </is>
-      </c>
-      <c r="F128" s="12" t="n">
-        <v>101.6</v>
-      </c>
-      <c r="G128" s="12" t="n">
-        <v>174563.5</v>
-      </c>
-      <c r="H128" s="12" t="n">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 RXDL-61 OPERACIONES</t>
-        </is>
-      </c>
-      <c r="B129" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C129" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/23 10:03:44</t>
-        </is>
-      </c>
-      <c r="D129" s="15" t="inlineStr">
-        <is>
-          <t>-33.085761,-71.544134</t>
-        </is>
-      </c>
-      <c r="E129" s="12" t="inlineStr">
-        <is>
-          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F129" s="12" t="n">
-        <v>105.6</v>
-      </c>
-      <c r="G129" s="12" t="n">
-        <v>174563.8</v>
-      </c>
-      <c r="H129" s="12" t="n">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 RXDL-61 OPERACIONES</t>
-        </is>
-      </c>
-      <c r="B130" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C130" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/23 10:04:19</t>
-        </is>
-      </c>
-      <c r="D130" s="15" t="inlineStr">
-        <is>
-          <t>-33.078217,-71.546978</t>
-        </is>
-      </c>
-      <c r="E130" s="12" t="inlineStr">
-        <is>
-          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F130" s="12" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="G130" s="12" t="n">
-        <v>174564.7</v>
-      </c>
-      <c r="H130" s="12" t="n">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 RXDL-61 OPERACIONES</t>
-        </is>
-      </c>
-      <c r="B131" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="C131" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/23 10:06:00</t>
-        </is>
-      </c>
-      <c r="D131" s="15" t="inlineStr">
-        <is>
-          <t>-33.065183,-71.531366</t>
-        </is>
-      </c>
-      <c r="E131" s="12" t="inlineStr">
-        <is>
-          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F131" s="12" t="n">
-        <v>105.5</v>
-      </c>
-      <c r="G131" s="12" t="n">
-        <v>174566.9</v>
-      </c>
-      <c r="H131" s="12" t="n">
-        <v>295.5</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 RXDL-61 OPERACIONES</t>
-        </is>
-      </c>
-      <c r="B132" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="C132" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/23 10:06:13</t>
-        </is>
-      </c>
-      <c r="D132" s="15" t="inlineStr">
-        <is>
-          <t>-33.062309,-71.530029</t>
-        </is>
-      </c>
-      <c r="E132" s="12" t="inlineStr">
-        <is>
-          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F132" s="12" t="n">
-        <v>98</v>
-      </c>
-      <c r="G132" s="12" t="n">
-        <v>174567.3</v>
-      </c>
-      <c r="H132" s="12" t="n">
-        <v>278.3</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 RXDL-61 OPERACIONES</t>
-        </is>
-      </c>
-      <c r="B133" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="C133" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/23 10:13:01</t>
-        </is>
-      </c>
-      <c r="D133" s="15" t="inlineStr">
-        <is>
-          <t>-33.01484,-71.499892</t>
-        </is>
-      </c>
-      <c r="E133" s="12" t="inlineStr">
-        <is>
-          <t>Camino Internacional Valparaíso - Mendoza, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F133" s="12" t="n">
-        <v>106.6</v>
-      </c>
-      <c r="G133" s="12" t="n">
-        <v>174576.8</v>
-      </c>
-      <c r="H133" s="12" t="n">
-        <v>235.2</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 RXDL-61 OPERACIONES</t>
-        </is>
-      </c>
-      <c r="B134" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="C134" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/23 10:13:44</t>
-        </is>
-      </c>
-      <c r="D134" s="15" t="inlineStr">
-        <is>
-          <t>-33.00551,-71.508908</t>
-        </is>
-      </c>
-      <c r="E134" s="12" t="inlineStr">
-        <is>
-          <t>Camino Internacional Valparaíso - Mendoza, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F134" s="12" t="n">
-        <v>103</v>
-      </c>
-      <c r="G134" s="12" t="n">
-        <v>174578.1</v>
-      </c>
-      <c r="H134" s="12" t="n">
-        <v>204.9</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 RXDL-61 OPERACIONES</t>
-        </is>
-      </c>
-      <c r="B135" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="C135" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/23 10:13:56</t>
-        </is>
-      </c>
-      <c r="D135" s="15" t="inlineStr">
-        <is>
-          <t>-33.002751,-71.510215</t>
-        </is>
-      </c>
-      <c r="E135" s="12" t="inlineStr">
-        <is>
-          <t>Avenida Carlos Ibáñez del Campo, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
-        </is>
-      </c>
-      <c r="F135" s="12" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="G135" s="12" t="n">
-        <v>174578.4</v>
-      </c>
-      <c r="H135" s="12" t="n">
-        <v>200.8</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 RXDL-61 OPERACIONES</t>
-        </is>
-      </c>
-      <c r="B136" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="C136" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/23 10:18:44</t>
-        </is>
-      </c>
-      <c r="D136" s="15" t="inlineStr">
-        <is>
-          <t>-32.949168,-71.510894</t>
-        </is>
-      </c>
-      <c r="E136" s="12" t="inlineStr">
-        <is>
-          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
-        </is>
-      </c>
-      <c r="F136" s="12" t="n">
-        <v>107.8</v>
-      </c>
-      <c r="G136" s="12" t="n">
-        <v>174585.7</v>
-      </c>
-      <c r="H136" s="12" t="n">
-        <v>151.7</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 RXDL-61 OPERACIONES</t>
-        </is>
-      </c>
-      <c r="B137" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="C137" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/23 10:19:44</t>
-        </is>
-      </c>
-      <c r="D137" s="15" t="inlineStr">
-        <is>
-          <t>-32.933913,-71.513453</t>
-        </is>
-      </c>
-      <c r="E137" s="12" t="inlineStr">
-        <is>
-          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
-        </is>
-      </c>
-      <c r="F137" s="12" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="G137" s="12" t="n">
-        <v>174587.4</v>
-      </c>
-      <c r="H137" s="12" t="n">
-        <v>71.59999999999999</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 RXDL-61 OPERACIONES</t>
-        </is>
-      </c>
-      <c r="B138" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="C138" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/24 20:12:46</t>
-        </is>
-      </c>
-      <c r="D138" s="15" t="inlineStr">
-        <is>
-          <t>-32.981829,-71.500282</t>
-        </is>
-      </c>
-      <c r="E138" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 64, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
-        </is>
-      </c>
-      <c r="F138" s="12" t="n">
-        <v>107.5</v>
-      </c>
-      <c r="G138" s="12" t="n">
-        <v>175199.2</v>
-      </c>
-      <c r="H138" s="12" t="n">
-        <v>123.4</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 RXDL-61 OPERACIONES</t>
-        </is>
-      </c>
-      <c r="B139" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="C139" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/24 20:13:47</t>
-        </is>
-      </c>
-      <c r="D139" s="15" t="inlineStr">
-        <is>
-          <t>-32.9948,-71.501299</t>
-        </is>
-      </c>
-      <c r="E139" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 64, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
-        </is>
-      </c>
-      <c r="F139" s="12" t="n">
-        <v>85.8</v>
-      </c>
-      <c r="G139" s="12" t="n">
-        <v>175200.7</v>
-      </c>
-      <c r="H139" s="12" t="n">
-        <v>138.7</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 RXDL-61 OPERACIONES</t>
-        </is>
-      </c>
-      <c r="B140" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="C140" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/24 20:24:48</t>
-        </is>
-      </c>
-      <c r="D140" s="15" t="inlineStr">
-        <is>
-          <t>-33.075325,-71.544371</t>
-        </is>
-      </c>
-      <c r="E140" s="12" t="inlineStr">
-        <is>
-          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F140" s="12" t="n">
-        <v>100.1</v>
-      </c>
-      <c r="G140" s="12" t="n">
-        <v>175215.7</v>
-      </c>
-      <c r="H140" s="12" t="n">
-        <v>343.2</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 RXDL-61 OPERACIONES</t>
-        </is>
-      </c>
-      <c r="B141" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="C141" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/24 20:25:12</t>
-        </is>
-      </c>
-      <c r="D141" s="15" t="inlineStr">
-        <is>
-          <t>-33.078418,-71.548691</t>
-        </is>
-      </c>
-      <c r="E141" s="12" t="inlineStr">
-        <is>
-          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
-        </is>
-      </c>
-      <c r="F141" s="12" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="G141" s="12" t="n">
-        <v>175216.2</v>
-      </c>
-      <c r="H141" s="12" t="n">
-        <v>321.2</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 RXDL-61 OPERACIONES</t>
-        </is>
-      </c>
-      <c r="B142" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="C142" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/24 20:26:12</t>
-        </is>
-      </c>
-      <c r="D142" s="15" t="inlineStr">
-        <is>
-          <t>-33.090191,-71.541746</t>
-        </is>
-      </c>
-      <c r="E142" s="12" t="inlineStr">
-        <is>
-          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
-        </is>
-      </c>
-      <c r="F142" s="12" t="n">
-        <v>103.2</v>
-      </c>
-      <c r="G142" s="12" t="n">
-        <v>175217.7</v>
-      </c>
-      <c r="H142" s="12" t="n">
-        <v>320.6</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 RXDL-61 OPERACIONES</t>
-        </is>
-      </c>
-      <c r="B143" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="C143" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/24 20:26:32</t>
-        </is>
-      </c>
-      <c r="D143" s="15" t="inlineStr">
-        <is>
-          <t>-33.094784,-71.543372</t>
-        </is>
-      </c>
-      <c r="E143" s="12" t="inlineStr">
-        <is>
-          <t>Vía Las Palmas, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
-        </is>
-      </c>
-      <c r="F143" s="12" t="n">
-        <v>100.5</v>
-      </c>
-      <c r="G143" s="12" t="n">
-        <v>175218.3</v>
-      </c>
-      <c r="H143" s="12" t="n">
-        <v>313.6</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 RXDL-61 OPERACIONES</t>
-        </is>
-      </c>
-      <c r="B144" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="C144" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/24 20:26:50</t>
-        </is>
-      </c>
-      <c r="D144" s="15" t="inlineStr">
-        <is>
-          <t>-33.097308,-71.547427</t>
-        </is>
-      </c>
-      <c r="E144" s="12" t="inlineStr">
-        <is>
-          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
-        </is>
-      </c>
-      <c r="F144" s="12" t="n">
-        <v>86.90000000000001</v>
-      </c>
-      <c r="G144" s="12" t="n">
-        <v>175218.8</v>
-      </c>
-      <c r="H144" s="12" t="n">
-        <v>319.2</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 RXDL-61 OPERACIONES</t>
-        </is>
-      </c>
-      <c r="B145" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="C145" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/24 20:28:16</t>
-        </is>
-      </c>
-      <c r="D145" s="15" t="inlineStr">
-        <is>
-          <t>-33.111189,-71.559772</t>
-        </is>
-      </c>
-      <c r="E145" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F145" s="12" t="n">
-        <v>101.9</v>
-      </c>
-      <c r="G145" s="12" t="n">
-        <v>175221</v>
-      </c>
-      <c r="H145" s="12" t="n">
-        <v>345.3</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 RXDL-61 OPERACIONES</t>
-        </is>
-      </c>
-      <c r="B146" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="C146" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/24 20:28:49</t>
-        </is>
-      </c>
-      <c r="D146" s="15" t="inlineStr">
-        <is>
-          <t>-33.119619,-71.560914</t>
-        </is>
-      </c>
-      <c r="E146" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F146" s="12" t="n">
-        <v>82.59999999999999</v>
-      </c>
-      <c r="G146" s="12" t="n">
-        <v>175221.9</v>
-      </c>
-      <c r="H146" s="12" t="n">
-        <v>347.4</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 RXDL-61 OPERACIONES</t>
-        </is>
-      </c>
-      <c r="B147" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="C147" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/24 20:56:46</t>
-        </is>
-      </c>
-      <c r="D147" s="15" t="inlineStr">
-        <is>
-          <t>-33.079385,-71.626351</t>
-        </is>
-      </c>
-      <c r="E147" s="12" t="inlineStr">
-        <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
-        </is>
-      </c>
-      <c r="F147" s="12" t="n">
-        <v>101.6</v>
-      </c>
-      <c r="G147" s="12" t="n">
-        <v>175236.5</v>
-      </c>
-      <c r="H147" s="12" t="n">
-        <v>460.8</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 RXDL-61 OPERACIONES</t>
-        </is>
-      </c>
-      <c r="B148" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="C148" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/24 20:57:46</t>
-        </is>
-      </c>
-      <c r="D148" s="15" t="inlineStr">
-        <is>
-          <t>-33.06751,-71.633245</t>
-        </is>
-      </c>
-      <c r="E148" s="12" t="inlineStr">
-        <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
-        </is>
-      </c>
-      <c r="F148" s="12" t="n">
-        <v>102.3</v>
-      </c>
-      <c r="G148" s="12" t="n">
-        <v>175238.1</v>
-      </c>
-      <c r="H148" s="12" t="n">
-        <v>436.3</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 RXDL-61 OPERACIONES</t>
-        </is>
-      </c>
-      <c r="B149" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="C149" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/24 20:58:04</t>
-        </is>
-      </c>
-      <c r="D149" s="15" t="inlineStr">
-        <is>
-          <t>-33.066265,-71.637746</t>
-        </is>
-      </c>
-      <c r="E149" s="12" t="inlineStr">
-        <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
-        </is>
-      </c>
-      <c r="F149" s="12" t="n">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="G149" s="12" t="n">
-        <v>175238.5</v>
-      </c>
-      <c r="H149" s="12" t="n">
-        <v>415.3</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 RXDL-61 OPERACIONES</t>
-        </is>
-      </c>
-      <c r="B150" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="C150" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/25 21:08:17</t>
-        </is>
-      </c>
-      <c r="D150" s="15" t="inlineStr">
-        <is>
-          <t>-33.066598,-71.635033</t>
-        </is>
-      </c>
-      <c r="E150" s="12" t="inlineStr">
-        <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
-        </is>
-      </c>
-      <c r="F150" s="12" t="n">
-        <v>100.7</v>
-      </c>
-      <c r="G150" s="12" t="n">
-        <v>175669.8</v>
-      </c>
-      <c r="H150" s="12" t="n">
-        <v>431.4</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="7" t="inlineStr">
-        <is>
-          <t>GLP DF6 RXDL-61 OPERACIONES</t>
-        </is>
-      </c>
-      <c r="B151" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="C151" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/25 21:08:54</t>
-        </is>
-      </c>
-      <c r="D151" s="15" t="inlineStr">
-        <is>
-          <t>-33.072071,-71.62779</t>
-        </is>
-      </c>
-      <c r="E151" s="12" t="inlineStr">
-        <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
-        </is>
-      </c>
-      <c r="F151" s="12" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="G151" s="12" t="n">
-        <v>175670.8</v>
-      </c>
-      <c r="H151" s="12" t="n">
-        <v>431.3</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="7" t="inlineStr">
-        <is>
-          <t>GLP SKDX-44 V VIAL</t>
-        </is>
-      </c>
-      <c r="B152" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C152" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/23 07:47:11</t>
-        </is>
-      </c>
-      <c r="D152" s="15" t="inlineStr">
-        <is>
-          <t>-33.028376,-71.652639</t>
-        </is>
-      </c>
-      <c r="E152" s="12" t="inlineStr">
-        <is>
-          <t>Camino La Pólvora Costero, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
-        </is>
-      </c>
-      <c r="F152" s="12" t="n">
-        <v>141.7</v>
-      </c>
-      <c r="G152" s="12" t="n">
-        <v>145184.4</v>
-      </c>
-      <c r="H152" s="12" t="n">
-        <v>91.59999999999999</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="7" t="inlineStr">
-        <is>
-          <t>GLP SKDX-44 V VIAL</t>
-        </is>
-      </c>
-      <c r="B153" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C153" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/23 07:47:11</t>
-        </is>
-      </c>
-      <c r="D153" s="15" t="inlineStr">
-        <is>
-          <t>-33.028376,-71.652639</t>
-        </is>
-      </c>
-      <c r="E153" s="12" t="inlineStr">
-        <is>
-          <t>Camino La Pólvora Costero, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
-        </is>
-      </c>
-      <c r="F153" s="12" t="n">
-        <v>141.7</v>
-      </c>
-      <c r="G153" s="12" t="n">
-        <v>145184.4</v>
-      </c>
-      <c r="H153" s="12" t="n">
-        <v>91.59999999999999</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="7" t="inlineStr">
-        <is>
-          <t>GLP SKDX-44 V VIAL</t>
-        </is>
-      </c>
-      <c r="B154" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C154" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/23 07:47:58</t>
-        </is>
-      </c>
-      <c r="D154" s="15" t="inlineStr">
-        <is>
-          <t>-33.028376,-71.652639</t>
-        </is>
-      </c>
-      <c r="E154" s="12" t="inlineStr">
-        <is>
-          <t>Camino La Pólvora Costero, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
-        </is>
-      </c>
-      <c r="F154" s="12" t="n">
-        <v>141.7</v>
-      </c>
-      <c r="G154" s="12" t="n">
-        <v>145184.5</v>
-      </c>
-      <c r="H154" s="12" t="n">
-        <v>91.59999999999999</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="7" t="inlineStr">
-        <is>
-          <t>GLP SKDX-44 V VIAL</t>
-        </is>
-      </c>
-      <c r="B155" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C155" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/23 07:48:56</t>
-        </is>
-      </c>
-      <c r="D155" s="15" t="inlineStr">
-        <is>
-          <t>-33.032598,-71.629362</t>
-        </is>
-      </c>
-      <c r="E155" s="12" t="inlineStr">
-        <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
-        </is>
-      </c>
-      <c r="F155" s="12" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="G155" s="12" t="n">
-        <v>145186.8</v>
-      </c>
-      <c r="H155" s="12" t="n">
-        <v>11.6</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B156" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C156" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/24 19:07:17</t>
-        </is>
-      </c>
-      <c r="D156" s="15" t="inlineStr">
-        <is>
-          <t>-32.97347,-71.302447</t>
-        </is>
-      </c>
-      <c r="E156" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F156" s="12" t="n">
-        <v>100.5</v>
-      </c>
-      <c r="G156" s="12" t="n">
-        <v>115202.5</v>
-      </c>
-      <c r="H156" s="12" t="n">
-        <v>75.40000000000001</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B157" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C157" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/24 19:07:59</t>
-        </is>
-      </c>
-      <c r="D157" s="15" t="inlineStr">
-        <is>
-          <t>-32.981261,-71.310045</t>
-        </is>
-      </c>
-      <c r="E157" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F157" s="12" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="G157" s="12" t="n">
-        <v>115203.6</v>
-      </c>
-      <c r="H157" s="12" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B158" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C158" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/24 19:08:30</t>
-        </is>
-      </c>
-      <c r="D158" s="15" t="inlineStr">
-        <is>
-          <t>-32.984069,-71.317887</t>
-        </is>
-      </c>
-      <c r="E158" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F158" s="12" t="n">
-        <v>101.1</v>
-      </c>
-      <c r="G158" s="12" t="n">
-        <v>115204.4</v>
-      </c>
-      <c r="H158" s="12" t="n">
-        <v>77.2</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B159" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C159" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/24 19:08:46</t>
-        </is>
-      </c>
-      <c r="D159" s="15" t="inlineStr">
-        <is>
-          <t>-32.986648,-71.321198</t>
-        </is>
-      </c>
-      <c r="E159" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F159" s="12" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="G159" s="12" t="n">
-        <v>115204.9</v>
-      </c>
-      <c r="H159" s="12" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B160" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C160" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/24 19:09:11</t>
-        </is>
-      </c>
-      <c r="D160" s="15" t="inlineStr">
-        <is>
-          <t>-32.989576,-71.327162</t>
-        </is>
-      </c>
-      <c r="E160" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F160" s="12" t="n">
-        <v>100.9</v>
-      </c>
-      <c r="G160" s="12" t="n">
-        <v>115205.5</v>
-      </c>
-      <c r="H160" s="12" t="n">
-        <v>74.40000000000001</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B161" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C161" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/24 19:09:16</t>
-        </is>
-      </c>
-      <c r="D161" s="15" t="inlineStr">
-        <is>
-          <t>-32.990725,-71.327755</t>
-        </is>
-      </c>
-      <c r="E161" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F161" s="12" t="n">
-        <v>100.1</v>
-      </c>
-      <c r="G161" s="12" t="n">
-        <v>115205.7</v>
-      </c>
-      <c r="H161" s="12" t="n">
-        <v>75.09999999999999</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B162" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C162" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/24 19:10:18</t>
-        </is>
-      </c>
-      <c r="D162" s="15" t="inlineStr">
-        <is>
-          <t>-33.005592,-71.328105</t>
-        </is>
-      </c>
-      <c r="E162" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F162" s="12" t="n">
-        <v>99</v>
-      </c>
-      <c r="G162" s="12" t="n">
-        <v>115207.4</v>
-      </c>
-      <c r="H162" s="12" t="n">
-        <v>95.90000000000001</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B163" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="C163" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/24 19:14:19</t>
-        </is>
-      </c>
-      <c r="D163" s="15" t="inlineStr">
-        <is>
-          <t>-33.054475,-71.335471</t>
-        </is>
-      </c>
-      <c r="E163" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F163" s="12" t="n">
-        <v>106.7</v>
-      </c>
-      <c r="G163" s="12" t="n">
-        <v>115213.9</v>
-      </c>
-      <c r="H163" s="12" t="n">
-        <v>183.1</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B164" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="C164" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/24 19:15:19</t>
-        </is>
-      </c>
-      <c r="D164" s="15" t="inlineStr">
-        <is>
-          <t>-33.063683,-71.34876</t>
-        </is>
-      </c>
-      <c r="E164" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F164" s="12" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="G164" s="12" t="n">
-        <v>115215.5</v>
-      </c>
-      <c r="H164" s="12" t="n">
-        <v>204.1</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -12637,117 +9921,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId159"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="default" paperSize="1" scale="100" pageOrder="downThenOver" blackAndWhite="0" draft="0" errors="displayed"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId160"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId55"/>
   </tableParts>
 </worksheet>
 </file>
--- a/INFORME EXCESOS DE VELOCIDAD.xlsx
+++ b/INFORME EXCESOS DE VELOCIDAD.xlsx
@@ -222,8 +222,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SpeedingFleetsSummaryTable_1" displayName="SpeedingFleetsSummaryTable_1" ref="A5:I14" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A5:I14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SpeedingFleetsSummaryTable_1" displayName="SpeedingFleetsSummaryTable_1" ref="A5:I11" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A5:I11"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Alias"/>
     <tableColumn id="2" name="Excesos" dataDxfId="0"/>
@@ -240,8 +240,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SpeedingFleetsDetailTable_1" displayName="SpeedingFleetsDetailTable_1" ref="A5:O27" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A5:O27"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SpeedingFleetsDetailTable_1" displayName="SpeedingFleetsDetailTable_1" ref="A5:O20" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A5:O20"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Alias"/>
     <tableColumn id="2" name="Conductor"/>
@@ -264,8 +264,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SpeedingFleetsDataTable_1" displayName="SpeedingFleetsDataTable_1" ref="A5:H59" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A5:H59"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SpeedingFleetsDataTable_1" displayName="SpeedingFleetsDataTable_1" ref="A5:H36" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A5:H36"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Alias"/>
     <tableColumn id="2" name="Secuencial" dataDxfId="0"/>
@@ -569,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.710625" customWidth="1" style="7" min="1" max="1"/>
@@ -593,7 +593,7 @@
     <row r="3" ht="25" customHeight="1" s="8">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Desde : 2026/07/13 00:00:00 Hasta: 2026/08/08 23:59:59</t>
+          <t>Desde : 2026/07/13 00:00:00 Hasta: 2026/08/14 23:59:59</t>
         </is>
       </c>
     </row>
@@ -647,26 +647,26 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>GV TDLD-98 J PACHECHO</t>
+          <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>0.0006944444444444445</v>
+        <v>0.001840277777777778</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>0.0006944444444444445</v>
+        <v>0.0006134259259259259</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>100.1</v>
+        <v>104.6</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>100.1</v>
+        <v>102.2</v>
       </c>
       <c r="H6" s="12" t="n">
         <v>0</v>
@@ -678,26 +678,26 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>0.001388888888888889</v>
+        <v>0.002777777777777778</v>
       </c>
       <c r="D7" s="13" t="n">
         <v>0.0006944444444444445</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>2.9</v>
+        <v>6.4</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>104.7</v>
+        <v>103.5</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>104.4</v>
+        <v>102.2</v>
       </c>
       <c r="H7" s="12" t="n">
         <v>0</v>
@@ -709,26 +709,26 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>GV TDKV-88 L CORDERO</t>
+          <t>GV SHLC-74 B MIRANDA</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>6.944444444444444e-05</v>
+        <v>0.001388888888888889</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>6.944444444444444e-05</v>
+        <v>0.0006944444444444445</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>101.3</v>
+        <v>101.5</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>101.3</v>
+        <v>101</v>
       </c>
       <c r="H8" s="12" t="n">
         <v>0</v>
@@ -740,26 +740,26 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>GV SHLC-74 B MIRANDA</t>
+          <t>GV TM5 RXXG-15 E CABANILLA</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>0.0006944444444444445</v>
+        <v>0.001388888888888889</v>
       </c>
       <c r="D9" s="13" t="n">
         <v>0.0006944444444444445</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>100.5</v>
+        <v>102.8</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>100.5</v>
+        <v>102.6</v>
       </c>
       <c r="H9" s="12" t="n">
         <v>0</v>
@@ -771,26 +771,26 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>GV PEUGEOT THJY-73 J PONCE</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>0.0002546296296296296</v>
+        <v>0.002650462962962963</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>0.0002546296296296296</v>
+        <v>0.0008834837962962963</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>0.6</v>
+        <v>5.8</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>100.1</v>
+        <v>103.7</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>100.1</v>
+        <v>101.8</v>
       </c>
       <c r="H10" s="12" t="n">
         <v>0</v>
@@ -802,7 +802,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>JAC  LYTS-17 G GALEA</t>
         </is>
       </c>
       <c r="B11" s="12" t="n">
@@ -815,111 +815,18 @@
         <v>0.0006944444444444445</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>100.8</v>
+        <v>101.1</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>100.8</v>
+        <v>101.1</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>GLP SKDX-44 V VIAL</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="C12" s="13" t="n">
-        <v>0.002708333333333333</v>
-      </c>
-      <c r="D12" s="13" t="n">
-        <v>0.0003869097222222222</v>
-      </c>
-      <c r="E12" s="12" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="F12" s="12" t="n">
-        <v>103.6</v>
-      </c>
-      <c r="G12" s="12" t="n">
-        <v>101.7</v>
-      </c>
-      <c r="H12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="C13" s="13" t="n">
-        <v>0.008148148148148147</v>
-      </c>
-      <c r="D13" s="13" t="n">
-        <v>0.001164016203703704</v>
-      </c>
-      <c r="E13" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="F13" s="12" t="n">
-        <v>104</v>
-      </c>
-      <c r="G13" s="12" t="n">
-        <v>101.7</v>
-      </c>
-      <c r="H13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PCRF-25 TERRENO</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="13" t="n">
-        <v>0.0006944444444444445</v>
-      </c>
-      <c r="D14" s="13" t="n">
-        <v>0.0006944444444444445</v>
-      </c>
-      <c r="E14" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F14" s="12" t="n">
-        <v>100.4</v>
-      </c>
-      <c r="G14" s="12" t="n">
-        <v>100.4</v>
-      </c>
-      <c r="H14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -944,7 +851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O123"/>
+  <dimension ref="A1:O157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.710625" customWidth="1" style="7" min="1" max="1"/>
@@ -972,7 +879,7 @@
     <row r="3" ht="25" customHeight="1" s="8">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Desde : 2026/07/27 00:00:00 Hasta: 2026/08/02 23:59:58</t>
+          <t>Desde : 2026/08/03 00:00:00 Hasta: 2026/08/09 23:59:58</t>
         </is>
       </c>
     </row>
@@ -7052,7 +6959,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
         <v>1</v>
       </c>
@@ -7111,7 +7017,6 @@
           <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr"/>
       <c r="C110" t="n">
         <v>1</v>
       </c>
@@ -7170,7 +7075,6 @@
           <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
         <v>1</v>
       </c>
@@ -7229,7 +7133,6 @@
           <t>GV SHLC-74 B MIRANDA</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr"/>
       <c r="C112" t="n">
         <v>1</v>
       </c>
@@ -7288,7 +7191,6 @@
           <t>JAC  LYTS-17 G GALEA</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
         <v>1</v>
       </c>
@@ -7347,7 +7249,6 @@
           <t>GV SHLC-74 B MIRANDA</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr"/>
       <c r="C114" t="n">
         <v>2</v>
       </c>
@@ -7406,7 +7307,6 @@
           <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr"/>
       <c r="C115" t="n">
         <v>2</v>
       </c>
@@ -7465,7 +7365,6 @@
           <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr"/>
       <c r="C116" t="n">
         <v>2</v>
       </c>
@@ -7524,7 +7423,6 @@
           <t>GV TM5 RXXG-15 E CABANILLA</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
         <v>1</v>
       </c>
@@ -7583,7 +7481,6 @@
           <t>GV TM5 RXXG-15 E CABANILLA</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr"/>
       <c r="C118" t="n">
         <v>2</v>
       </c>
@@ -7642,7 +7539,6 @@
           <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
         <v>3</v>
       </c>
@@ -7701,7 +7597,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr"/>
       <c r="C120" t="n">
         <v>2</v>
       </c>
@@ -7760,7 +7655,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr"/>
       <c r="C121" t="n">
         <v>3</v>
       </c>
@@ -7819,7 +7713,6 @@
           <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr"/>
       <c r="C122" t="n">
         <v>3</v>
       </c>
@@ -7878,7 +7771,6 @@
           <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr"/>
       <c r="C123" t="n">
         <v>4</v>
       </c>
@@ -7928,6 +7820,2012 @@
         <v>0</v>
       </c>
       <c r="O123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>GV SHLC-74 B MIRANDA</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2026/08/10 09:12:32</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>-33.157548,-71.549489</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Ruta 64, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>2026/08/10 09:13:32</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>-33.165047,-71.534798</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J124" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K124" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L124" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="M124" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2026/08/10 10:29:37</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>-32.757227,-71.420873</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Ruta 64, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>2026/08/10 10:30:38</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>-32.743513,-71.417967</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Ruta F-190, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J125" s="14" t="n">
+        <v>0.0007060185185185185</v>
+      </c>
+      <c r="K125" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L125" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="M125" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>GV TDLD-98 J PACHECHO</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
+      <c r="C126" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026/08/11 00:47:13</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>-32.977793,-71.499934</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Ruta 64, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>2026/08/11 00:48:13</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>-32.992004,-71.501153</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Ruta 64, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J126" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L126" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="M126" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>GLP SKDX-44 V VIAL</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="n">
+        <v>1</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026/08/11 01:18:36</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>-33.031585,-71.631541</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Ruta 64, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>2026/08/11 01:22:22</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>-33.031872,-71.6299</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J127" s="14" t="n">
+        <v>0.002615740740740741</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L127" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="M127" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>GV SHLC-74 B MIRANDA</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="n">
+        <v>2</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026/08/11 09:46:56</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>-33.216008,-71.473704</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>2026/08/11 09:47:57</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>-33.229387,-71.466181</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J128" s="14" t="n">
+        <v>0.0007060185185185185</v>
+      </c>
+      <c r="K128" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L128" t="n">
+        <v>101</v>
+      </c>
+      <c r="M128" t="n">
+        <v>101</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>GV TDLD-98 J PACHECHO</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="n">
+        <v>2</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026/08/11 14:25:21</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>-33.15983,-71.544708</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Ruta 64, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>2026/08/11 14:26:21</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>-33.15096,-71.557673</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J129" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K129" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L129" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="M129" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>GV TDLD-98 J PACHECHO</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="n">
+        <v>3</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026/08/11 14:48:43</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>-32.951646,-71.509458</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>2026/08/11 14:49:21</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>-32.943313,-71.513542</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="J130" s="14" t="n">
+        <v>0.0004398148148148148</v>
+      </c>
+      <c r="K130" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L130" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="M130" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
+      <c r="C131" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026/08/11 15:16:59</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>-33.093469,-71.603099</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Ruta 64, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>2026/08/11 15:17:02</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>-33.094082,-71.602581</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="J131" s="14" t="n">
+        <v>3.472222222222222e-05</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L131" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="M131" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
+      <c r="C132" t="n">
+        <v>1</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026/08/11 17:10:00</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>-32.798908,-71.440814</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Ruta 64, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>2026/08/11 17:11:00</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>-32.810983,-71.441434</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Ruta F-190, Quintero, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J132" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K132" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L132" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="M132" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" t="n">
+        <v>2</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026/08/11 17:31:29</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>-32.942137,-71.482014</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Ruta F-190, Quintero, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>2026/08/11 17:32:08</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>-32.9487,-71.483747</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Ruta 64, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="J133" s="14" t="n">
+        <v>0.0004513888888888889</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L133" t="n">
+        <v>104</v>
+      </c>
+      <c r="M133" t="n">
+        <v>104</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>GV SHLC-74 B MIRANDA</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
+      <c r="C134" t="n">
+        <v>3</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026/08/11 22:16:04</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>-33.217343,-71.472838</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>2026/08/11 22:17:04</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>-33.205626,-71.484055</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J134" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K134" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L134" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="M134" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="n">
+        <v>3</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026/08/12 11:16:15</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>-33.38297,-71.391372</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Ruta 64, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>2026/08/12 11:17:15</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>-33.396877,-71.394671</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Ruta F-74-G, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="J135" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K135" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L135" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="M135" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>GLP SKDX-44 V VIAL</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" t="n">
+        <v>2</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026/08/12 12:27:11</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>-33.113036,-71.560164</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>2026/08/12 12:27:50</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>-33.121189,-71.561416</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J136" s="14" t="n">
+        <v>0.0004513888888888889</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L136" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="M136" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>GV TDLD-98 J PACHECHO</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" t="n">
+        <v>4</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026/08/12 14:44:39</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>-33.163382,-71.537721</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>2026/08/12 14:45:39</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>-33.155922,-71.552342</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J137" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K137" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L137" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="M137" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>GV TDLD-98 J PACHECHO</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" t="n">
+        <v>5</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026/08/12 14:47:39</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>-33.13014,-71.561957</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>2026/08/12 14:48:39</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>-33.115708,-71.560383</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J138" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K138" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L138" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="M138" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="n">
+        <v>4</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026/08/12 15:55:12</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>-33.376179,-71.386332</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Ruta F-74-G, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>2026/08/12 15:55:25</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>-33.373618,-71.385271</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Ruta F-74-G, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="J139" s="14" t="n">
+        <v>0.000150462962962963</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L139" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="M139" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="n">
+        <v>5</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026/08/12 16:13:58</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>-33.305002,-71.411287</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Ruta F-74-G, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>2026/08/12 16:15:57</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>-33.277849,-71.428907</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J140" s="14" t="n">
+        <v>0.001377314814814815</v>
+      </c>
+      <c r="K140" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L140" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="M140" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="n">
+        <v>6</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026/08/12 17:29:08</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>-32.982117,-71.500227</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>2026/08/12 17:29:59</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>-32.970275,-71.5001</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Ruta E-30-F, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="J141" s="14" t="n">
+        <v>0.0005902777777777778</v>
+      </c>
+      <c r="K141" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L141" t="n">
+        <v>107</v>
+      </c>
+      <c r="M141" t="n">
+        <v>107</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="n">
+        <v>7</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2026/08/12 17:32:09</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>-32.943489,-71.513534</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Ruta E-30-F, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>2026/08/12 17:33:09</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>-32.929667,-71.512068</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="J142" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K142" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L142" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="M142" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026/08/13 07:27:21</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>-33.054539,-71.335674</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Ruta 64, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>2026/08/13 07:28:21</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>-33.063291,-71.348177</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J143" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K143" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L143" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="M143" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="n">
+        <v>2</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2026/08/13 09:17:07</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>-33.09653,-71.545845</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>2026/08/13 09:17:46</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>-33.088266,-71.5422</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="J144" s="14" t="n">
+        <v>0.0004513888888888889</v>
+      </c>
+      <c r="K144" t="n">
+        <v>1</v>
+      </c>
+      <c r="L144" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="M144" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="n">
+        <v>8</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2026/08/13 09:24:35</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>-32.985661,-71.500562</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>2026/08/13 09:25:32</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>-32.998254,-71.502383</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Camino Internacional Valparaíso - Mendoza, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J145" s="14" t="n">
+        <v>0.0006597222222222222</v>
+      </c>
+      <c r="K145" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L145" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="M145" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="N145" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>GV SHLC-74 B MIRANDA</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="n">
+        <v>4</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2026/08/13 10:02:31</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>-33.35848,-71.326553</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>2026/08/13 10:03:31</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>-33.364972,-71.312258</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J146" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K146" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L146" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="M146" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="N146" t="n">
+        <v>0</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="n">
+        <v>2</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2026/08/13 10:39:59</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>-33.227,-71.467768</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Ruta F-190, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>2026/08/13 10:40:59</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>-33.213935,-71.475097</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J147" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K147" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L147" t="n">
+        <v>108</v>
+      </c>
+      <c r="M147" t="n">
+        <v>108</v>
+      </c>
+      <c r="N147" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="n">
+        <v>3</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2026/08/13 10:49:59</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>-33.119158,-71.56076</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>2026/08/13 10:50:42</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>-33.109677,-71.558209</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J148" s="14" t="n">
+        <v>0.0004976851851851852</v>
+      </c>
+      <c r="K148" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L148" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="M148" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="N148" t="n">
+        <v>0</v>
+      </c>
+      <c r="O148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>JAC  LYTS-17 G GALEA</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="n">
+        <v>1</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2026/08/13 11:57:49</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>-33.285524,-71.411366</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Ruta 64, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>2026/08/13 11:58:27</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>-33.279484,-71.413704</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Ruta F-852, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J149" s="14" t="n">
+        <v>0.0004398148148148148</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L149" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="M149" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="N149" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>GV TDLD-98 J PACHECHO</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="n">
+        <v>6</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2026/08/13 14:31:13</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>-33.225857,-71.468365</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>2026/08/13 14:32:13</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>-33.213027,-71.475997</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J150" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K150" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L150" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="M150" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="N150" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="n">
+        <v>4</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2026/08/13 18:25:02</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>-33.268542,-71.432855</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>2026/08/13 18:26:02</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>-33.255908,-71.44039</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J151" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K151" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L151" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="M151" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="N151" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="n">
+        <v>5</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026/08/13 18:48:02</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>-33.071993,-71.571936</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>2026/08/13 18:48:57</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>-33.063353,-71.582457</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="J152" s="14" t="n">
+        <v>0.0006365740740740741</v>
+      </c>
+      <c r="K152" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L152" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="M152" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="N152" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>GV SHLC-74 B MIRANDA</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" t="n">
+        <v>5</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026/08/13 22:23:11</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>-33.203884,-71.485888</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>2026/08/13 22:24:11</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>-33.192111,-71.496379</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J153" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K153" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L153" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="M153" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="N153" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>GV TDLD-98 J PACHECHO</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
+      <c r="C154" t="n">
+        <v>7</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026/08/14 00:38:07</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>-32.98055,-71.500149</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>2026/08/14 00:39:07</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>-32.994359,-71.501297</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Ruta 64, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J154" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K154" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L154" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="M154" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="N154" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
+      <c r="C155" t="n">
+        <v>6</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2026/08/14 08:05:03</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>-33.10634,-71.549378</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>2026/08/14 08:05:51</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>-33.112291,-71.560068</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J155" s="14" t="n">
+        <v>0.0005555555555555556</v>
+      </c>
+      <c r="K155" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L155" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="M155" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="N155" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="n">
+        <v>1</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2026/08/14 19:10:37</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>-33.053836,-71.334523</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Ruta 64, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>2026/08/14 19:11:38</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>-33.063285,-71.348089</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J156" s="14" t="n">
+        <v>0.0007060185185185185</v>
+      </c>
+      <c r="K156" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L156" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="M156" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="N156" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
+      <c r="C157" t="n">
+        <v>2</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2026/08/14 19:12:38</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>-33.06932,-71.363576</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>2026/08/14 19:13:38</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>-33.067875,-71.380877</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J157" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K157" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L157" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="M157" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="N157" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7952,7 +9850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.710625" customWidth="1" style="7" min="1" max="1"/>
@@ -7978,7 +9876,7 @@
     <row r="3" ht="25" customHeight="1" s="8">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Desde : 2026/07/27 00:00:00 Hasta: 2026/08/02 23:59:58</t>
+          <t>Desde : 2026/08/03 00:00:00 Hasta: 2026/08/09 23:59:58</t>
         </is>
       </c>
     </row>
@@ -8027,7 +9925,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>GV TDLD-98 J PACHECHO</t>
+          <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
@@ -8035,33 +9933,33 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>2026/08/02 14:32:36</t>
+          <t>2026/08/05 12:23:39</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>-33.16243,-71.539564</t>
+          <t>-33.080686,-71.561833</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F6" s="12" t="n">
-        <v>100.1</v>
+        <v>104.6</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>77880.5</v>
+        <v>61389.2</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>360.8</v>
+        <v>176.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>GV TDLD-98 J PACHECHO</t>
+          <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
       <c r="B7" s="12" t="n">
@@ -8069,169 +9967,169 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>2026/08/02 14:33:36</t>
+          <t>2026/08/05 12:24:39</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>-33.15517,-71.553769</t>
+          <t>-33.070089,-71.574806</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F7" s="12" t="n">
-        <v>91.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>77882.10000000001</v>
+        <v>61390.9</v>
       </c>
       <c r="H7" s="12" t="n">
-        <v>356.3</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>2026/07/30 18:54:20</t>
+          <t>2026/08/06 12:13:09</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>-32.897768,-71.449538</t>
+          <t>-33.059575,-71.530514</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-190, Quillota, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F8" s="12" t="n">
-        <v>104.7</v>
+        <v>101.7</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>187456</v>
+        <v>61506.4</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>125.6</v>
+        <v>267.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>2026/07/30 18:55:20</t>
+          <t>2026/08/06 12:13:48</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>-32.906604,-71.440511</t>
+          <t>-33.066788,-71.533562</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-190, Quillota, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F9" s="12" t="n">
-        <v>76.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>187457.3</v>
+        <v>61507.3</v>
       </c>
       <c r="H9" s="12" t="n">
-        <v>124.3</v>
+        <v>305.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>2026/07/31 13:08:39</t>
+          <t>2026/08/07 12:07:15</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>-33.219324,-71.471926</t>
+          <t>-33.094897,-71.600273</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
         </is>
       </c>
       <c r="F10" s="12" t="n">
-        <v>104.1</v>
+        <v>100.2</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>187526.8</v>
+        <v>61623.8</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>330.6</v>
+        <v>427.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>2026/07/31 13:09:39</t>
+          <t>2026/08/07 12:08:15</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>-33.231962,-71.464083</t>
+          <t>-33.089443,-71.614598</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>94.7</v>
+        <v>84</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>187528.4</v>
+        <v>61625.3</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>337.4</v>
+        <v>469.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>GV TDKV-88 L CORDERO</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
@@ -8239,12 +10137,12 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>2026/07/30 17:56:03</t>
+          <t>2026/08/05 14:23:46</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>-33.10693,-71.550214</t>
+          <t>-33.163504,-71.537483</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
@@ -8253,19 +10151,19 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>101.3</v>
+        <v>101</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>76539</v>
+        <v>78551.10000000001</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>351.1</v>
+        <v>367.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>GV TDKV-88 L CORDERO</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B13" s="12" t="n">
@@ -8273,12 +10171,12 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>2026/07/30 17:56:09</t>
+          <t>2026/08/05 14:24:46</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>-33.107497,-71.5518</t>
+          <t>-33.156097,-71.552015</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
@@ -8287,223 +10185,223 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>93.2</v>
+        <v>93</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>76539.2</v>
+        <v>78552.7</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>347.1</v>
+        <v>368.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>GV SHLC-74 B MIRANDA</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>2026/07/31 07:36:59</t>
+          <t>2026/08/06 14:22:56</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>-33.158797,-71.546799</t>
+          <t>-33.231385,-71.464327</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>100.5</v>
+        <v>100.8</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>122625.2</v>
+        <v>78768</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>369.3</v>
+        <v>340</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>GV SHLC-74 B MIRANDA</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>2026/07/31 07:37:59</t>
+          <t>2026/08/06 14:23:56</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>-33.149438,-71.558461</t>
+          <t>-33.219271,-71.471768</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>89.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>122626.7</v>
+        <v>78769.5</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>344.9</v>
+        <v>335.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>GV PEUGEOT THJY-73 J PONCE</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>2026/07/28 15:58:20</t>
+          <t>2026/08/08 01:32:10</t>
         </is>
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>-32.733776,-71.436634</t>
+          <t>-33.234063,-71.462269</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-20, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>100.1</v>
+        <v>103.3</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>122447.9</v>
+        <v>79183.89999999999</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>26.1</v>
+        <v>344</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>GV PEUGEOT THJY-73 J PONCE</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>2026/07/28 15:58:42</t>
+          <t>2026/08/08 01:33:10</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>-32.736051,-71.431128</t>
+          <t>-33.244036,-71.449798</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-20, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>93</v>
+        <v>98.2</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>122448.5</v>
+        <v>79185.5</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>16.5</v>
+        <v>276.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>2026/07/28 02:11:25</t>
+          <t>2026/08/08 14:19:07</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>-32.944023,-71.513376</t>
+          <t>-33.232909,-71.463096</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>100.8</v>
+        <v>103.5</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>261970.6</v>
+        <v>79225.7</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>123</v>
+        <v>345.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>2026/07/28 02:12:25</t>
+          <t>2026/08/08 14:20:07</t>
         </is>
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>-32.935778,-71.513703</t>
+          <t>-33.219807,-71.471478</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>0</v>
+        <v>90.2</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>261971.5</v>
+        <v>79227.39999999999</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>84.90000000000001</v>
+        <v>336.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>GLP SKDX-44 V VIAL</t>
+          <t>GV SHLC-74 B MIRANDA</t>
         </is>
       </c>
       <c r="B20" s="12" t="n">
@@ -8511,33 +10409,33 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>2026/08/01 06:30:23</t>
+          <t>2026/08/05 16:09:19</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>-33.102452,-71.54806</t>
+          <t>-32.786803,-71.431676</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta F-190, Quintero, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>102.1</v>
+        <v>101.5</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>147132</v>
+        <v>124111.7</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>345.3</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>GLP SKDX-44 V VIAL</t>
+          <t>GV SHLC-74 B MIRANDA</t>
         </is>
       </c>
       <c r="B21" s="12" t="n">
@@ -8545,33 +10443,33 @@
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>2026/08/01 06:30:48</t>
+          <t>2026/08/05 16:10:19</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>-33.096687,-71.546062</t>
+          <t>-32.797308,-71.44036</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>s/n, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Ruta F-190, Quintero, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>95.90000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>147132.7</v>
+        <v>124113.1</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>310.4</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>GLP SKDX-44 V VIAL</t>
+          <t>GV SHLC-74 B MIRANDA</t>
         </is>
       </c>
       <c r="B22" s="12" t="n">
@@ -8579,33 +10477,33 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>2026/08/01 06:46:24</t>
+          <t>2026/08/06 09:46:47</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>-32.967111,-71.503823</t>
+          <t>-33.205819,-71.48396</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Ruta E-30-F, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>102.6</v>
+        <v>100.5</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>147153.7</v>
+        <v>124379.3</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>159.9</v>
+        <v>400</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>GLP SKDX-44 V VIAL</t>
+          <t>GV SHLC-74 B MIRANDA</t>
         </is>
       </c>
       <c r="B23" s="12" t="n">
@@ -8613,1251 +10511,469 @@
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>2026/08/01 06:47:14</t>
+          <t>2026/08/06 09:47:47</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>-32.957174,-71.510191</t>
+          <t>-33.216959,-71.473175</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>88.8</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>147155</v>
+        <v>124380.9</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>171.1</v>
+        <v>335.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>GLP SKDX-44 V VIAL</t>
+          <t>GV TM5 RXXG-15 E CABANILLA</t>
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>2026/08/01 06:50:24</t>
+          <t>2026/08/07 07:01:46</t>
         </is>
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>-32.989287,-71.500906</t>
+          <t>-33.275515,-71.429868</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Camino Internacional, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>103.1</v>
+        <v>102.3</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>147159.5</v>
+        <v>22879</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>136.8</v>
+        <v>298.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>GLP SKDX-44 V VIAL</t>
+          <t>GV TM5 RXXG-15 E CABANILLA</t>
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>2026/08/01 06:51:02</t>
+          <t>2026/08/07 07:02:46</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>-32.998137,-71.50228</t>
+          <t>-33.262462,-71.43552</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Camino Internacional, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>80</v>
+        <v>91.8</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>147160.4</v>
+        <v>22880.5</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>153.9</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>GLP SKDX-44 V VIAL</t>
+          <t>GV TM5 RXXG-15 E CABANILLA</t>
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>2026/08/01 09:40:00</t>
+          <t>2026/08/07 07:14:46</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>-33.013677,-71.500475</t>
+          <t>-33.143468,-71.561375</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Avenida Carlos Ibáñez del Campo, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>100.4</v>
+        <v>102.8</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>147253.8</v>
+        <v>22898.6</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>249.7</v>
+        <v>331.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>GLP SKDX-44 V VIAL</t>
+          <t>GV TM5 RXXG-15 E CABANILLA</t>
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>2026/08/01 09:40:16</t>
+          <t>2026/08/07 07:15:46</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>-33.017375,-71.500179</t>
+          <t>-33.130053,-71.561948</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Avenida Rubén Hurtado, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>93.3</v>
+        <v>87.7</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>147254.2</v>
+        <v>22900.1</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>240.3</v>
+        <v>336</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>GLP SKDX-44 V VIAL</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>2026/08/01 11:31:13</t>
+          <t>2026/08/03 06:01:10</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>-33.059472,-71.645814</t>
+          <t>-33.063154,-71.469437</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+          <t>Autopista Troncal Sur, Quilpué, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>100.6</v>
+        <v>100.2</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>147292.5</v>
+        <v>117052.1</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>322.9</v>
+        <v>116.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>GLP SKDX-44 V VIAL</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B29" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>2026/08/01 11:31:21</t>
+          <t>2026/08/03 06:02:10</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>-33.060679,-71.644303</t>
+          <t>-33.061893,-71.457259</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+          <t>s/n, Quilpué, Marga Marga, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>89.59999999999999</v>
+        <v>29.7</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>147292.8</v>
+        <v>117053.3</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>335.3</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>GLP SKDX-44 V VIAL</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B30" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>2026/08/01 11:31:50</t>
+          <t>2026/08/07 18:21:12</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>-33.06623,-71.64223</t>
+          <t>-32.924007,-71.28105</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>101.2</v>
+        <v>101.6</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>147293.5</v>
+        <v>118469.3</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>386.3</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>GLP SKDX-44 V VIAL</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B31" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>2026/08/01 11:31:55</t>
+          <t>2026/08/07 18:22:01</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>-33.067011,-71.641101</t>
+          <t>-32.933575,-71.288625</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>100.6</v>
+        <v>73.3</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>147293.7</v>
+        <v>118470.6</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>395.6</v>
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>GLP SKDX-44 V VIAL</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>2026/08/01 11:32:00</t>
+          <t>2026/08/07 18:36:12</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>-33.066878,-71.63965</t>
+          <t>-33.06936,-71.36277</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>101.8</v>
+        <v>103.7</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>147293.8</v>
+        <v>118490.2</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>404.3</v>
+        <v>192.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>GLP SKDX-44 V VIAL</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>2026/08/01 11:32:04</t>
+          <t>2026/08/07 18:37:12</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>-33.066455,-71.638545</t>
+          <t>-33.067906,-71.380727</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
         <v>103.6</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>147294</v>
+        <v>118491.9</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>410.7</v>
+        <v>177</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>GLP SKDX-44 V VIAL</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>2026/08/01 11:32:17</t>
+          <t>2026/08/07 18:38:12</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>-33.066758,-71.634562</t>
+          <t>-33.066117,-71.397749</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>101</v>
+        <v>88.2</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>147294.3</v>
+        <v>118493.5</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>432.8</v>
+        <v>169.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>GLP SKDX-44 V VIAL</t>
+          <t>JAC  LYTS-17 G GALEA</t>
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>2026/08/01 11:32:53</t>
+          <t>2026/08/06 07:52:03</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>-33.072407,-71.627597</t>
+          <t>-32.680652,-71.425247</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta E-30-F, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>85.90000000000001</v>
+        <v>101.1</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>147295.2</v>
+        <v>226852.1</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>431.9</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>GLP SKDX-44 V VIAL</t>
+          <t>JAC  LYTS-17 G GALEA</t>
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>2026/08/02 12:14:56</t>
+          <t>2026/08/06 07:53:03</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>-33.09045,-71.541794</t>
+          <t>-32.670624,-71.425352</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta E-30-F, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>102.2</v>
+        <v>63.9</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>147585.4</v>
+        <v>226853.2</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>321.6</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>GLP SKDX-44 V VIAL</t>
-        </is>
-      </c>
-      <c r="B37" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="C37" s="12" t="inlineStr">
-        <is>
-          <t>2026/08/02 12:15:15</t>
-        </is>
-      </c>
-      <c r="D37" s="15" t="inlineStr">
-        <is>
-          <t>-33.094806,-71.543443</t>
-        </is>
-      </c>
-      <c r="E37" s="12" t="inlineStr">
-        <is>
-          <t>Vía Las Palmas, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
-        </is>
-      </c>
-      <c r="F37" s="12" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="G37" s="12" t="n">
-        <v>147586</v>
-      </c>
-      <c r="H37" s="12" t="n">
-        <v>318.4</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>GLP SKDX-44 V VIAL</t>
-        </is>
-      </c>
-      <c r="B38" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="C38" s="12" t="inlineStr">
-        <is>
-          <t>2026/08/02 12:15:30</t>
-        </is>
-      </c>
-      <c r="D38" s="15" t="inlineStr">
-        <is>
-          <t>-33.096963,-71.546855</t>
-        </is>
-      </c>
-      <c r="E38" s="12" t="inlineStr">
-        <is>
-          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
-        </is>
-      </c>
-      <c r="F38" s="12" t="n">
-        <v>94.09999999999999</v>
-      </c>
-      <c r="G38" s="12" t="n">
-        <v>147586.4</v>
-      </c>
-      <c r="H38" s="12" t="n">
-        <v>321.6</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B39" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/27 06:25:04</t>
-        </is>
-      </c>
-      <c r="D39" s="15" t="inlineStr">
-        <is>
-          <t>-33.067327,-71.387599</t>
-        </is>
-      </c>
-      <c r="E39" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F39" s="12" t="n">
-        <v>104</v>
-      </c>
-      <c r="G39" s="12" t="n">
-        <v>115264</v>
-      </c>
-      <c r="H39" s="12" t="n">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B40" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/27 06:26:04</t>
-        </is>
-      </c>
-      <c r="D40" s="15" t="inlineStr">
-        <is>
-          <t>-33.068846,-71.370499</t>
-        </is>
-      </c>
-      <c r="E40" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F40" s="12" t="n">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="G40" s="12" t="n">
-        <v>115265.6</v>
-      </c>
-      <c r="H40" s="12" t="n">
-        <v>176.9</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B41" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C41" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/27 06:32:04</t>
-        </is>
-      </c>
-      <c r="D41" s="15" t="inlineStr">
-        <is>
-          <t>-33.016759,-71.31988</t>
-        </is>
-      </c>
-      <c r="E41" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F41" s="12" t="n">
-        <v>100.2</v>
-      </c>
-      <c r="G41" s="12" t="n">
-        <v>115274.5</v>
-      </c>
-      <c r="H41" s="12" t="n">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B42" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/27 06:33:04</t>
-        </is>
-      </c>
-      <c r="D42" s="15" t="inlineStr">
-        <is>
-          <t>-33.004069,-71.328408</t>
-        </is>
-      </c>
-      <c r="E42" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F42" s="12" t="n">
-        <v>88.7</v>
-      </c>
-      <c r="G42" s="12" t="n">
-        <v>115276.1</v>
-      </c>
-      <c r="H42" s="12" t="n">
-        <v>96.59999999999999</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B43" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/27 06:43:04</t>
-        </is>
-      </c>
-      <c r="D43" s="15" t="inlineStr">
-        <is>
-          <t>-32.911064,-71.269813</t>
-        </is>
-      </c>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F43" s="12" t="n">
-        <v>100.4</v>
-      </c>
-      <c r="G43" s="12" t="n">
-        <v>115289.1</v>
-      </c>
-      <c r="H43" s="12" t="n">
-        <v>96.90000000000001</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B44" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C44" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/27 06:44:04</t>
-        </is>
-      </c>
-      <c r="D44" s="15" t="inlineStr">
-        <is>
-          <t>-32.903617,-71.254498</t>
-        </is>
-      </c>
-      <c r="E44" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F44" s="12" t="n">
-        <v>96.2</v>
-      </c>
-      <c r="G44" s="12" t="n">
-        <v>115290.8</v>
-      </c>
-      <c r="H44" s="12" t="n">
-        <v>105.4</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B45" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/27 07:46:04</t>
-        </is>
-      </c>
-      <c r="D45" s="15" t="inlineStr">
-        <is>
-          <t>-32.572429,-71.289271</t>
-        </is>
-      </c>
-      <c r="E45" s="12" t="inlineStr">
-        <is>
-          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
-        </is>
-      </c>
-      <c r="F45" s="12" t="n">
-        <v>101.5</v>
-      </c>
-      <c r="G45" s="12" t="n">
-        <v>115358.6</v>
-      </c>
-      <c r="H45" s="12" t="n">
-        <v>82.5</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B46" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="C46" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/27 07:47:04</t>
-        </is>
-      </c>
-      <c r="D46" s="15" t="inlineStr">
-        <is>
-          <t>-32.569254,-71.276721</t>
-        </is>
-      </c>
-      <c r="E46" s="12" t="inlineStr">
-        <is>
-          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
-        </is>
-      </c>
-      <c r="F46" s="12" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="G46" s="12" t="n">
-        <v>115359.8</v>
-      </c>
-      <c r="H46" s="12" t="n">
-        <v>96.3</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B47" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="C47" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/27 07:50:04</t>
-        </is>
-      </c>
-      <c r="D47" s="15" t="inlineStr">
-        <is>
-          <t>-32.549855,-71.268268</t>
-        </is>
-      </c>
-      <c r="E47" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F47" s="12" t="n">
-        <v>103.1</v>
-      </c>
-      <c r="G47" s="12" t="n">
-        <v>115363.5</v>
-      </c>
-      <c r="H47" s="12" t="n">
-        <v>107.9</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B48" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="C48" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/27 07:51:04</t>
-        </is>
-      </c>
-      <c r="D48" s="15" t="inlineStr">
-        <is>
-          <t>-32.534791,-71.264781</t>
-        </is>
-      </c>
-      <c r="E48" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F48" s="12" t="n">
-        <v>102</v>
-      </c>
-      <c r="G48" s="12" t="n">
-        <v>115365.2</v>
-      </c>
-      <c r="H48" s="12" t="n">
-        <v>114.7</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B49" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="C49" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/27 07:52:04</t>
-        </is>
-      </c>
-      <c r="D49" s="15" t="inlineStr">
-        <is>
-          <t>-32.519725,-71.261213</t>
-        </is>
-      </c>
-      <c r="E49" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F49" s="12" t="n">
-        <v>100.7</v>
-      </c>
-      <c r="G49" s="12" t="n">
-        <v>115366.9</v>
-      </c>
-      <c r="H49" s="12" t="n">
-        <v>101.1</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B50" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="C50" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/27 07:53:04</t>
-        </is>
-      </c>
-      <c r="D50" s="15" t="inlineStr">
-        <is>
-          <t>-32.506255,-71.259684</t>
-        </is>
-      </c>
-      <c r="E50" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F50" s="12" t="n">
-        <v>89.3</v>
-      </c>
-      <c r="G50" s="12" t="n">
-        <v>115368.4</v>
-      </c>
-      <c r="H50" s="12" t="n">
-        <v>77.7</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B51" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="C51" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/31 19:07:11</t>
-        </is>
-      </c>
-      <c r="D51" s="15" t="inlineStr">
-        <is>
-          <t>-32.870929,-71.229809</t>
-        </is>
-      </c>
-      <c r="E51" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F51" s="12" t="n">
-        <v>101.9</v>
-      </c>
-      <c r="G51" s="12" t="n">
-        <v>116983.2</v>
-      </c>
-      <c r="H51" s="12" t="n">
-        <v>126.4</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B52" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="C52" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/31 19:08:11</t>
-        </is>
-      </c>
-      <c r="D52" s="15" t="inlineStr">
-        <is>
-          <t>-32.885976,-71.232073</t>
-        </is>
-      </c>
-      <c r="E52" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F52" s="12" t="n">
-        <v>102.4</v>
-      </c>
-      <c r="G52" s="12" t="n">
-        <v>116984.9</v>
-      </c>
-      <c r="H52" s="12" t="n">
-        <v>117.9</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B53" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="C53" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/31 19:09:11</t>
-        </is>
-      </c>
-      <c r="D53" s="15" t="inlineStr">
-        <is>
-          <t>-32.898972,-71.239656</t>
-        </is>
-      </c>
-      <c r="E53" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F53" s="12" t="n">
-        <v>97.40000000000001</v>
-      </c>
-      <c r="G53" s="12" t="n">
-        <v>116986.6</v>
-      </c>
-      <c r="H53" s="12" t="n">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B54" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="C54" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/31 19:10:11</t>
-        </is>
-      </c>
-      <c r="D54" s="15" t="inlineStr">
-        <is>
-          <t>-32.904194,-71.25627</t>
-        </is>
-      </c>
-      <c r="E54" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F54" s="12" t="n">
-        <v>100.9</v>
-      </c>
-      <c r="G54" s="12" t="n">
-        <v>116988.3</v>
-      </c>
-      <c r="H54" s="12" t="n">
-        <v>100.9</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B55" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="C55" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/31 19:11:11</t>
-        </is>
-      </c>
-      <c r="D55" s="15" t="inlineStr">
-        <is>
-          <t>-32.912396,-71.271115</t>
-        </is>
-      </c>
-      <c r="E55" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F55" s="12" t="n">
-        <v>102.5</v>
-      </c>
-      <c r="G55" s="12" t="n">
-        <v>116990</v>
-      </c>
-      <c r="H55" s="12" t="n">
-        <v>91.09999999999999</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B56" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="C56" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/31 19:12:11</t>
-        </is>
-      </c>
-      <c r="D56" s="15" t="inlineStr">
-        <is>
-          <t>-32.924905,-71.281892</t>
-        </is>
-      </c>
-      <c r="E56" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F56" s="12" t="n">
-        <v>100.7</v>
-      </c>
-      <c r="G56" s="12" t="n">
-        <v>116991.7</v>
-      </c>
-      <c r="H56" s="12" t="n">
-        <v>81.3</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B57" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="C57" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/31 19:12:55</t>
-        </is>
-      </c>
-      <c r="D57" s="15" t="inlineStr">
-        <is>
-          <t>-32.933783,-71.288593</t>
-        </is>
-      </c>
-      <c r="E57" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
-        </is>
-      </c>
-      <c r="F57" s="12" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="G57" s="12" t="n">
-        <v>116992.9</v>
-      </c>
-      <c r="H57" s="12" t="n">
-        <v>76.90000000000001</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PCRF-25 TERRENO</t>
-        </is>
-      </c>
-      <c r="B58" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C58" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/31 14:57:40</t>
-        </is>
-      </c>
-      <c r="D58" s="15" t="inlineStr">
-        <is>
-          <t>-32.577562,-71.309168</t>
-        </is>
-      </c>
-      <c r="E58" s="12" t="inlineStr">
-        <is>
-          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
-        </is>
-      </c>
-      <c r="F58" s="12" t="n">
-        <v>100.4</v>
-      </c>
-      <c r="G58" s="12" t="n">
-        <v>90949.10000000001</v>
-      </c>
-      <c r="H58" s="12" t="n">
-        <v>67.5</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PCRF-25 TERRENO</t>
-        </is>
-      </c>
-      <c r="B59" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C59" s="12" t="inlineStr">
-        <is>
-          <t>2026/07/31 14:58:40</t>
-        </is>
-      </c>
-      <c r="D59" s="15" t="inlineStr">
-        <is>
-          <t>-32.583363,-71.323384</t>
-        </is>
-      </c>
-      <c r="E59" s="12" t="inlineStr">
-        <is>
-          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
-        </is>
-      </c>
-      <c r="F59" s="12" t="n">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="G59" s="12" t="n">
-        <v>90950.60000000001</v>
-      </c>
-      <c r="H59" s="12" t="n">
-        <v>66.90000000000001</v>
+        <v>110.3</v>
       </c>
     </row>
   </sheetData>
@@ -9898,35 +11014,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId54"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="default" paperSize="1" scale="100" pageOrder="downThenOver" blackAndWhite="0" draft="0" errors="displayed"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId55"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId32"/>
   </tableParts>
 </worksheet>
 </file>
--- a/INFORME EXCESOS DE VELOCIDAD.xlsx
+++ b/INFORME EXCESOS DE VELOCIDAD.xlsx
@@ -222,8 +222,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SpeedingFleetsSummaryTable_1" displayName="SpeedingFleetsSummaryTable_1" ref="A5:I11" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A5:I11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SpeedingFleetsSummaryTable_1" displayName="SpeedingFleetsSummaryTable_1" ref="A5:I14" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A5:I14"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Alias"/>
     <tableColumn id="2" name="Excesos" dataDxfId="0"/>
@@ -240,8 +240,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SpeedingFleetsDetailTable_1" displayName="SpeedingFleetsDetailTable_1" ref="A5:O20" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A5:O20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SpeedingFleetsDetailTable_1" displayName="SpeedingFleetsDetailTable_1" ref="A5:O39" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A5:O39"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Alias"/>
     <tableColumn id="2" name="Conductor"/>
@@ -264,8 +264,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SpeedingFleetsDataTable_1" displayName="SpeedingFleetsDataTable_1" ref="A5:H36" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A5:H36"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SpeedingFleetsDataTable_1" displayName="SpeedingFleetsDataTable_1" ref="A5:H78" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A5:H78"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Alias"/>
     <tableColumn id="2" name="Secuencial" dataDxfId="0"/>
@@ -569,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.710625" customWidth="1" style="7" min="1" max="1"/>
@@ -593,7 +593,7 @@
     <row r="3" ht="25" customHeight="1" s="8">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Desde : 2026/07/13 00:00:00 Hasta: 2026/08/14 23:59:59</t>
+          <t>Desde : 2026/07/13 00:00:00 Hasta: 2026/08/23 23:59:59</t>
         </is>
       </c>
     </row>
@@ -647,26 +647,26 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>GLP SSZD-71  J VALLEJOS</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>0.001840277777777778</v>
+        <v>0.004606481481481481</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>0.0006134259259259259</v>
+        <v>0.0006580671296296296</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>4.1</v>
+        <v>10.7</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>104.6</v>
+        <v>103.6</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>102.2</v>
+        <v>101</v>
       </c>
       <c r="H6" s="12" t="n">
         <v>0</v>
@@ -678,26 +678,26 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>GV TDLD-98 J PACHECHO</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>0.002777777777777778</v>
+        <v>0.003784722222222222</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>0.0006944444444444445</v>
+        <v>0.000630787037037037</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>103.5</v>
+        <v>109.5</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>102.2</v>
+        <v>106.9</v>
       </c>
       <c r="H7" s="12" t="n">
         <v>0</v>
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>0.001388888888888889</v>
+        <v>0.003483796296296296</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>0.0006944444444444445</v>
+        <v>0.0006967592592592593</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>3</v>
+        <v>8.1</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>101.5</v>
+        <v>103.4</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>101</v>
+        <v>102.3</v>
       </c>
       <c r="H8" s="12" t="n">
         <v>0</v>
@@ -740,26 +740,26 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>GV TM5 RXXG-15 E CABANILLA</t>
+          <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>0.001388888888888889</v>
+        <v>3.472222222222222e-05</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>0.0006944444444444445</v>
+        <v>3.472222222222222e-05</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>102.8</v>
+        <v>104.6</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>102.6</v>
+        <v>104.6</v>
       </c>
       <c r="H9" s="12" t="n">
         <v>0</v>
@@ -771,26 +771,26 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>GC TSVS-89 M AEDO</t>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>0.002650462962962963</v>
+        <v>0.001145833333333333</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>0.0008834837962962963</v>
+        <v>0.0005729166666666667</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>5.8</v>
+        <v>2.6</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>103.7</v>
+        <v>100.6</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>101.8</v>
+        <v>100.4</v>
       </c>
       <c r="H10" s="12" t="n">
         <v>0</v>
@@ -802,31 +802,124 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
+          <t>GLP SKDX-44 V VIAL</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>0.00306712962962963</v>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>0.001533564814814815</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>0.001400462962962963</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>0.0007002314814814815</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
           <t>JAC  LYTS-17 G GALEA</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B13" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="13" t="n">
-        <v>0.0006944444444444445</v>
-      </c>
-      <c r="D11" s="13" t="n">
-        <v>0.0006944444444444445</v>
-      </c>
-      <c r="E11" s="12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F11" s="12" t="n">
-        <v>101.1</v>
-      </c>
-      <c r="G11" s="12" t="n">
-        <v>101.1</v>
-      </c>
-      <c r="H11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="12" t="n">
+      <c r="C13" s="13" t="n">
+        <v>0.0004398148148148148</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>0.0004398148148148148</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>0.0053125</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>0.0006640625</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="H14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -851,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O157"/>
+  <dimension ref="A1:O221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.710625" customWidth="1" style="7" min="1" max="1"/>
@@ -879,7 +972,7 @@
     <row r="3" ht="25" customHeight="1" s="8">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Desde : 2026/08/03 00:00:00 Hasta: 2026/08/09 23:59:58</t>
+          <t>Desde : 2026/08/10 00:00:00 Hasta: 2026/08/16 23:59:58</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7922,6 @@
           <t>GV SHLC-74 B MIRANDA</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr"/>
       <c r="C124" t="n">
         <v>1</v>
       </c>
@@ -7888,7 +7980,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr"/>
       <c r="C125" t="n">
         <v>1</v>
       </c>
@@ -7947,7 +8038,6 @@
           <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr"/>
       <c r="C126" t="n">
         <v>1</v>
       </c>
@@ -8006,7 +8096,6 @@
           <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr"/>
       <c r="C127" t="n">
         <v>1</v>
       </c>
@@ -8065,7 +8154,6 @@
           <t>GV SHLC-74 B MIRANDA</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr"/>
       <c r="C128" t="n">
         <v>2</v>
       </c>
@@ -8124,7 +8212,6 @@
           <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr"/>
       <c r="C129" t="n">
         <v>2</v>
       </c>
@@ -8183,7 +8270,6 @@
           <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr"/>
       <c r="C130" t="n">
         <v>3</v>
       </c>
@@ -8242,7 +8328,6 @@
           <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr"/>
       <c r="C131" t="n">
         <v>1</v>
       </c>
@@ -8301,7 +8386,6 @@
           <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr"/>
       <c r="C132" t="n">
         <v>1</v>
       </c>
@@ -8360,7 +8444,6 @@
           <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr"/>
       <c r="C133" t="n">
         <v>2</v>
       </c>
@@ -8419,7 +8502,6 @@
           <t>GV SHLC-74 B MIRANDA</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr"/>
       <c r="C134" t="n">
         <v>3</v>
       </c>
@@ -8478,7 +8560,6 @@
           <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr"/>
       <c r="C135" t="n">
         <v>3</v>
       </c>
@@ -8537,7 +8618,6 @@
           <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr"/>
       <c r="C136" t="n">
         <v>2</v>
       </c>
@@ -8596,7 +8676,6 @@
           <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr"/>
       <c r="C137" t="n">
         <v>4</v>
       </c>
@@ -8655,7 +8734,6 @@
           <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr"/>
       <c r="C138" t="n">
         <v>5</v>
       </c>
@@ -8714,7 +8792,6 @@
           <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr"/>
       <c r="C139" t="n">
         <v>4</v>
       </c>
@@ -8773,7 +8850,6 @@
           <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr"/>
       <c r="C140" t="n">
         <v>5</v>
       </c>
@@ -8832,7 +8908,6 @@
           <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr"/>
       <c r="C141" t="n">
         <v>6</v>
       </c>
@@ -8891,7 +8966,6 @@
           <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr"/>
       <c r="C142" t="n">
         <v>7</v>
       </c>
@@ -8950,7 +9024,6 @@
           <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr"/>
       <c r="C143" t="n">
         <v>1</v>
       </c>
@@ -9009,7 +9082,6 @@
           <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr"/>
       <c r="C144" t="n">
         <v>2</v>
       </c>
@@ -9068,7 +9140,6 @@
           <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr"/>
       <c r="C145" t="n">
         <v>8</v>
       </c>
@@ -9127,7 +9198,6 @@
           <t>GV SHLC-74 B MIRANDA</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr"/>
       <c r="C146" t="n">
         <v>4</v>
       </c>
@@ -9186,7 +9256,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr"/>
       <c r="C147" t="n">
         <v>2</v>
       </c>
@@ -9245,7 +9314,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr"/>
       <c r="C148" t="n">
         <v>3</v>
       </c>
@@ -9304,7 +9372,6 @@
           <t>JAC  LYTS-17 G GALEA</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr"/>
       <c r="C149" t="n">
         <v>1</v>
       </c>
@@ -9363,7 +9430,6 @@
           <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr"/>
       <c r="C150" t="n">
         <v>6</v>
       </c>
@@ -9422,7 +9488,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr"/>
       <c r="C151" t="n">
         <v>4</v>
       </c>
@@ -9481,7 +9546,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr"/>
       <c r="C152" t="n">
         <v>5</v>
       </c>
@@ -9540,7 +9604,6 @@
           <t>GV SHLC-74 B MIRANDA</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr"/>
       <c r="C153" t="n">
         <v>5</v>
       </c>
@@ -9599,7 +9662,6 @@
           <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr"/>
       <c r="C154" t="n">
         <v>7</v>
       </c>
@@ -9658,7 +9720,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr"/>
       <c r="C155" t="n">
         <v>6</v>
       </c>
@@ -9717,7 +9778,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr"/>
       <c r="C156" t="n">
         <v>1</v>
       </c>
@@ -9776,7 +9836,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr"/>
       <c r="C157" t="n">
         <v>2</v>
       </c>
@@ -9826,6 +9885,3786 @@
         <v>0</v>
       </c>
       <c r="O157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="n">
+        <v>1</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026/08/17 18:14:01</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>-33.160176,-71.544064</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>2026/08/17 18:15:01</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>-33.151717,-71.557304</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J158" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K158" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L158" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="M158" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="N158" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
+      <c r="C159" t="n">
+        <v>2</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026/08/17 18:33:01</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>-33.055411,-71.52942</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>2026/08/17 18:33:12</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>-33.053064,-71.52918</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="J159" s="14" t="n">
+        <v>0.0001273148148148148</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L159" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="M159" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="N159" t="n">
+        <v>0</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
+      <c r="C160" t="n">
+        <v>1</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2026/08/18 07:49:01</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>-32.530144,-70.815085</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>2026/08/18 07:49:20</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>-32.532986,-70.818559</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Ruta E-411, Putaendo, San Felipe, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J160" s="14" t="n">
+        <v>0.0002199074074074074</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L160" t="n">
+        <v>101</v>
+      </c>
+      <c r="M160" t="n">
+        <v>101</v>
+      </c>
+      <c r="N160" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
+      <c r="C161" t="n">
+        <v>2</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2026/08/19 07:05:09</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>-32.821743,-71.222786</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Ruta E-411, Putaendo, San Felipe, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>2026/08/19 07:06:09</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>-32.807764,-71.219789</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J161" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K161" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L161" t="n">
+        <v>101</v>
+      </c>
+      <c r="M161" t="n">
+        <v>101</v>
+      </c>
+      <c r="N161" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
+      <c r="C162" t="n">
+        <v>3</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2026/08/19 07:11:09</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>-32.782806,-71.174599</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>2026/08/19 07:14:09</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>-32.744809,-71.19742</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J162" s="14" t="n">
+        <v>0.002083333333333333</v>
+      </c>
+      <c r="K162" t="n">
+        <v>5</v>
+      </c>
+      <c r="L162" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="M162" t="n">
+        <v>101</v>
+      </c>
+      <c r="N162" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
+      <c r="C163" t="n">
+        <v>4</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2026/08/19 07:16:09</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>-32.71589,-71.204527</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>2026/08/19 07:17:09</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>-32.701007,-71.206654</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J163" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K163" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L163" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="M163" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="N163" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
+      <c r="C164" t="n">
+        <v>5</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2026/08/19 07:18:09</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>-32.686246,-71.209765</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>2026/08/19 07:19:09</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>-32.671547,-71.213168</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>s/n, Nogales, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J164" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K164" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L164" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="M164" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="N164" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" t="n">
+        <v>6</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2026/08/19 07:21:49</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>-32.635806,-71.232128</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>s/n, Nogales, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>2026/08/19 07:25:09</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>-32.589536,-71.245251</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J165" s="14" t="n">
+        <v>0.002314814814814815</v>
+      </c>
+      <c r="K165" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L165" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="M165" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="N165" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
+      <c r="C166" t="n">
+        <v>7</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2026/08/19 07:26:09</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>-32.577264,-71.255286</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>2026/08/19 07:28:09</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>-32.549474,-71.268194</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J166" s="14" t="n">
+        <v>0.001388888888888889</v>
+      </c>
+      <c r="K166" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L166" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="M166" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="N166" t="n">
+        <v>0</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="n">
+        <v>8</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2026/08/20 07:07:09</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>-32.799799,-71.206358</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>2026/08/20 07:08:10</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>-32.791891,-71.191591</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Calera, Quillota, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="J167" s="14" t="n">
+        <v>0.0007060185185185185</v>
+      </c>
+      <c r="K167" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L167" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="M167" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="N167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+      <c r="C168" t="n">
+        <v>9</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2026/08/20 07:11:10</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>-32.781931,-71.175729</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Calera, Quillota, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>2026/08/20 07:13:10</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>-32.758091,-71.19483</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J168" s="14" t="n">
+        <v>0.001388888888888889</v>
+      </c>
+      <c r="K168" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L168" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="M168" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="N168" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
+      <c r="C169" t="n">
+        <v>10</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2026/08/20 07:20:09</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>-32.657495,-71.220065</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>2026/08/20 07:21:10</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>-32.644382,-71.229461</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J169" s="14" t="n">
+        <v>0.0007060185185185185</v>
+      </c>
+      <c r="K169" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L169" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="M169" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="N169" t="n">
+        <v>0</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
+      <c r="C170" t="n">
+        <v>11</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2026/08/20 07:22:10</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>-32.630176,-71.230736</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>2026/08/20 07:24:12</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>-32.616292,-71.229904</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J170" s="14" t="n">
+        <v>0.001412037037037037</v>
+      </c>
+      <c r="K170" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L170" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="M170" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="N170" t="n">
+        <v>0</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
+      <c r="C171" t="n">
+        <v>12</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2026/08/20 07:25:10</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>-32.588579,-71.245847</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>2026/08/20 07:32:09</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>-32.488665,-71.258352</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>s/n, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J171" s="14" t="n">
+        <v>0.004849537037037037</v>
+      </c>
+      <c r="K171" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="L171" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="M171" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="N171" t="n">
+        <v>0</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
+      <c r="C172" t="n">
+        <v>1</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2026/08/20 09:01:07</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>-32.931996,-71.478943</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>2026/08/20 09:01:23</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>-32.935124,-71.481164</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Ruta 64, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="J172" s="14" t="n">
+        <v>0.0001851851851851852</v>
+      </c>
+      <c r="K172" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L172" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="M172" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="N172" t="n">
+        <v>0</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>GV TDLD-98 J PACHECHO</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" t="n">
+        <v>1</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2026/08/20 09:01:12</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>-33.142737,-71.561705</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>2026/08/20 09:02:12</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>-33.129457,-71.561884</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J173" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K173" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L173" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="M173" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="N173" t="n">
+        <v>0</v>
+      </c>
+      <c r="O173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>GV TDLD-98 J PACHECHO</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
+      <c r="C174" t="n">
+        <v>2</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2026/08/20 09:19:12</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>-33.008772,-71.505475</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>2026/08/20 09:19:44</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>-33.002592,-71.510204</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Avenida Carlos Ibáñez del Campo, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="J174" s="14" t="n">
+        <v>0.0003703703703703704</v>
+      </c>
+      <c r="K174" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L174" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="M174" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="N174" t="n">
+        <v>0</v>
+      </c>
+      <c r="O174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>GV TDLD-98 J PACHECHO</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
+      <c r="C175" t="n">
+        <v>3</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2026/08/20 09:38:50</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>-32.951473,-71.509554</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Avenida Carlos Ibáñez del Campo, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>2026/08/20 09:39:49</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>-32.937746,-71.51403</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="J175" s="14" t="n">
+        <v>0.0006828703703703704</v>
+      </c>
+      <c r="K175" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L175" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="M175" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="N175" t="n">
+        <v>0</v>
+      </c>
+      <c r="O175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr"/>
+      <c r="C176" t="n">
+        <v>2</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2026/08/20 10:50:54</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>-33.352393,-71.375785</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Ruta 64, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>2026/08/20 10:51:54</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>-33.342378,-71.363904</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Ruta F-90-G, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="J176" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K176" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L176" t="n">
+        <v>117</v>
+      </c>
+      <c r="M176" t="n">
+        <v>117</v>
+      </c>
+      <c r="N176" t="n">
+        <v>0</v>
+      </c>
+      <c r="O176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr"/>
+      <c r="C177" t="n">
+        <v>3</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2026/08/20 10:52:54</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>-33.337902,-71.372132</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Ruta F-90-G, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>2026/08/20 10:53:55</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>-33.331425,-71.386417</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J177" s="14" t="n">
+        <v>0.0007060185185185185</v>
+      </c>
+      <c r="K177" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L177" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="M177" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="N177" t="n">
+        <v>0</v>
+      </c>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr"/>
+      <c r="C178" t="n">
+        <v>4</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2026/08/20 10:54:54</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>-33.319175,-71.396951</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>2026/08/20 10:55:54</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>-33.307794,-71.40857</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>s/n, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J178" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K178" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L178" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="M178" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="N178" t="n">
+        <v>0</v>
+      </c>
+      <c r="O178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr"/>
+      <c r="C179" t="n">
+        <v>5</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2026/08/20 10:57:54</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>-33.283395,-71.411513</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>s/n, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>2026/08/20 10:58:13</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>-33.279461,-71.413734</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Ruta F-852, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J179" s="14" t="n">
+        <v>0.0002199074074074074</v>
+      </c>
+      <c r="K179" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L179" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="M179" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="N179" t="n">
+        <v>0</v>
+      </c>
+      <c r="O179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" t="n">
+        <v>6</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2026/08/20 10:58:56</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>-33.275198,-71.4257</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Ruta F-852, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>2026/08/20 10:59:27</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>-33.268717,-71.430666</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Ruta F-852, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J180" s="14" t="n">
+        <v>0.0003587962962962963</v>
+      </c>
+      <c r="K180" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L180" t="n">
+        <v>121.7</v>
+      </c>
+      <c r="M180" t="n">
+        <v>121.7</v>
+      </c>
+      <c r="N180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr"/>
+      <c r="C181" t="n">
+        <v>7</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2026/08/20 11:42:35</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>-33.286247,-71.411266</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Ruta F-852, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>2026/08/20 11:43:35</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>-33.30091,-71.41017</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Ruta F-852, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J181" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K181" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L181" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="M181" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="N181" t="n">
+        <v>0</v>
+      </c>
+      <c r="O181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
+      <c r="C182" t="n">
+        <v>8</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2026/08/20 11:53:35</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>-33.327825,-71.394773</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Ruta F-852, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>2026/08/20 11:54:16</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>-33.325557,-71.400218</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Melipilla, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J182" s="14" t="n">
+        <v>0.000474537037037037</v>
+      </c>
+      <c r="K182" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L182" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="M182" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="N182" t="n">
+        <v>0</v>
+      </c>
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="n">
+        <v>9</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2026/08/20 11:59:36</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>-33.376217,-71.386345</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Melipilla, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>2026/08/20 12:00:36</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>-33.389996,-71.395401</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Ruta F-74-G, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="J183" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K183" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L183" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="M183" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="N183" t="n">
+        <v>0</v>
+      </c>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
+      <c r="C184" t="n">
+        <v>3</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2026/08/20 14:29:14</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>-33.346943,-71.351958</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>2026/08/20 14:30:14</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>-33.340219,-71.367006</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J184" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K184" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L184" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="M184" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="N184" t="n">
+        <v>0</v>
+      </c>
+      <c r="O184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>GV TDLD-98 J PACHECHO</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr"/>
+      <c r="C185" t="n">
+        <v>4</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2026/08/20 16:37:34</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>-33.169294,-71.526495</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>2026/08/20 16:38:34</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>-33.176611,-71.51215</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J185" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K185" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L185" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="M185" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="N185" t="n">
+        <v>0</v>
+      </c>
+      <c r="O185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr"/>
+      <c r="C186" t="n">
+        <v>13</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2026/08/20 16:56:33</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>-32.454363,-71.100068</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>s/n, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>2026/08/20 16:57:33</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>-32.461252,-71.106287</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Ruta E-35, Cabildo, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J186" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K186" t="n">
+        <v>1</v>
+      </c>
+      <c r="L186" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="M186" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="N186" t="n">
+        <v>0</v>
+      </c>
+      <c r="O186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
+      <c r="C187" t="n">
+        <v>14</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2026/08/21 07:05:04</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>-32.817143,-71.223555</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Ruta E-35, Cabildo, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>2026/08/21 07:05:59</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>-32.804745,-71.217531</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J187" s="14" t="n">
+        <v>0.0006365740740740741</v>
+      </c>
+      <c r="K187" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L187" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="M187" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="N187" t="n">
+        <v>0</v>
+      </c>
+      <c r="O187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
+      <c r="C188" t="n">
+        <v>15</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2026/08/21 07:07:05</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>-32.797402,-71.200269</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>2026/08/21 07:08:01</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>-32.79047,-71.188293</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Calera, Quillota, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="J188" s="14" t="n">
+        <v>0.0006481481481481481</v>
+      </c>
+      <c r="K188" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L188" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="M188" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="N188" t="n">
+        <v>0</v>
+      </c>
+      <c r="O188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
+      <c r="C189" t="n">
+        <v>16</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2026/08/21 07:12:04</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>-32.76685,-71.193175</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Calera, Quillota, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>2026/08/21 07:15:05</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>-32.722409,-71.203591</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J189" s="14" t="n">
+        <v>0.002094907407407407</v>
+      </c>
+      <c r="K189" t="n">
+        <v>5</v>
+      </c>
+      <c r="L189" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="M189" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="N189" t="n">
+        <v>0</v>
+      </c>
+      <c r="O189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr"/>
+      <c r="C190" t="n">
+        <v>17</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2026/08/21 07:16:04</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>-32.707723,-71.205703</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>2026/08/21 07:18:04</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>-32.678094,-71.211653</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J190" s="14" t="n">
+        <v>0.001388888888888889</v>
+      </c>
+      <c r="K190" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L190" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="M190" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="N190" t="n">
+        <v>0</v>
+      </c>
+      <c r="O190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr"/>
+      <c r="C191" t="n">
+        <v>18</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2026/08/21 07:22:23</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>-32.617989,-71.229113</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>2026/08/21 07:26:04</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>-32.571113,-71.257823</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J191" s="14" t="n">
+        <v>0.002557870370370371</v>
+      </c>
+      <c r="K191" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="L191" t="n">
+        <v>101</v>
+      </c>
+      <c r="M191" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="N191" t="n">
+        <v>0</v>
+      </c>
+      <c r="O191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
+      <c r="C192" t="n">
+        <v>19</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2026/08/21 07:30:04</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>-32.513499,-71.260158</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2026/08/21 07:31:04</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>-32.499411,-71.259165</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J192" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K192" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L192" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="M192" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="N192" t="n">
+        <v>0</v>
+      </c>
+      <c r="O192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr"/>
+      <c r="C193" t="n">
+        <v>4</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2026/08/21 08:09:13</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>-33.223211,-71.469875</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>2026/08/21 08:10:13</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>-33.235583,-71.460825</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J193" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K193" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L193" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="M193" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="N193" t="n">
+        <v>0</v>
+      </c>
+      <c r="O193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr"/>
+      <c r="C194" t="n">
+        <v>20</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2026/08/21 10:51:46</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>-32.509631,-71.260064</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>2026/08/21 10:54:46</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>-32.553877,-71.266773</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J194" s="14" t="n">
+        <v>0.002083333333333333</v>
+      </c>
+      <c r="K194" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L194" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="M194" t="n">
+        <v>101</v>
+      </c>
+      <c r="N194" t="n">
+        <v>0</v>
+      </c>
+      <c r="O194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr"/>
+      <c r="C195" t="n">
+        <v>21</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2026/08/21 10:55:46</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>-32.567495,-71.25956</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>2026/08/21 10:57:42</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>-32.592534,-71.243801</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="J195" s="14" t="n">
+        <v>0.001342592592592592</v>
+      </c>
+      <c r="K195" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L195" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="M195" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="N195" t="n">
+        <v>0</v>
+      </c>
+      <c r="O195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr"/>
+      <c r="C196" t="n">
+        <v>22</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:01:46</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>-32.630672,-71.230994</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:02:46</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>-32.645001,-71.22917</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J196" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K196" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L196" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="M196" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="N196" t="n">
+        <v>0</v>
+      </c>
+      <c r="O196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr"/>
+      <c r="C197" t="n">
+        <v>23</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:03:46</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>-32.657987,-71.219943</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:03:46</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>-32.657987,-71.219943</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J197" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L197" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="M197" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="N197" t="n">
+        <v>0</v>
+      </c>
+      <c r="O197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr"/>
+      <c r="C198" t="n">
+        <v>24</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:04:46</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>-32.672,-71.213217</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:04:46</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>-32.672,-71.213217</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J198" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L198" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="M198" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="N198" t="n">
+        <v>0</v>
+      </c>
+      <c r="O198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr"/>
+      <c r="C199" t="n">
+        <v>25</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:05:46</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>-32.686857,-71.209718</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:06:46</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>-32.701804,-71.206652</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J199" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K199" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L199" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="M199" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="N199" t="n">
+        <v>0</v>
+      </c>
+      <c r="O199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr"/>
+      <c r="C200" t="n">
+        <v>26</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:07:46</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>-32.716872,-71.204538</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:08:45</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>-32.731461,-71.20107</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J200" s="14" t="n">
+        <v>0.0006828703703703704</v>
+      </c>
+      <c r="K200" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L200" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="M200" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="N200" t="n">
+        <v>0</v>
+      </c>
+      <c r="O200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="n">
+        <v>27</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:09:46</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>-32.746504,-71.197175</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:11:46</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>-32.771829,-71.189922</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>s/n, Calera, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J201" s="14" t="n">
+        <v>0.001388888888888889</v>
+      </c>
+      <c r="K201" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L201" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="M201" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="N201" t="n">
+        <v>0</v>
+      </c>
+      <c r="O201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="n">
+        <v>28</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:28:46</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>-32.799702,-71.206422</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>s/n, Calera, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:30:46</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>-32.822655,-71.223108</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="J202" s="14" t="n">
+        <v>0.001388888888888889</v>
+      </c>
+      <c r="K202" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L202" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="M202" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="N202" t="n">
+        <v>0</v>
+      </c>
+      <c r="O202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="n">
+        <v>29</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:31:46</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>-32.836586,-71.221254</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:32:45</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>-32.851149,-71.224474</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J203" s="14" t="n">
+        <v>0.0006828703703703704</v>
+      </c>
+      <c r="K203" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L203" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="M203" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="N203" t="n">
+        <v>0</v>
+      </c>
+      <c r="O203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="n">
+        <v>30</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:33:46</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>-32.866108,-71.22795</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:35:46</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>-32.895297,-71.235293</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J204" s="14" t="n">
+        <v>0.001388888888888889</v>
+      </c>
+      <c r="K204" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L204" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="M204" t="n">
+        <v>101</v>
+      </c>
+      <c r="N204" t="n">
+        <v>0</v>
+      </c>
+      <c r="O204" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="n">
+        <v>31</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:36:46</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>-32.902265,-71.250674</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:39:46</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>-32.932324,-71.288644</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J205" s="14" t="n">
+        <v>0.002083333333333333</v>
+      </c>
+      <c r="K205" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L205" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="M205" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="N205" t="n">
+        <v>0</v>
+      </c>
+      <c r="O205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="n">
+        <v>32</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:42:46</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>-32.962176,-71.288986</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:43:46</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>-32.971848,-71.301426</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J206" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K206" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L206" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="M206" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="N206" t="n">
+        <v>0</v>
+      </c>
+      <c r="O206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="n">
+        <v>33</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:44:34</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>-32.981189,-71.309935</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:44:46</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>-32.981819,-71.313399</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J207" s="14" t="n">
+        <v>0.0001388888888888889</v>
+      </c>
+      <c r="K207" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L207" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="M207" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="N207" t="n">
+        <v>0</v>
+      </c>
+      <c r="O207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr"/>
+      <c r="C208" t="n">
+        <v>34</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:45:04</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>-32.983966,-71.317872</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:45:46</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-32.990023,-71.327423</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J208" s="14" t="n">
+        <v>0.0004861111111111111</v>
+      </c>
+      <c r="K208" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L208" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="M208" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="N208" t="n">
+        <v>0</v>
+      </c>
+      <c r="O208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr"/>
+      <c r="C209" t="n">
+        <v>35</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:46:46</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>-33.004446,-71.328509</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:48:46</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>-33.032106,-71.31984</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J209" s="14" t="n">
+        <v>0.001388888888888889</v>
+      </c>
+      <c r="K209" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L209" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="M209" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="N209" t="n">
+        <v>0</v>
+      </c>
+      <c r="O209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr"/>
+      <c r="C210" t="n">
+        <v>36</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:49:29</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>-33.04256,-71.319453</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:49:46</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>-33.044888,-71.323532</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="J210" s="14" t="n">
+        <v>0.0001967592592592593</v>
+      </c>
+      <c r="K210" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L210" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="M210" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="N210" t="n">
+        <v>0</v>
+      </c>
+      <c r="O210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr"/>
+      <c r="C211" t="n">
+        <v>37</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:52:33</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>-33.069343,-71.362224</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:52:46</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>-33.069099,-71.366073</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J211" s="14" t="n">
+        <v>0.000150462962962963</v>
+      </c>
+      <c r="K211" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L211" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="M211" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="N211" t="n">
+        <v>0</v>
+      </c>
+      <c r="O211" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr"/>
+      <c r="C212" t="n">
+        <v>38</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:53:46</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>-33.067592,-71.383795</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:58:17</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>-33.061032,-71.463302</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Quilpué, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J212" s="14" t="n">
+        <v>0.003136574074074074</v>
+      </c>
+      <c r="K212" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L212" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="M212" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="N212" t="n">
+        <v>0</v>
+      </c>
+      <c r="O212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr"/>
+      <c r="C213" t="n">
+        <v>39</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:59:46</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>-33.061569,-71.486547</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Quilpué, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>2026/08/21 12:00:46</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>-33.05298,-71.497836</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J213" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K213" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L213" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="M213" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="N213" t="n">
+        <v>0</v>
+      </c>
+      <c r="O213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr"/>
+      <c r="C214" t="n">
+        <v>1</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2026/08/21 14:35:29</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>-33.064528,-71.642204</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>2026/08/21 14:35:37</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>-33.066337,-71.642205</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="J214" s="14" t="n">
+        <v>9.259259259259259e-05</v>
+      </c>
+      <c r="K214" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L214" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="M214" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="N214" t="n">
+        <v>0</v>
+      </c>
+      <c r="O214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr"/>
+      <c r="C215" t="n">
+        <v>2</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2026/08/21 14:57:52</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>-33.09928,-71.547628</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>2026/08/21 14:58:52</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>-33.095375,-71.54421</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Vía Las Palmas, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="J215" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K215" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L215" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="M215" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="N215" t="n">
+        <v>0</v>
+      </c>
+      <c r="O215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr"/>
+      <c r="C216" t="n">
+        <v>3</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2026/08/21 15:30:39</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>-33.094809,-71.543396</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Vía Las Palmas, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>2026/08/21 15:30:57</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>-33.097242,-71.547303</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J216" s="14" t="n">
+        <v>0.0002083333333333333</v>
+      </c>
+      <c r="K216" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L216" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="M216" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="N216" t="n">
+        <v>0</v>
+      </c>
+      <c r="O216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr"/>
+      <c r="C217" t="n">
+        <v>5</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2026/08/21 17:24:14</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>-33.09359,-71.548843</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>2026/08/21 17:25:21</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>-33.081909,-71.560913</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J217" s="14" t="n">
+        <v>0.0007754629629629629</v>
+      </c>
+      <c r="K217" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L217" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="M217" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="N217" t="n">
+        <v>0</v>
+      </c>
+      <c r="O217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr"/>
+      <c r="C218" t="n">
+        <v>10</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2026/08/21 17:37:45</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>-33.254758,-71.44134</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Ruta F-74-G, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>2026/08/21 17:38:31</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>-33.245884,-71.447565</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>s/n, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J218" s="14" t="n">
+        <v>0.0005324074074074074</v>
+      </c>
+      <c r="K218" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L218" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="M218" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="N218" t="n">
+        <v>0</v>
+      </c>
+      <c r="O218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr"/>
+      <c r="C219" t="n">
+        <v>4</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2026/08/22 14:46:01</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>-33.058827,-71.646622</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>2026/08/22 14:46:27</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>-33.062522,-71.641579</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="J219" s="14" t="n">
+        <v>0.0003009259259259259</v>
+      </c>
+      <c r="K219" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L219" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="M219" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="N219" t="n">
+        <v>0</v>
+      </c>
+      <c r="O219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr"/>
+      <c r="C220" t="n">
+        <v>5</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2026/08/23 22:17:56</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>-33.06655,-71.635321</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>2026/08/23 22:18:36</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>-33.072195,-71.627738</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="J220" s="14" t="n">
+        <v>0.000462962962962963</v>
+      </c>
+      <c r="K220" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L220" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="M220" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="N220" t="n">
+        <v>0</v>
+      </c>
+      <c r="O220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr"/>
+      <c r="C221" t="n">
+        <v>6</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2026/08/23 22:25:43</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>-33.117601,-71.56072</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>2026/08/23 22:26:04</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>-33.121138,-71.56138</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J221" s="14" t="n">
+        <v>0.0002430555555555555</v>
+      </c>
+      <c r="K221" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L221" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="M221" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="N221" t="n">
+        <v>0</v>
+      </c>
+      <c r="O221" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9850,7 +13689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.710625" customWidth="1" style="7" min="1" max="1"/>
@@ -9876,7 +13715,7 @@
     <row r="3" ht="25" customHeight="1" s="8">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Desde : 2026/08/03 00:00:00 Hasta: 2026/08/09 23:59:58</t>
+          <t>Desde : 2026/08/10 00:00:00 Hasta: 2026/08/16 23:59:58</t>
         </is>
       </c>
     </row>
@@ -9925,7 +13764,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>GLP SSZD-71  J VALLEJOS</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
@@ -9933,33 +13772,33 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>2026/08/05 12:23:39</t>
+          <t>2026/08/11 00:47:13</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>-33.080686,-71.561833</t>
+          <t>-32.977793,-71.499934</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Camino Internacional, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F6" s="12" t="n">
-        <v>104.6</v>
+        <v>101.7</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>61389.2</v>
+        <v>79826.3</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>176.4</v>
+        <v>160.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>GLP SSZD-71  J VALLEJOS</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B7" s="12" t="n">
@@ -9967,33 +13806,33 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>2026/08/05 12:24:39</t>
+          <t>2026/08/11 00:48:13</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>-33.070089,-71.574806</t>
+          <t>-32.992004,-71.501153</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 64, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F7" s="12" t="n">
-        <v>92.90000000000001</v>
+        <v>94</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>61390.9</v>
+        <v>79827.89999999999</v>
       </c>
       <c r="H7" s="12" t="n">
-        <v>162</v>
+        <v>144.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>GLP SSZD-71  J VALLEJOS</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
@@ -10001,33 +13840,33 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>2026/08/06 12:13:09</t>
+          <t>2026/08/11 14:25:21</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>-33.059575,-71.530514</t>
+          <t>-33.15983,-71.544708</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F8" s="12" t="n">
-        <v>101.7</v>
+        <v>100.1</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>61506.4</v>
+        <v>79918.89999999999</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>267.7</v>
+        <v>365.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>GLP SSZD-71  J VALLEJOS</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
@@ -10035,33 +13874,33 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>2026/08/06 12:13:48</t>
+          <t>2026/08/11 14:26:21</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>-33.066788,-71.533562</t>
+          <t>-33.15096,-71.557673</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F9" s="12" t="n">
-        <v>80.59999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>61507.3</v>
+        <v>79920.5</v>
       </c>
       <c r="H9" s="12" t="n">
-        <v>305.9</v>
+        <v>349.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>GLP SSZD-71  J VALLEJOS</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
@@ -10069,33 +13908,33 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>2026/08/07 12:07:15</t>
+          <t>2026/08/11 14:48:43</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>-33.094897,-71.600273</t>
+          <t>-32.951646,-71.509458</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F10" s="12" t="n">
-        <v>100.2</v>
+        <v>100.5</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>61623.8</v>
+        <v>79950.2</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>427.8</v>
+        <v>157.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>GLP SSZD-71  J VALLEJOS</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B11" s="12" t="n">
@@ -10103,27 +13942,27 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>2026/08/07 12:08:15</t>
+          <t>2026/08/11 14:49:21</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>-33.089443,-71.614598</t>
+          <t>-32.943313,-71.513542</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>84</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>61625.3</v>
+        <v>79951.3</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>469.4</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12">
@@ -10133,16 +13972,16 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>2026/08/05 14:23:46</t>
+          <t>2026/08/12 14:44:39</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>-33.163504,-71.537483</t>
+          <t>-33.163382,-71.537721</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
@@ -10151,13 +13990,13 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>101</v>
+        <v>100.3</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>78551.10000000001</v>
+        <v>80145.10000000001</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>367.4</v>
+        <v>367</v>
       </c>
     </row>
     <row r="13">
@@ -10167,16 +14006,16 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>2026/08/05 14:24:46</t>
+          <t>2026/08/12 14:45:39</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>-33.156097,-71.552015</t>
+          <t>-33.155922,-71.552342</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
@@ -10185,13 +14024,13 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>93</v>
+        <v>88.5</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>78552.7</v>
+        <v>80146.7</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>368.1</v>
+        <v>363.7</v>
       </c>
     </row>
     <row r="14">
@@ -10201,31 +14040,31 @@
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>2026/08/06 14:22:56</t>
+          <t>2026/08/12 14:47:39</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>-33.231385,-71.464327</t>
+          <t>-33.13014,-71.561957</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>100.8</v>
+        <v>103.6</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>78768</v>
+        <v>80149.89999999999</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>340</v>
+        <v>338.2</v>
       </c>
     </row>
     <row r="15">
@@ -10235,31 +14074,31 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>2026/08/06 14:23:56</t>
+          <t>2026/08/12 14:48:39</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>-33.219271,-71.471768</t>
+          <t>-33.115708,-71.560383</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>85.7</v>
+        <v>94.7</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>78769.5</v>
+        <v>80151.5</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>335.5</v>
+        <v>338.3</v>
       </c>
     </row>
     <row r="16">
@@ -10269,16 +14108,16 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>2026/08/08 01:32:10</t>
+          <t>2026/08/13 14:31:13</t>
         </is>
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>-33.234063,-71.462269</t>
+          <t>-33.225857,-71.468365</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
@@ -10287,13 +14126,13 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>103.3</v>
+        <v>100.3</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>79183.89999999999</v>
+        <v>80372.5</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>344</v>
+        <v>330.1</v>
       </c>
     </row>
     <row r="17">
@@ -10303,16 +14142,16 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>2026/08/08 01:33:10</t>
+          <t>2026/08/13 14:32:13</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>-33.244036,-71.449798</t>
+          <t>-33.213027,-71.475997</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
@@ -10321,13 +14160,13 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>98.2</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>79185.5</v>
+        <v>80374.10000000001</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>276.9</v>
+        <v>349.6</v>
       </c>
     </row>
     <row r="18">
@@ -10337,31 +14176,31 @@
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>2026/08/08 14:19:07</t>
+          <t>2026/08/14 00:38:07</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>-33.232909,-71.463096</t>
+          <t>-32.98055,-71.500149</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Camino Internacional, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>103.5</v>
+        <v>100.2</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>79225.7</v>
+        <v>80520</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>345.6</v>
+        <v>140.8</v>
       </c>
     </row>
     <row r="19">
@@ -10371,37 +14210,37 @@
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>2026/08/08 14:20:07</t>
+          <t>2026/08/14 00:39:07</t>
         </is>
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>-33.219807,-71.471478</t>
+          <t>-32.994359,-71.501297</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 64, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>90.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>79227.39999999999</v>
+        <v>80521.60000000001</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>336.1</v>
+        <v>142.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>GV SHLC-74 B MIRANDA</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B20" s="12" t="n">
@@ -10409,33 +14248,33 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>2026/08/05 16:09:19</t>
+          <t>2026/08/10 10:29:37</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>-32.786803,-71.431676</t>
+          <t>-32.757227,-71.420873</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-190, Quintero, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta F-190, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>101.5</v>
+        <v>104.2</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>124111.7</v>
+        <v>188637</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>67.40000000000001</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>GV SHLC-74 B MIRANDA</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B21" s="12" t="n">
@@ -10443,33 +14282,33 @@
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>2026/08/05 16:10:19</t>
+          <t>2026/08/10 10:30:38</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>-32.797308,-71.44036</t>
+          <t>-32.743513,-71.417967</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-190, Quintero, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta F-190, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>97.8</v>
+        <v>86.2</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>124113.1</v>
+        <v>188638.6</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>44</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>GV SHLC-74 B MIRANDA</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B22" s="12" t="n">
@@ -10477,33 +14316,33 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>2026/08/06 09:46:47</t>
+          <t>2026/08/13 10:39:59</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>-33.205819,-71.48396</t>
+          <t>-33.227,-71.467768</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>100.5</v>
+        <v>108</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>124379.3</v>
+        <v>189448.4</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>400</v>
+        <v>322.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>GV SHLC-74 B MIRANDA</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B23" s="12" t="n">
@@ -10511,12 +14350,12 @@
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>2026/08/06 09:47:47</t>
+          <t>2026/08/13 10:40:59</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>-33.216959,-71.473175</t>
+          <t>-33.213935,-71.475097</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
@@ -10525,455 +14364,1883 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>94.40000000000001</v>
+        <v>92</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>124380.9</v>
+        <v>189450</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>335.6</v>
+        <v>339.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>GV TM5 RXXG-15 E CABANILLA</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>2026/08/07 07:01:46</t>
+          <t>2026/08/13 10:49:59</t>
         </is>
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>-33.275515,-71.429868</t>
+          <t>-33.119158,-71.56076</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>102.3</v>
+        <v>108.5</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>22879</v>
+        <v>189464.3</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>298.5</v>
+        <v>346.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>GV TM5 RXXG-15 E CABANILLA</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>2026/08/07 07:02:46</t>
+          <t>2026/08/13 10:50:42</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>-33.262462,-71.43552</t>
+          <t>-33.109677,-71.558209</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>91.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>22880.5</v>
+        <v>189465.4</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>291</v>
+        <v>345.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>GV TM5 RXXG-15 E CABANILLA</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>2026/08/07 07:14:46</t>
+          <t>2026/08/13 18:25:02</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>-33.143468,-71.561375</t>
+          <t>-33.268542,-71.432855</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>102.8</v>
+        <v>103.6</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>22898.6</v>
+        <v>189651.3</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>331.1</v>
+        <v>282.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>GV TM5 RXXG-15 E CABANILLA</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>2026/08/07 07:15:46</t>
+          <t>2026/08/13 18:26:02</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>-33.130053,-71.561948</t>
+          <t>-33.255908,-71.44039</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>87.7</v>
+        <v>95</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>22900.1</v>
+        <v>189652.9</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>336</v>
+        <v>270.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>GC TSVS-89 M AEDO</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>2026/08/03 06:01:10</t>
+          <t>2026/08/13 18:48:02</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>-33.063154,-71.469437</t>
+          <t>-33.071993,-71.571936</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Autopista Troncal Sur, Quilpué, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>100.2</v>
+        <v>109.5</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>117052.1</v>
+        <v>189679.6</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>116.8</v>
+        <v>161.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>GC TSVS-89 M AEDO</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B29" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>2026/08/03 06:02:10</t>
+          <t>2026/08/13 18:48:57</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>-33.061893,-71.457259</t>
+          <t>-33.063353,-71.582457</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>s/n, Quilpué, Marga Marga, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>29.7</v>
+        <v>83.7</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>117053.3</v>
+        <v>189681</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>172</v>
+        <v>138.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>GC TSVS-89 M AEDO</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B30" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>2026/08/07 18:21:12</t>
+          <t>2026/08/14 08:05:03</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>-32.924007,-71.28105</t>
+          <t>-33.10634,-71.549378</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>101.6</v>
+        <v>108.7</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>118469.3</v>
+        <v>189719.9</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>85.5</v>
+        <v>349.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>GC TSVS-89 M AEDO</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B31" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>2026/08/07 18:22:01</t>
+          <t>2026/08/14 08:05:05</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>-32.933575,-71.288625</t>
+          <t>-33.106701,-71.549852</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>73.3</v>
+        <v>106.6</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>118470.6</v>
+        <v>189720</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>80.90000000000001</v>
+        <v>347.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>GC TSVS-89 M AEDO</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>2026/08/07 18:36:12</t>
+          <t>2026/08/14 08:05:51</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>-33.06936,-71.36277</t>
+          <t>-33.112291,-71.560068</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>103.7</v>
+        <v>95.7</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>118490.2</v>
+        <v>189721.2</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>192.3</v>
+        <v>342.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>GC TSVS-89 M AEDO</t>
+          <t>GV SHLC-74 B MIRANDA</t>
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>2026/08/07 18:37:12</t>
+          <t>2026/08/10 09:12:32</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>-33.067906,-71.380727</t>
+          <t>-33.157548,-71.549489</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>103.6</v>
+        <v>101.7</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>118491.9</v>
+        <v>125165</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>177</v>
+        <v>367.1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>GC TSVS-89 M AEDO</t>
+          <t>GV SHLC-74 B MIRANDA</t>
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>2026/08/07 18:38:12</t>
+          <t>2026/08/10 09:13:32</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>-33.066117,-71.397749</t>
+          <t>-33.165047,-71.534798</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>88.2</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>118493.5</v>
+        <v>125166.6</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>169.5</v>
+        <v>357.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>JAC  LYTS-17 G GALEA</t>
+          <t>GV SHLC-74 B MIRANDA</t>
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>2026/08/06 07:52:03</t>
+          <t>2026/08/11 09:46:56</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>-32.680652,-71.425247</t>
+          <t>-33.216008,-71.473704</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Ruta E-30-F, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>101.1</v>
+        <v>101</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>226852.1</v>
+        <v>125408.6</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>88.7</v>
+        <v>337.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
+          <t>GV SHLC-74 B MIRANDA</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/11 09:47:57</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>-33.229387,-71.466181</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>125410.3</v>
+      </c>
+      <c r="H36" s="12" t="n">
+        <v>336.2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>GV SHLC-74 B MIRANDA</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/11 22:16:04</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>-33.217343,-71.472838</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>125456.3</v>
+      </c>
+      <c r="H37" s="12" t="n">
+        <v>337.8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>GV SHLC-74 B MIRANDA</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/11 22:17:04</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>-33.205626,-71.484055</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>125457.9</v>
+      </c>
+      <c r="H38" s="12" t="n">
+        <v>401.1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>GV SHLC-74 B MIRANDA</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/13 10:02:31</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>-33.35848,-71.326553</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>125971</v>
+      </c>
+      <c r="H39" s="12" t="n">
+        <v>301.6</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>GV SHLC-74 B MIRANDA</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/13 10:03:31</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>-33.364972,-71.312258</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>125972.5</v>
+      </c>
+      <c r="H40" s="12" t="n">
+        <v>312.6</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>GV SHLC-74 B MIRANDA</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/13 22:23:11</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>-33.203884,-71.485888</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>125999.8</v>
+      </c>
+      <c r="H41" s="12" t="n">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>GV SHLC-74 B MIRANDA</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/13 22:24:11</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>-33.192111,-71.496379</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>126001.5</v>
+      </c>
+      <c r="H42" s="12" t="n">
+        <v>364.2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/11 15:16:59</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="inlineStr">
+        <is>
+          <t>-33.093469,-71.603099</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>54938.9</v>
+      </c>
+      <c r="H43" s="12" t="n">
+        <v>416.5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/11 15:17:02</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="inlineStr">
+        <is>
+          <t>-33.094082,-71.602581</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>54939</v>
+      </c>
+      <c r="H44" s="12" t="n">
+        <v>417.8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/13 07:27:21</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>-33.054539,-71.335674</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>124058.8</v>
+      </c>
+      <c r="H45" s="12" t="n">
+        <v>181.1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/13 07:28:21</t>
+        </is>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>-33.063291,-71.348177</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="G46" s="12" t="n">
+        <v>124060.4</v>
+      </c>
+      <c r="H46" s="12" t="n">
+        <v>201.6</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/13 09:17:07</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="inlineStr">
+        <is>
+          <t>-33.09653,-71.545845</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>s/n, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>124118.2</v>
+      </c>
+      <c r="H47" s="12" t="n">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/13 09:17:25</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>-33.093518,-71.542204</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="inlineStr">
+        <is>
+          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="G48" s="12" t="n">
+        <v>124118.7</v>
+      </c>
+      <c r="H48" s="12" t="n">
+        <v>322.7</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/13 09:17:46</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t>-33.088266,-71.5422</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="G49" s="12" t="n">
+        <v>124119.2</v>
+      </c>
+      <c r="H49" s="12" t="n">
+        <v>331.2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>GLP SKDX-44 V VIAL</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/11 01:18:36</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>-33.031585,-71.631541</t>
+        </is>
+      </c>
+      <c r="E50" s="12" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="G50" s="12" t="n">
+        <v>148436.9</v>
+      </c>
+      <c r="H50" s="12" t="n">
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>GLP SKDX-44 V VIAL</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/11 01:22:16</t>
+        </is>
+      </c>
+      <c r="D51" s="15" t="inlineStr">
+        <is>
+          <t>-33.031585,-71.631541</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>148436.9</v>
+      </c>
+      <c r="H51" s="12" t="n">
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>GLP SKDX-44 V VIAL</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/11 01:22:22</t>
+        </is>
+      </c>
+      <c r="D52" s="15" t="inlineStr">
+        <is>
+          <t>-33.031872,-71.6299</t>
+        </is>
+      </c>
+      <c r="E52" s="12" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>148437.1</v>
+      </c>
+      <c r="H52" s="12" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>GLP SKDX-44 V VIAL</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/12 12:27:11</t>
+        </is>
+      </c>
+      <c r="D53" s="15" t="inlineStr">
+        <is>
+          <t>-33.113036,-71.560164</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="G53" s="12" t="n">
+        <v>148506.5</v>
+      </c>
+      <c r="H53" s="12" t="n">
+        <v>338.1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>GLP SKDX-44 V VIAL</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/12 12:27:50</t>
+        </is>
+      </c>
+      <c r="D54" s="15" t="inlineStr">
+        <is>
+          <t>-33.121189,-71.561416</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="G54" s="12" t="n">
+        <v>148507.3</v>
+      </c>
+      <c r="H54" s="12" t="n">
+        <v>352.7</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/14 19:10:37</t>
+        </is>
+      </c>
+      <c r="D55" s="15" t="inlineStr">
+        <is>
+          <t>-33.053836,-71.334523</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="G55" s="12" t="n">
+        <v>119886.3</v>
+      </c>
+      <c r="H55" s="12" t="n">
+        <v>191.8</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B56" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/14 19:11:38</t>
+        </is>
+      </c>
+      <c r="D56" s="15" t="inlineStr">
+        <is>
+          <t>-33.063285,-71.348089</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="G56" s="12" t="n">
+        <v>119887.9</v>
+      </c>
+      <c r="H56" s="12" t="n">
+        <v>201.8</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/14 19:12:38</t>
+        </is>
+      </c>
+      <c r="D57" s="15" t="inlineStr">
+        <is>
+          <t>-33.06932,-71.363576</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="G57" s="12" t="n">
+        <v>119889.5</v>
+      </c>
+      <c r="H57" s="12" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/14 19:13:38</t>
+        </is>
+      </c>
+      <c r="D58" s="15" t="inlineStr">
+        <is>
+          <t>-33.067875,-71.380877</t>
+        </is>
+      </c>
+      <c r="E58" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F58" s="12" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="G58" s="12" t="n">
+        <v>119891.2</v>
+      </c>
+      <c r="H58" s="12" t="n">
+        <v>181.5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
           <t>JAC  LYTS-17 G GALEA</t>
         </is>
       </c>
-      <c r="B36" s="12" t="n">
+      <c r="B59" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="12" t="inlineStr">
-        <is>
-          <t>2026/08/06 07:53:03</t>
-        </is>
-      </c>
-      <c r="D36" s="15" t="inlineStr">
-        <is>
-          <t>-32.670624,-71.425352</t>
-        </is>
-      </c>
-      <c r="E36" s="12" t="inlineStr">
-        <is>
-          <t>Ruta E-30-F, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
-        </is>
-      </c>
-      <c r="F36" s="12" t="n">
-        <v>63.9</v>
-      </c>
-      <c r="G36" s="12" t="n">
-        <v>226853.2</v>
-      </c>
-      <c r="H36" s="12" t="n">
-        <v>110.3</v>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/13 11:57:49</t>
+        </is>
+      </c>
+      <c r="D59" s="15" t="inlineStr">
+        <is>
+          <t>-33.285524,-71.411366</t>
+        </is>
+      </c>
+      <c r="E59" s="12" t="inlineStr">
+        <is>
+          <t>Ruta F-852, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F59" s="12" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="G59" s="12" t="n">
+        <v>227898.2</v>
+      </c>
+      <c r="H59" s="12" t="n">
+        <v>261.6</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>JAC  LYTS-17 G GALEA</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/13 11:58:27</t>
+        </is>
+      </c>
+      <c r="D60" s="15" t="inlineStr">
+        <is>
+          <t>-33.279484,-71.413704</t>
+        </is>
+      </c>
+      <c r="E60" s="12" t="inlineStr">
+        <is>
+          <t>Ruta F-852, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F60" s="12" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="G60" s="12" t="n">
+        <v>227898.9</v>
+      </c>
+      <c r="H60" s="12" t="n">
+        <v>297.5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B61" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/11 17:10:00</t>
+        </is>
+      </c>
+      <c r="D61" s="15" t="inlineStr">
+        <is>
+          <t>-32.798908,-71.440814</t>
+        </is>
+      </c>
+      <c r="E61" s="12" t="inlineStr">
+        <is>
+          <t>Ruta F-190, Quintero, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="F61" s="12" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="G61" s="12" t="n">
+        <v>281024.7</v>
+      </c>
+      <c r="H61" s="12" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/11 17:11:00</t>
+        </is>
+      </c>
+      <c r="D62" s="15" t="inlineStr">
+        <is>
+          <t>-32.810983,-71.441434</t>
+        </is>
+      </c>
+      <c r="E62" s="12" t="inlineStr">
+        <is>
+          <t>Ruta F-190, Quintero, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F62" s="12" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="G62" s="12" t="n">
+        <v>281026.1</v>
+      </c>
+      <c r="H62" s="12" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B63" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/11 17:31:29</t>
+        </is>
+      </c>
+      <c r="D63" s="15" t="inlineStr">
+        <is>
+          <t>-32.942137,-71.482014</t>
+        </is>
+      </c>
+      <c r="E63" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 64, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="F63" s="12" t="n">
+        <v>104</v>
+      </c>
+      <c r="G63" s="12" t="n">
+        <v>281045</v>
+      </c>
+      <c r="H63" s="12" t="n">
+        <v>68.5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B64" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/11 17:32:08</t>
+        </is>
+      </c>
+      <c r="D64" s="15" t="inlineStr">
+        <is>
+          <t>-32.9487,-71.483747</t>
+        </is>
+      </c>
+      <c r="E64" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 64, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="F64" s="12" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="G64" s="12" t="n">
+        <v>281045.7</v>
+      </c>
+      <c r="H64" s="12" t="n">
+        <v>109.1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/12 11:16:15</t>
+        </is>
+      </c>
+      <c r="D65" s="15" t="inlineStr">
+        <is>
+          <t>-33.38297,-71.391372</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="inlineStr">
+        <is>
+          <t>Ruta F-74-G, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="F65" s="12" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="G65" s="12" t="n">
+        <v>281111.9</v>
+      </c>
+      <c r="H65" s="12" t="n">
+        <v>246.1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C66" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/12 11:17:01</t>
+        </is>
+      </c>
+      <c r="D66" s="15" t="inlineStr">
+        <is>
+          <t>-33.393885,-71.395297</t>
+        </is>
+      </c>
+      <c r="E66" s="12" t="inlineStr">
+        <is>
+          <t>Ruta F-74-G, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="F66" s="12" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="G66" s="12" t="n">
+        <v>281113.2</v>
+      </c>
+      <c r="H66" s="12" t="n">
+        <v>262.5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/12 11:17:15</t>
+        </is>
+      </c>
+      <c r="D67" s="15" t="inlineStr">
+        <is>
+          <t>-33.396877,-71.394671</t>
+        </is>
+      </c>
+      <c r="E67" s="12" t="inlineStr">
+        <is>
+          <t>Ruta F-74-G, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="F67" s="12" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="G67" s="12" t="n">
+        <v>281113.5</v>
+      </c>
+      <c r="H67" s="12" t="n">
+        <v>271.2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B68" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C68" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/12 15:55:12</t>
+        </is>
+      </c>
+      <c r="D68" s="15" t="inlineStr">
+        <is>
+          <t>-33.376179,-71.386332</t>
+        </is>
+      </c>
+      <c r="E68" s="12" t="inlineStr">
+        <is>
+          <t>Ruta F-74-G, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="F68" s="12" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="G68" s="12" t="n">
+        <v>281121.8</v>
+      </c>
+      <c r="H68" s="12" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/12 15:55:25</t>
+        </is>
+      </c>
+      <c r="D69" s="15" t="inlineStr">
+        <is>
+          <t>-33.373618,-71.385271</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="inlineStr">
+        <is>
+          <t>Ruta F-74-G, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="F69" s="12" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="G69" s="12" t="n">
+        <v>281122.1</v>
+      </c>
+      <c r="H69" s="12" t="n">
+        <v>265.3</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B70" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C70" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/12 16:13:58</t>
+        </is>
+      </c>
+      <c r="D70" s="15" t="inlineStr">
+        <is>
+          <t>-33.305002,-71.411287</t>
+        </is>
+      </c>
+      <c r="E70" s="12" t="inlineStr">
+        <is>
+          <t>s/n, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F70" s="12" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="G70" s="12" t="n">
+        <v>281132.6</v>
+      </c>
+      <c r="H70" s="12" t="n">
+        <v>256.6</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/12 16:14:58</t>
+        </is>
+      </c>
+      <c r="D71" s="15" t="inlineStr">
+        <is>
+          <t>-33.292213,-71.422649</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F71" s="12" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="G71" s="12" t="n">
+        <v>281134.4</v>
+      </c>
+      <c r="H71" s="12" t="n">
+        <v>287.9</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B72" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C72" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/12 16:15:57</t>
+        </is>
+      </c>
+      <c r="D72" s="15" t="inlineStr">
+        <is>
+          <t>-33.277849,-71.428907</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F72" s="12" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="G72" s="12" t="n">
+        <v>281136.1</v>
+      </c>
+      <c r="H72" s="12" t="n">
+        <v>309.8</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B73" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/12 17:29:08</t>
+        </is>
+      </c>
+      <c r="D73" s="15" t="inlineStr">
+        <is>
+          <t>-32.982117,-71.500227</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>Camino Internacional Valparaíso - Mendoza, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F73" s="12" t="n">
+        <v>107</v>
+      </c>
+      <c r="G73" s="12" t="n">
+        <v>281187.3</v>
+      </c>
+      <c r="H73" s="12" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B74" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C74" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/12 17:29:59</t>
+        </is>
+      </c>
+      <c r="D74" s="15" t="inlineStr">
+        <is>
+          <t>-32.970275,-71.5001</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="inlineStr">
+        <is>
+          <t>Ruta E-30-F, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="F74" s="12" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="G74" s="12" t="n">
+        <v>281188.6</v>
+      </c>
+      <c r="H74" s="12" t="n">
+        <v>173.6</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/12 17:32:09</t>
+        </is>
+      </c>
+      <c r="D75" s="15" t="inlineStr">
+        <is>
+          <t>-32.943489,-71.513534</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="inlineStr">
+        <is>
+          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="F75" s="12" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="G75" s="12" t="n">
+        <v>281192</v>
+      </c>
+      <c r="H75" s="12" t="n">
+        <v>118.9</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B76" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C76" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/12 17:33:09</t>
+        </is>
+      </c>
+      <c r="D76" s="15" t="inlineStr">
+        <is>
+          <t>-32.929667,-71.512068</t>
+        </is>
+      </c>
+      <c r="E76" s="12" t="inlineStr">
+        <is>
+          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="F76" s="12" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="G76" s="12" t="n">
+        <v>281193.6</v>
+      </c>
+      <c r="H76" s="12" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/13 09:24:35</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="inlineStr">
+        <is>
+          <t>-32.985661,-71.500562</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="inlineStr">
+        <is>
+          <t>Camino Internacional Valparaíso - Mendoza, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F77" s="12" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="G77" s="12" t="n">
+        <v>281301.3</v>
+      </c>
+      <c r="H77" s="12" t="n">
+        <v>132.1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B78" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/13 09:25:32</t>
+        </is>
+      </c>
+      <c r="D78" s="15" t="inlineStr">
+        <is>
+          <t>-32.998254,-71.502383</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="inlineStr">
+        <is>
+          <t>Camino Internacional Valparaíso - Mendoza, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F78" s="12" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="G78" s="12" t="n">
+        <v>281302.7</v>
+      </c>
+      <c r="H78" s="12" t="n">
+        <v>158.4</v>
       </c>
     </row>
   </sheetData>
@@ -11014,12 +16281,54 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId73"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="default" paperSize="1" scale="100" pageOrder="downThenOver" blackAndWhite="0" draft="0" errors="displayed"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId32"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId74"/>
   </tableParts>
 </worksheet>
 </file>
--- a/INFORME EXCESOS DE VELOCIDAD.xlsx
+++ b/INFORME EXCESOS DE VELOCIDAD.xlsx
@@ -222,8 +222,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SpeedingFleetsSummaryTable_1" displayName="SpeedingFleetsSummaryTable_1" ref="A5:I14" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A5:I14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SpeedingFleetsSummaryTable_1" displayName="SpeedingFleetsSummaryTable_1" ref="A5:I10" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A5:I10"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Alias"/>
     <tableColumn id="2" name="Excesos" dataDxfId="0"/>
@@ -240,8 +240,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SpeedingFleetsDetailTable_1" displayName="SpeedingFleetsDetailTable_1" ref="A5:O39" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A5:O39"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SpeedingFleetsDetailTable_1" displayName="SpeedingFleetsDetailTable_1" ref="A5:O69" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A5:O69"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Alias"/>
     <tableColumn id="2" name="Conductor"/>
@@ -264,8 +264,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SpeedingFleetsDataTable_1" displayName="SpeedingFleetsDataTable_1" ref="A5:H78" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A5:H78"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SpeedingFleetsDataTable_1" displayName="SpeedingFleetsDataTable_1" ref="A5:H168" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A5:H168"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Alias"/>
     <tableColumn id="2" name="Secuencial" dataDxfId="0"/>
@@ -569,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.710625" customWidth="1" style="7" min="1" max="1"/>
@@ -593,7 +593,7 @@
     <row r="3" ht="25" customHeight="1" s="8">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Desde : 2026/07/13 00:00:00 Hasta: 2026/08/23 23:59:59</t>
+          <t>Desde : 2026/07/13 00:00:00 Hasta: 2026/08/29 23:59:59</t>
         </is>
       </c>
     </row>
@@ -651,22 +651,22 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>0.004606481481481481</v>
+        <v>0.00244212962962963</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>0.0006580671296296296</v>
+        <v>0.0006105324074074074</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>10.7</v>
+        <v>5.7</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>103.6</v>
+        <v>106.1</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>101</v>
+        <v>102.4</v>
       </c>
       <c r="H6" s="12" t="n">
         <v>0</v>
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>0.003784722222222222</v>
+        <v>0.002986111111111111</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>0.000630787037037037</v>
+        <v>0.0005972222222222222</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>8.6</v>
+        <v>6.9</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>109.5</v>
+        <v>108.6</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>106.9</v>
+        <v>104.4</v>
       </c>
       <c r="H7" s="12" t="n">
         <v>0</v>
@@ -709,26 +709,26 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>GV SHLC-74 B MIRANDA</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>0.003483796296296296</v>
+        <v>0.002002314814814815</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>0.0006967592592592593</v>
+        <v>0.0003337152777777778</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>8.1</v>
+        <v>3.1</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>103.4</v>
+        <v>104.6</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>102.3</v>
+        <v>102.8</v>
       </c>
       <c r="H8" s="12" t="n">
         <v>0</v>
@@ -740,26 +740,26 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>3.472222222222222e-05</v>
+        <v>0.04518518518518518</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3.472222222222222e-05</v>
+        <v>0.001158599537037037</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>0.1</v>
+        <v>105.3</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>104.6</v>
+        <v>102.7</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>104.6</v>
+        <v>100.8</v>
       </c>
       <c r="H9" s="12" t="n">
         <v>0</v>
@@ -771,155 +771,31 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>GV PEUGEOT THJY-73 J PONCE</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>0.001145833333333333</v>
+        <v>0.00525462962962963</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>0.0005729166666666667</v>
+        <v>0.0005254629629629629</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>2.6</v>
+        <v>11.5</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>100.6</v>
+        <v>121.7</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>100.4</v>
+        <v>107.4</v>
       </c>
       <c r="H10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>GLP SKDX-44 V VIAL</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" s="13" t="n">
-        <v>0.00306712962962963</v>
-      </c>
-      <c r="D11" s="13" t="n">
-        <v>0.001533564814814815</v>
-      </c>
-      <c r="E11" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="12" t="n">
-        <v>109.2</v>
-      </c>
-      <c r="G11" s="12" t="n">
-        <v>106.5</v>
-      </c>
-      <c r="H11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" s="13" t="n">
-        <v>0.001400462962962963</v>
-      </c>
-      <c r="D12" s="13" t="n">
-        <v>0.0007002314814814815</v>
-      </c>
-      <c r="E12" s="12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="F12" s="12" t="n">
-        <v>103.6</v>
-      </c>
-      <c r="G12" s="12" t="n">
-        <v>102.4</v>
-      </c>
-      <c r="H12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>JAC  LYTS-17 G GALEA</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="13" t="n">
-        <v>0.0004398148148148148</v>
-      </c>
-      <c r="D13" s="13" t="n">
-        <v>0.0004398148148148148</v>
-      </c>
-      <c r="E13" s="12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F13" s="12" t="n">
-        <v>107.6</v>
-      </c>
-      <c r="G13" s="12" t="n">
-        <v>107.6</v>
-      </c>
-      <c r="H13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="C14" s="13" t="n">
-        <v>0.0053125</v>
-      </c>
-      <c r="D14" s="13" t="n">
-        <v>0.0006640625</v>
-      </c>
-      <c r="E14" s="12" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="F14" s="12" t="n">
-        <v>110.7</v>
-      </c>
-      <c r="G14" s="12" t="n">
-        <v>106.1</v>
-      </c>
-      <c r="H14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -944,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O221"/>
+  <dimension ref="A1:O259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.710625" customWidth="1" style="7" min="1" max="1"/>
@@ -972,7 +848,7 @@
     <row r="3" ht="25" customHeight="1" s="8">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Desde : 2026/08/10 00:00:00 Hasta: 2026/08/16 23:59:58</t>
+          <t>Desde : 2026/08/17 00:00:00 Hasta: 2026/08/23 23:59:58</t>
         </is>
       </c>
     </row>
@@ -9894,7 +9770,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr"/>
       <c r="C158" t="n">
         <v>1</v>
       </c>
@@ -9953,7 +9828,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr"/>
       <c r="C159" t="n">
         <v>2</v>
       </c>
@@ -10012,7 +9886,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr"/>
       <c r="C160" t="n">
         <v>1</v>
       </c>
@@ -10071,7 +9944,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr"/>
       <c r="C161" t="n">
         <v>2</v>
       </c>
@@ -10130,7 +10002,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr"/>
       <c r="C162" t="n">
         <v>3</v>
       </c>
@@ -10189,7 +10060,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr"/>
       <c r="C163" t="n">
         <v>4</v>
       </c>
@@ -10248,7 +10118,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr"/>
       <c r="C164" t="n">
         <v>5</v>
       </c>
@@ -10307,7 +10176,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr"/>
       <c r="C165" t="n">
         <v>6</v>
       </c>
@@ -10366,7 +10234,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr"/>
       <c r="C166" t="n">
         <v>7</v>
       </c>
@@ -10425,7 +10292,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr"/>
       <c r="C167" t="n">
         <v>8</v>
       </c>
@@ -10484,7 +10350,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr"/>
       <c r="C168" t="n">
         <v>9</v>
       </c>
@@ -10543,7 +10408,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr"/>
       <c r="C169" t="n">
         <v>10</v>
       </c>
@@ -10602,7 +10466,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr"/>
       <c r="C170" t="n">
         <v>11</v>
       </c>
@@ -10661,7 +10524,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr"/>
       <c r="C171" t="n">
         <v>12</v>
       </c>
@@ -10720,7 +10582,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr"/>
       <c r="C172" t="n">
         <v>1</v>
       </c>
@@ -10779,7 +10640,6 @@
           <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr"/>
       <c r="C173" t="n">
         <v>1</v>
       </c>
@@ -10838,7 +10698,6 @@
           <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr"/>
       <c r="C174" t="n">
         <v>2</v>
       </c>
@@ -10897,7 +10756,6 @@
           <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr"/>
       <c r="C175" t="n">
         <v>3</v>
       </c>
@@ -10956,7 +10814,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr"/>
       <c r="C176" t="n">
         <v>2</v>
       </c>
@@ -11015,7 +10872,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr"/>
       <c r="C177" t="n">
         <v>3</v>
       </c>
@@ -11074,7 +10930,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr"/>
       <c r="C178" t="n">
         <v>4</v>
       </c>
@@ -11133,7 +10988,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr"/>
       <c r="C179" t="n">
         <v>5</v>
       </c>
@@ -11192,7 +11046,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr"/>
       <c r="C180" t="n">
         <v>6</v>
       </c>
@@ -11251,7 +11104,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr"/>
       <c r="C181" t="n">
         <v>7</v>
       </c>
@@ -11310,7 +11162,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr"/>
       <c r="C182" t="n">
         <v>8</v>
       </c>
@@ -11369,7 +11220,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr"/>
       <c r="C183" t="n">
         <v>9</v>
       </c>
@@ -11428,7 +11278,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr"/>
       <c r="C184" t="n">
         <v>3</v>
       </c>
@@ -11487,7 +11336,6 @@
           <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr"/>
       <c r="C185" t="n">
         <v>4</v>
       </c>
@@ -11546,7 +11394,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr"/>
       <c r="C186" t="n">
         <v>13</v>
       </c>
@@ -11605,7 +11452,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr"/>
       <c r="C187" t="n">
         <v>14</v>
       </c>
@@ -11664,7 +11510,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr"/>
       <c r="C188" t="n">
         <v>15</v>
       </c>
@@ -11723,7 +11568,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr"/>
       <c r="C189" t="n">
         <v>16</v>
       </c>
@@ -11782,7 +11626,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr"/>
       <c r="C190" t="n">
         <v>17</v>
       </c>
@@ -11841,7 +11684,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr"/>
       <c r="C191" t="n">
         <v>18</v>
       </c>
@@ -11900,7 +11742,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr"/>
       <c r="C192" t="n">
         <v>19</v>
       </c>
@@ -11959,7 +11800,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr"/>
       <c r="C193" t="n">
         <v>4</v>
       </c>
@@ -12018,7 +11858,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr"/>
       <c r="C194" t="n">
         <v>20</v>
       </c>
@@ -12077,7 +11916,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr"/>
       <c r="C195" t="n">
         <v>21</v>
       </c>
@@ -12136,7 +11974,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr"/>
       <c r="C196" t="n">
         <v>22</v>
       </c>
@@ -12195,7 +12032,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr"/>
       <c r="C197" t="n">
         <v>23</v>
       </c>
@@ -12256,7 +12092,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr"/>
       <c r="C198" t="n">
         <v>24</v>
       </c>
@@ -12317,7 +12152,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr"/>
       <c r="C199" t="n">
         <v>25</v>
       </c>
@@ -12376,7 +12210,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr"/>
       <c r="C200" t="n">
         <v>26</v>
       </c>
@@ -12435,7 +12268,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr"/>
       <c r="C201" t="n">
         <v>27</v>
       </c>
@@ -12494,7 +12326,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr"/>
       <c r="C202" t="n">
         <v>28</v>
       </c>
@@ -12553,7 +12384,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr"/>
       <c r="C203" t="n">
         <v>29</v>
       </c>
@@ -12612,7 +12442,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr"/>
       <c r="C204" t="n">
         <v>30</v>
       </c>
@@ -12671,7 +12500,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr"/>
       <c r="C205" t="n">
         <v>31</v>
       </c>
@@ -12730,7 +12558,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr"/>
       <c r="C206" t="n">
         <v>32</v>
       </c>
@@ -12789,7 +12616,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr"/>
       <c r="C207" t="n">
         <v>33</v>
       </c>
@@ -12848,7 +12674,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr"/>
       <c r="C208" t="n">
         <v>34</v>
       </c>
@@ -12907,7 +12732,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr"/>
       <c r="C209" t="n">
         <v>35</v>
       </c>
@@ -12966,7 +12790,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr"/>
       <c r="C210" t="n">
         <v>36</v>
       </c>
@@ -13025,7 +12848,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr"/>
       <c r="C211" t="n">
         <v>37</v>
       </c>
@@ -13084,7 +12906,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr"/>
       <c r="C212" t="n">
         <v>38</v>
       </c>
@@ -13143,7 +12964,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr"/>
       <c r="C213" t="n">
         <v>39</v>
       </c>
@@ -13202,7 +13022,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr"/>
       <c r="C214" t="n">
         <v>1</v>
       </c>
@@ -13261,7 +13080,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr"/>
       <c r="C215" t="n">
         <v>2</v>
       </c>
@@ -13320,7 +13138,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr"/>
       <c r="C216" t="n">
         <v>3</v>
       </c>
@@ -13379,7 +13196,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr"/>
       <c r="C217" t="n">
         <v>5</v>
       </c>
@@ -13438,7 +13254,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr"/>
       <c r="C218" t="n">
         <v>10</v>
       </c>
@@ -13497,7 +13312,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr"/>
       <c r="C219" t="n">
         <v>4</v>
       </c>
@@ -13556,7 +13370,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr"/>
       <c r="C220" t="n">
         <v>5</v>
       </c>
@@ -13615,7 +13428,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr"/>
       <c r="C221" t="n">
         <v>6</v>
       </c>
@@ -13665,6 +13477,2252 @@
         <v>0</v>
       </c>
       <c r="O221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr"/>
+      <c r="C222" t="n">
+        <v>1</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2026/08/24 07:03:40</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>-32.869319,-71.229053</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>2026/08/24 07:04:41</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>-32.854629,-71.224404</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J222" s="14" t="n">
+        <v>0.0007060185185185185</v>
+      </c>
+      <c r="K222" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L222" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="M222" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="N222" t="n">
+        <v>0</v>
+      </c>
+      <c r="O222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr"/>
+      <c r="C223" t="n">
+        <v>2</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2026/08/24 07:08:40</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>-32.800992,-71.210406</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>2026/08/24 07:10:09</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>-32.790331,-71.188678</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Calera, Quillota, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="J223" s="14" t="n">
+        <v>0.001030092592592593</v>
+      </c>
+      <c r="K223" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L223" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="M223" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="N223" t="n">
+        <v>0</v>
+      </c>
+      <c r="O223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr"/>
+      <c r="C224" t="n">
+        <v>3</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2026/08/24 07:10:41</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>-32.792331,-71.180253</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Calera, Quillota, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>2026/08/24 07:11:41</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>-32.787079,-71.167123</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>s/n, Hijuelas, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J224" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K224" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L224" t="n">
+        <v>101</v>
+      </c>
+      <c r="M224" t="n">
+        <v>101</v>
+      </c>
+      <c r="N224" t="n">
+        <v>0</v>
+      </c>
+      <c r="O224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr"/>
+      <c r="C225" t="n">
+        <v>4</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>2026/08/24 07:12:41</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>-32.784126,-71.172964</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>s/n, Hijuelas, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>2026/08/24 07:13:40</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>-32.773865,-71.185517</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Calera, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J225" s="14" t="n">
+        <v>0.0006828703703703704</v>
+      </c>
+      <c r="K225" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L225" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="M225" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="N225" t="n">
+        <v>0</v>
+      </c>
+      <c r="O225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr"/>
+      <c r="C226" t="n">
+        <v>5</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>2026/08/24 07:16:40</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>-32.732096,-71.200727</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Calera, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>2026/08/24 07:17:40</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>-32.717426,-71.204309</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J226" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K226" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L226" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="M226" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="N226" t="n">
+        <v>0</v>
+      </c>
+      <c r="O226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr"/>
+      <c r="C227" t="n">
+        <v>6</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>2026/08/24 07:19:41</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>-32.687515,-71.209493</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>2026/08/24 07:20:41</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>-32.672782,-71.21286</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J227" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K227" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L227" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="M227" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="N227" t="n">
+        <v>0</v>
+      </c>
+      <c r="O227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr"/>
+      <c r="C228" t="n">
+        <v>7</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2026/08/24 07:24:41</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>-32.617527,-71.229299</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>2026/08/24 07:24:41</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>-32.617527,-71.229299</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J228" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L228" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="M228" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="N228" t="n">
+        <v>0</v>
+      </c>
+      <c r="O228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr"/>
+      <c r="C229" t="n">
+        <v>8</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2026/08/24 07:25:43</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>-32.617527,-71.229299</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>2026/08/24 07:27:41</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>-32.578559,-71.254056</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J229" s="14" t="n">
+        <v>0.001365740740740741</v>
+      </c>
+      <c r="K229" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L229" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="M229" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="N229" t="n">
+        <v>0</v>
+      </c>
+      <c r="O229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr"/>
+      <c r="C230" t="n">
+        <v>9</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2026/08/24 07:31:41</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>-32.522197,-71.261776</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>2026/08/24 07:32:40</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>-32.507638,-71.25976</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J230" s="14" t="n">
+        <v>0.0006828703703703704</v>
+      </c>
+      <c r="K230" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L230" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="M230" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="N230" t="n">
+        <v>0</v>
+      </c>
+      <c r="O230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr"/>
+      <c r="C231" t="n">
+        <v>1</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2026/08/24 08:00:28</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>-33.108255,-71.554392</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>2026/08/24 08:00:52</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>-33.111176,-71.559844</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J231" s="14" t="n">
+        <v>0.0002777777777777778</v>
+      </c>
+      <c r="K231" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L231" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="M231" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="N231" t="n">
+        <v>0</v>
+      </c>
+      <c r="O231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr"/>
+      <c r="C232" t="n">
+        <v>2</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>2026/08/24 14:31:52</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>-33.337397,-71.373532</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>2026/08/24 14:32:52</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>-33.344117,-71.358588</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J232" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K232" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L232" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="M232" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="N232" t="n">
+        <v>0</v>
+      </c>
+      <c r="O232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>GV TDLD-98 J PACHECHO</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr"/>
+      <c r="C233" t="n">
+        <v>1</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>2026/08/25 08:09:47</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>-33.170747,-71.523259</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>2026/08/25 08:10:47</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>-33.163377,-71.537703</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J233" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K233" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L233" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="M233" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="N233" t="n">
+        <v>0</v>
+      </c>
+      <c r="O233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>GV TDLD-98 J PACHECHO</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr"/>
+      <c r="C234" t="n">
+        <v>2</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2026/08/25 08:11:47</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>-33.155925,-71.552301</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>2026/08/25 08:12:47</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>-33.144415,-71.560891</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J234" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K234" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L234" t="n">
+        <v>101</v>
+      </c>
+      <c r="M234" t="n">
+        <v>101</v>
+      </c>
+      <c r="N234" t="n">
+        <v>0</v>
+      </c>
+      <c r="O234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>GV TOLVA SPGW-29 V OLIVARES</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr"/>
+      <c r="C235" t="n">
+        <v>1</v>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2026/08/25 10:09:45</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>-32.762573,-71.265171</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>2026/08/25 10:10:06</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>-32.760544,-71.260001</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Ruta F-20, Nogales, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J235" s="14" t="n">
+        <v>0.0002430555555555555</v>
+      </c>
+      <c r="K235" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L235" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="M235" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="N235" t="n">
+        <v>0</v>
+      </c>
+      <c r="O235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr"/>
+      <c r="C236" t="n">
+        <v>1</v>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2026/08/25 11:15:09</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>-33.248331,-71.446442</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>2026/08/25 11:16:09</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>-33.261181,-71.436473</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J236" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K236" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L236" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="M236" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="N236" t="n">
+        <v>0</v>
+      </c>
+      <c r="O236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr"/>
+      <c r="C237" t="n">
+        <v>2</v>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2026/08/25 11:25:12</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>-33.35318,-71.338244</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>2026/08/25 11:26:12</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>-33.359706,-71.323842</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J237" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K237" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L237" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="M237" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="N237" t="n">
+        <v>0</v>
+      </c>
+      <c r="O237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr"/>
+      <c r="C238" t="n">
+        <v>3</v>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2026/08/26 08:02:05</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>-33.249826,-71.445313</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>2026/08/26 08:03:05</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>-33.259108,-71.438434</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Caletera Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J238" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K238" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L238" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="M238" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="N238" t="n">
+        <v>0</v>
+      </c>
+      <c r="O238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr"/>
+      <c r="C239" t="n">
+        <v>3</v>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>2026/08/26 12:53:40</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>-33.221106,-71.471013</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>2026/08/26 12:54:40</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>-33.233967,-71.462389</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J239" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K239" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L239" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="M239" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="N239" t="n">
+        <v>0</v>
+      </c>
+      <c r="O239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr"/>
+      <c r="C240" t="n">
+        <v>4</v>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2026/08/26 13:27:05</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>-33.172325,-71.520267</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>2026/08/26 13:28:04</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>-33.164461,-71.535605</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J240" s="14" t="n">
+        <v>0.0006828703703703704</v>
+      </c>
+      <c r="K240" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L240" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="M240" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="N240" t="n">
+        <v>0</v>
+      </c>
+      <c r="O240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>GLP SHLC-75 L FONSECA</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr"/>
+      <c r="C241" t="n">
+        <v>1</v>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2026/08/26 15:53:21</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>-33.17105,-71.522977</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>2026/08/26 15:53:21</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>-33.17105,-71.522977</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J241" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L241" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="M241" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="N241" t="n">
+        <v>0</v>
+      </c>
+      <c r="O241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>GLP SHLC-75 L FONSECA</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr"/>
+      <c r="C242" t="n">
+        <v>2</v>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>2026/08/26 15:54:21</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>-33.179029,-71.507584</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>2026/08/26 15:55:21</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>-33.190886,-71.497565</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J242" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K242" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L242" t="n">
+        <v>102</v>
+      </c>
+      <c r="M242" t="n">
+        <v>102</v>
+      </c>
+      <c r="N242" t="n">
+        <v>0</v>
+      </c>
+      <c r="O242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr"/>
+      <c r="C243" t="n">
+        <v>4</v>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>2026/08/26 17:26:03</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>-33.174293,-71.516064</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Caletera Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>2026/08/26 17:27:03</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>-33.166948,-71.530424</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J243" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K243" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L243" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="M243" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="N243" t="n">
+        <v>0</v>
+      </c>
+      <c r="O243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr"/>
+      <c r="C244" t="n">
+        <v>5</v>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>2026/08/27 07:53:27</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>-33.107919,-71.553395</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>2026/08/27 07:53:58</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>-33.111047,-71.559679</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J244" s="14" t="n">
+        <v>0.0003587962962962963</v>
+      </c>
+      <c r="K244" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L244" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="M244" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="N244" t="n">
+        <v>0</v>
+      </c>
+      <c r="O244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>GV TDLD-98 J PACHECHO</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr"/>
+      <c r="C245" t="n">
+        <v>3</v>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>2026/08/27 09:19:52</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>-33.009031,-71.505167</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>2026/08/27 09:20:27</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>-33.002637,-71.510223</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Avenida Carlos Ibáñez del Campo, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="J245" s="14" t="n">
+        <v>0.0004050925925925926</v>
+      </c>
+      <c r="K245" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L245" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="M245" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="N245" t="n">
+        <v>0</v>
+      </c>
+      <c r="O245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>GC MAXUS PCRF-25 TERRENO</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr"/>
+      <c r="C246" t="n">
+        <v>1</v>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>2026/08/27 09:20:09</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>-32.50726,-71.259884</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>2026/08/27 09:22:09</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>-32.536885,-71.265414</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J246" s="14" t="n">
+        <v>0.001388888888888889</v>
+      </c>
+      <c r="K246" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L246" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="M246" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="N246" t="n">
+        <v>0</v>
+      </c>
+      <c r="O246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>GC MAXUS PCRF-25 TERRENO</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr"/>
+      <c r="C247" t="n">
+        <v>2</v>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>2026/08/27 09:32:09</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>-32.597829,-71.362837</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>2026/08/27 09:33:09</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>-32.601822,-71.373519</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="J247" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K247" t="n">
+        <v>1</v>
+      </c>
+      <c r="L247" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="M247" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="N247" t="n">
+        <v>0</v>
+      </c>
+      <c r="O247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>GV TDLD-98 J PACHECHO</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr"/>
+      <c r="C248" t="n">
+        <v>4</v>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>2026/08/27 16:42:56</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>-33.17646,-71.512497</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Avenida Carlos Ibáñez del Campo, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>2026/08/27 16:43:57</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>-33.186829,-71.500874</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J248" s="14" t="n">
+        <v>0.0007060185185185185</v>
+      </c>
+      <c r="K248" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L248" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="M248" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="N248" t="n">
+        <v>0</v>
+      </c>
+      <c r="O248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>GC TM5-RXXG-13 D SILVA</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr"/>
+      <c r="C249" t="n">
+        <v>1</v>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>2026/08/27 20:19:00</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>-32.553571,-71.266767</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>2026/08/27 20:20:00</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>-32.539992,-71.265993</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J249" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K249" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L249" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="M249" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="N249" t="n">
+        <v>0</v>
+      </c>
+      <c r="O249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>GC TM5-RXXG-13 D SILVA</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr"/>
+      <c r="C250" t="n">
+        <v>2</v>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>2026/08/28 07:37:34</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>-32.589963,-71.339537</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>2026/08/28 07:38:35</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>-32.596058,-71.35637</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="J250" s="14" t="n">
+        <v>0.0007060185185185185</v>
+      </c>
+      <c r="K250" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L250" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="M250" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="N250" t="n">
+        <v>0</v>
+      </c>
+      <c r="O250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>GLP SHDV-51 J REBOLLEDO</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr"/>
+      <c r="C251" t="n">
+        <v>1</v>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>2026/08/28 07:40:48</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>-33.106543,-71.549786</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>2026/08/28 07:41:05</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>-33.10792,-71.554023</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J251" s="14" t="n">
+        <v>0.0001967592592592593</v>
+      </c>
+      <c r="K251" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L251" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="M251" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="N251" t="n">
+        <v>0</v>
+      </c>
+      <c r="O251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="n">
+        <v>1</v>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>2026/08/28 11:59:21</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>-32.447972,-71.324572</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>2026/08/28 11:59:59</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>-32.453159,-71.330792</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Ruta E-30-F, Papudo, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J252" s="14" t="n">
+        <v>0.0004398148148148148</v>
+      </c>
+      <c r="K252" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L252" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="M252" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="N252" t="n">
+        <v>0</v>
+      </c>
+      <c r="O252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>GLP SKDX-44 V VIAL</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr"/>
+      <c r="C253" t="n">
+        <v>1</v>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>2026/08/28 13:44:18</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>-33.130344,-71.562068</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>2026/08/28 13:45:18</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>-33.144777,-71.560864</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J253" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K253" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L253" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="M253" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="N253" t="n">
+        <v>0</v>
+      </c>
+      <c r="O253" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>GLP SKDX-44 V VIAL</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr"/>
+      <c r="C254" t="n">
+        <v>2</v>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>2026/08/28 13:52:18</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>-33.21104,-71.478235</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>2026/08/28 13:53:18</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>-33.224428,-71.469253</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J254" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K254" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L254" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="M254" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="N254" t="n">
+        <v>0</v>
+      </c>
+      <c r="O254" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>GV TDLD-98 J PACHECHO</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr"/>
+      <c r="C255" t="n">
+        <v>5</v>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>2026/08/28 16:24:45</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>-33.166113,-71.532652</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>2026/08/28 16:25:45</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>-33.173303,-71.518642</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J255" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K255" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L255" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="M255" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="N255" t="n">
+        <v>0</v>
+      </c>
+      <c r="O255" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr"/>
+      <c r="C256" t="n">
+        <v>10</v>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>2026/08/28 17:29:46</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>-32.552389,-71.267587</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>2026/08/28 17:31:47</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>-32.579658,-71.252833</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J256" s="14" t="n">
+        <v>0.001400462962962963</v>
+      </c>
+      <c r="K256" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L256" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="M256" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="N256" t="n">
+        <v>0</v>
+      </c>
+      <c r="O256" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr"/>
+      <c r="C257" t="n">
+        <v>11</v>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>2026/08/28 17:38:47</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>-32.657475,-71.220269</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>2026/08/28 17:39:47</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>-32.671322,-71.213376</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J257" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K257" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L257" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="M257" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="N257" t="n">
+        <v>0</v>
+      </c>
+      <c r="O257" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr"/>
+      <c r="C258" t="n">
+        <v>12</v>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>2026/08/28 17:42:47</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>-32.715757,-71.204734</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>2026/08/28 17:45:47</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>-32.759976,-71.194635</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J258" s="14" t="n">
+        <v>0.002083333333333333</v>
+      </c>
+      <c r="K258" t="n">
+        <v>5</v>
+      </c>
+      <c r="L258" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="M258" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="N258" t="n">
+        <v>0</v>
+      </c>
+      <c r="O258" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr"/>
+      <c r="C259" t="n">
+        <v>1</v>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>2026/08/29 08:52:05</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>-32.979021,-71.499986</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>2026/08/29 08:53:05</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>-32.993814,-71.501204</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Ruta 64, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="J259" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K259" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L259" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="M259" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="N259" t="n">
+        <v>0</v>
+      </c>
+      <c r="O259" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13689,7 +15747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.710625" customWidth="1" style="7" min="1" max="1"/>
@@ -13715,7 +15773,7 @@
     <row r="3" ht="25" customHeight="1" s="8">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Desde : 2026/08/10 00:00:00 Hasta: 2026/08/16 23:59:58</t>
+          <t>Desde : 2026/08/17 00:00:00 Hasta: 2026/08/23 23:59:58</t>
         </is>
       </c>
     </row>
@@ -13772,27 +15830,27 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>2026/08/11 00:47:13</t>
+          <t>2026/08/20 09:01:12</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>-32.977793,-71.499934</t>
+          <t>-33.142737,-71.561705</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Camino Internacional, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F6" s="12" t="n">
-        <v>101.7</v>
+        <v>100.7</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>79826.3</v>
+        <v>81486.89999999999</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>160.9</v>
+        <v>335.9</v>
       </c>
     </row>
     <row r="7">
@@ -13806,27 +15864,27 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>2026/08/11 00:48:13</t>
+          <t>2026/08/20 09:02:12</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>-32.992004,-71.501153</t>
+          <t>-33.129457,-71.561884</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Ruta 64, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F7" s="12" t="n">
-        <v>94</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>79827.89999999999</v>
+        <v>81488.39999999999</v>
       </c>
       <c r="H7" s="12" t="n">
-        <v>144.2</v>
+        <v>341.6</v>
       </c>
     </row>
     <row r="8">
@@ -13840,27 +15898,27 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>2026/08/11 14:25:21</t>
+          <t>2026/08/20 09:19:12</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>-33.15983,-71.544708</t>
+          <t>-33.008772,-71.505475</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Avenida Carlos Ibáñez del Campo, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
         </is>
       </c>
       <c r="F8" s="12" t="n">
-        <v>100.1</v>
+        <v>102.2</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>79918.89999999999</v>
+        <v>81507.89999999999</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>365.5</v>
+        <v>217.1</v>
       </c>
     </row>
     <row r="9">
@@ -13874,27 +15932,27 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>2026/08/11 14:26:21</t>
+          <t>2026/08/20 09:19:44</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>-33.15096,-71.557673</t>
+          <t>-33.002592,-71.510204</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Avenida Carlos Ibáñez del Campo, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
         </is>
       </c>
       <c r="F9" s="12" t="n">
-        <v>88.09999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>79920.5</v>
+        <v>81508.8</v>
       </c>
       <c r="H9" s="12" t="n">
-        <v>349.1</v>
+        <v>206.8</v>
       </c>
     </row>
     <row r="10">
@@ -13908,12 +15966,12 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>2026/08/11 14:48:43</t>
+          <t>2026/08/20 09:38:50</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>-32.951646,-71.509458</t>
+          <t>-32.951473,-71.509554</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
@@ -13922,13 +15980,13 @@
         </is>
       </c>
       <c r="F10" s="12" t="n">
-        <v>100.5</v>
+        <v>106.1</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>79950.2</v>
+        <v>81515.60000000001</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>157.6</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11">
@@ -13942,12 +16000,12 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>2026/08/11 14:49:21</t>
+          <t>2026/08/20 09:39:49</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>-32.943313,-71.513542</t>
+          <t>-32.937746,-71.51403</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -13956,13 +16014,13 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>91.90000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>79951.3</v>
+        <v>81517.3</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>123</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="12">
@@ -13976,27 +16034,27 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>2026/08/12 14:44:39</t>
+          <t>2026/08/20 16:37:34</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>-33.163382,-71.537721</t>
+          <t>-33.169294,-71.526495</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>100.3</v>
+        <v>100.7</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>80145.10000000001</v>
+        <v>81647.39999999999</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>367</v>
+        <v>347.8</v>
       </c>
     </row>
     <row r="13">
@@ -14010,46 +16068,46 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>2026/08/12 14:45:39</t>
+          <t>2026/08/20 16:38:34</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>-33.155922,-71.552342</t>
+          <t>-33.176611,-71.51215</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>88.5</v>
+        <v>91.2</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>80146.7</v>
+        <v>81649</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>363.7</v>
+        <v>350.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>GV TDLD-98 J PACHECHO</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>2026/08/12 14:47:39</t>
+          <t>2026/08/17 18:14:01</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>-33.13014,-71.561957</t>
+          <t>-33.160176,-71.544064</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
@@ -14058,32 +16116,32 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>103.6</v>
+        <v>107.9</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>80149.89999999999</v>
+        <v>190096.5</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>338.2</v>
+        <v>361.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>GV TDLD-98 J PACHECHO</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>2026/08/12 14:48:39</t>
+          <t>2026/08/17 18:15:01</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>-33.115708,-71.560383</t>
+          <t>-33.151717,-71.557304</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
@@ -14092,149 +16150,149 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>94.7</v>
+        <v>93.8</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>80151.5</v>
+        <v>190098.1</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>338.3</v>
+        <v>347.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>GV TDLD-98 J PACHECHO</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>2026/08/13 14:31:13</t>
+          <t>2026/08/17 18:33:01</t>
         </is>
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>-33.225857,-71.468365</t>
+          <t>-33.055411,-71.52942</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>100.3</v>
+        <v>102.5</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>80372.5</v>
+        <v>190110.7</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>330.1</v>
+        <v>253.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>GV TDLD-98 J PACHECHO</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>2026/08/13 14:32:13</t>
+          <t>2026/08/17 18:33:12</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>-33.213027,-71.475997</t>
+          <t>-33.053064,-71.52918</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>89.40000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>80374.10000000001</v>
+        <v>190110.9</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>349.6</v>
+        <v>242.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>GV TDLD-98 J PACHECHO</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>2026/08/14 00:38:07</t>
+          <t>2026/08/20 14:29:14</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>-32.98055,-71.500149</t>
+          <t>-33.346943,-71.351958</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Camino Internacional, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>100.2</v>
+        <v>101.5</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>80520</v>
+        <v>190645.4</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>140.8</v>
+        <v>277.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>GV TDLD-98 J PACHECHO</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>2026/08/14 00:39:07</t>
+          <t>2026/08/20 14:30:14</t>
         </is>
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>-32.994359,-71.501297</t>
+          <t>-33.340219,-71.367006</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Ruta 64, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>92.40000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>80521.60000000001</v>
+        <v>190647</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>142.3</v>
+        <v>266.4</v>
       </c>
     </row>
     <row r="20">
@@ -14244,31 +16302,31 @@
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>2026/08/10 10:29:37</t>
+          <t>2026/08/21 08:09:13</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>-32.757227,-71.420873</t>
+          <t>-33.223211,-71.469875</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-190, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>104.2</v>
+        <v>103.2</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>188637</v>
+        <v>190744.2</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>28.7</v>
+        <v>326.3</v>
       </c>
     </row>
     <row r="21">
@@ -14278,31 +16336,31 @@
         </is>
       </c>
       <c r="B21" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>2026/08/10 10:30:38</t>
+          <t>2026/08/21 08:10:13</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>-32.743513,-71.417967</t>
+          <t>-33.235583,-71.460825</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-190, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>86.2</v>
+        <v>95.7</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>188638.6</v>
+        <v>190745.9</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>28.4</v>
+        <v>331.4</v>
       </c>
     </row>
     <row r="22">
@@ -14312,31 +16370,31 @@
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>2026/08/13 10:39:59</t>
+          <t>2026/08/21 17:24:14</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>-33.227,-71.467768</t>
+          <t>-33.09359,-71.548843</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>189448.4</v>
+        <v>190855.9</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>322.5</v>
+        <v>286.9</v>
       </c>
     </row>
     <row r="23">
@@ -14346,31 +16404,31 @@
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>2026/08/13 10:40:59</t>
+          <t>2026/08/21 17:24:21</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>-33.213935,-71.475097</t>
+          <t>-33.092334,-71.550487</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>92</v>
+        <v>108.6</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>189450</v>
+        <v>190856.1</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>339.7</v>
+        <v>276</v>
       </c>
     </row>
     <row r="24">
@@ -14380,1867 +16438,4927 @@
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>2026/08/13 10:49:59</t>
+          <t>2026/08/21 17:25:21</t>
         </is>
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>-33.119158,-71.56076</t>
+          <t>-33.081909,-71.560913</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>108.5</v>
+        <v>95.2</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>189464.3</v>
+        <v>190857.7</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>346.7</v>
+        <v>185</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>2026/08/13 10:50:42</t>
+          <t>2026/08/21 14:35:29</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>-33.109677,-71.558209</t>
+          <t>-33.064528,-71.642204</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>90.90000000000001</v>
+        <v>100.7</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>189465.4</v>
+        <v>268791.6</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>345.8</v>
+        <v>365.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>2026/08/13 18:25:02</t>
+          <t>2026/08/21 14:35:37</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>-33.268542,-71.432855</t>
+          <t>-33.066337,-71.642205</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>103.6</v>
+        <v>94.5</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>189651.3</v>
+        <v>268791.8</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>282.8</v>
+        <v>384.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>2026/08/13 18:26:02</t>
+          <t>2026/08/21 14:57:52</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>-33.255908,-71.44039</t>
+          <t>-33.09928,-71.547628</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>95</v>
+        <v>101.2</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>189652.9</v>
+        <v>268811.1</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>270.5</v>
+        <v>327.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>2026/08/13 18:48:02</t>
+          <t>2026/08/21 14:58:52</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>-33.071993,-71.571936</t>
+          <t>-33.095375,-71.54421</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Vía Las Palmas, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>109.5</v>
+        <v>23.8</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>189679.6</v>
+        <v>268811.6</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>161.6</v>
+        <v>313.3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B29" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>2026/08/13 18:48:57</t>
+          <t>2026/08/21 15:30:39</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>-33.063353,-71.582457</t>
+          <t>-33.094809,-71.543396</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Vía Las Palmas, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>83.7</v>
+        <v>102.4</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>189681</v>
+        <v>268835.1</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>138.9</v>
+        <v>314.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B30" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>2026/08/14 08:05:03</t>
+          <t>2026/08/21 15:30:57</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>-33.10634,-71.549378</t>
+          <t>-33.097242,-71.547303</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>108.7</v>
+        <v>80.3</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>189719.9</v>
+        <v>268835.6</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>349.4</v>
+        <v>319.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B31" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>2026/08/14 08:05:05</t>
+          <t>2026/08/22 14:46:01</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>-33.106701,-71.549852</t>
+          <t>-33.058827,-71.646622</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>106.6</v>
+        <v>103.8</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>189720</v>
+        <v>269242.3</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>347.5</v>
+        <v>318.6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>2026/08/14 08:05:51</t>
+          <t>2026/08/22 14:46:27</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>-33.112291,-71.560068</t>
+          <t>-33.062522,-71.641579</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>95.7</v>
+        <v>94.7</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>189721.2</v>
+        <v>269243</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>342.2</v>
+        <v>360</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>GV SHLC-74 B MIRANDA</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>2026/08/10 09:12:32</t>
+          <t>2026/08/23 22:17:56</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>-33.157548,-71.549489</t>
+          <t>-33.06655,-71.635321</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>101.7</v>
+        <v>103.9</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>125165</v>
+        <v>269583.3</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>367.1</v>
+        <v>428.1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>GV SHLC-74 B MIRANDA</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>2026/08/10 09:13:32</t>
+          <t>2026/08/23 22:18:36</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>-33.165047,-71.534798</t>
+          <t>-33.072195,-71.627738</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>96.90000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>125166.6</v>
+        <v>269584.2</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>357.8</v>
+        <v>432.1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>GV SHLC-74 B MIRANDA</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>2026/08/11 09:46:56</t>
+          <t>2026/08/23 22:25:43</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>-33.216008,-71.473704</t>
+          <t>-33.117601,-71.56072</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>101</v>
+        <v>104.6</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>125408.6</v>
+        <v>269594.8</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>337.1</v>
+        <v>341.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>GV SHLC-74 B MIRANDA</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>2026/08/11 09:47:57</t>
+          <t>2026/08/23 22:26:04</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>-33.229387,-71.466181</t>
+          <t>-33.121138,-71.56138</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>96.40000000000001</v>
+        <v>24.7</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>125410.3</v>
+        <v>269595.1</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>336.2</v>
+        <v>352.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>GV SHLC-74 B MIRANDA</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B37" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2026/08/11 22:16:04</t>
+          <t>2026/08/18 07:49:01</t>
         </is>
       </c>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>-33.217343,-71.472838</t>
+          <t>-32.530144,-70.815085</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta E-411, Putaendo, San Felipe, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>103.4</v>
+        <v>101</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>125456.3</v>
+        <v>113566.5</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>337.8</v>
+        <v>742.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>GV SHLC-74 B MIRANDA</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>2026/08/11 22:17:04</t>
+          <t>2026/08/18 07:49:20</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>-33.205626,-71.484055</t>
+          <t>-32.532986,-70.818559</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta E-411, Putaendo, San Felipe, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>98.90000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>125457.9</v>
+        <v>113567</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>401.1</v>
+        <v>711.2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>GV SHLC-74 B MIRANDA</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B39" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>2026/08/13 10:02:31</t>
+          <t>2026/08/19 07:05:09</t>
         </is>
       </c>
       <c r="D39" s="15" t="inlineStr">
         <is>
-          <t>-33.35848,-71.326553</t>
+          <t>-32.821743,-71.222786</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>103.4</v>
+        <v>101</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>125971</v>
+        <v>113782.7</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>301.6</v>
+        <v>190.8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>GV SHLC-74 B MIRANDA</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B40" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>2026/08/13 10:03:31</t>
+          <t>2026/08/19 07:06:09</t>
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>-33.364972,-71.312258</t>
+          <t>-32.807764,-71.219789</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>88.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>125972.5</v>
+        <v>113784.4</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>312.6</v>
+        <v>188.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>GV SHLC-74 B MIRANDA</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B41" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>2026/08/13 22:23:11</t>
+          <t>2026/08/19 07:11:09</t>
         </is>
       </c>
       <c r="D41" s="15" t="inlineStr">
         <is>
-          <t>-33.203884,-71.485888</t>
+          <t>-32.782806,-71.174599</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 5 Norte, Calera, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>102.1</v>
+        <v>101.3</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>125999.8</v>
+        <v>113791.5</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>399</v>
+        <v>227.3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>GV SHLC-74 B MIRANDA</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B42" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>2026/08/13 22:24:11</t>
+          <t>2026/08/19 07:12:09</t>
         </is>
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>-33.192111,-71.496379</t>
+          <t>-32.772233,-71.187523</t>
         </is>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 5 Norte, Calera, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>97.8</v>
+        <v>101.3</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>126001.5</v>
+        <v>113793.2</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>364.2</v>
+        <v>217.8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B43" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>2026/08/11 15:16:59</t>
+          <t>2026/08/19 07:13:09</t>
         </is>
       </c>
       <c r="D43" s="15" t="inlineStr">
         <is>
-          <t>-33.093469,-71.603099</t>
+          <t>-32.759242,-71.194624</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>104.6</v>
+        <v>100.3</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>54938.9</v>
+        <v>113794.9</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>416.5</v>
+        <v>210.3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B44" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>2026/08/11 15:17:02</t>
+          <t>2026/08/19 07:14:09</t>
         </is>
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>-33.094082,-71.602581</t>
+          <t>-32.744809,-71.19742</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>95.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>54939</v>
+        <v>113796.5</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>417.8</v>
+        <v>215.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>GV PEUGEOT THJY-73 J PONCE</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B45" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>2026/08/13 07:27:21</t>
+          <t>2026/08/19 07:16:09</t>
         </is>
       </c>
       <c r="D45" s="15" t="inlineStr">
         <is>
-          <t>-33.054539,-71.335674</t>
+          <t>-32.71589,-71.204527</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>100.3</v>
+        <v>100.1</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>124058.8</v>
+        <v>113799.8</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>181.1</v>
+        <v>226</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>GV PEUGEOT THJY-73 J PONCE</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B46" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>2026/08/13 07:28:21</t>
+          <t>2026/08/19 07:17:09</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>-33.063291,-71.348177</t>
+          <t>-32.701007,-71.206654</t>
         </is>
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>89.7</v>
+        <v>99.7</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>124060.4</v>
+        <v>113801.5</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>201.6</v>
+        <v>234.4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>GV PEUGEOT THJY-73 J PONCE</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B47" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>2026/08/13 09:17:07</t>
+          <t>2026/08/19 07:18:09</t>
         </is>
       </c>
       <c r="D47" s="15" t="inlineStr">
         <is>
-          <t>-33.09653,-71.545845</t>
+          <t>-32.686246,-71.209765</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>s/n, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>100.6</v>
+        <v>101.1</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>124118.2</v>
+        <v>113803.2</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>314</v>
+        <v>241.2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>GV PEUGEOT THJY-73 J PONCE</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B48" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>2026/08/13 09:17:25</t>
+          <t>2026/08/19 07:19:09</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>-33.093518,-71.542204</t>
+          <t>-32.671547,-71.213168</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>s/n, Nogales, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>100.4</v>
+        <v>99.3</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>124118.7</v>
+        <v>113804.8</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>322.7</v>
+        <v>248.4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>GV PEUGEOT THJY-73 J PONCE</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B49" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>2026/08/13 09:17:46</t>
+          <t>2026/08/19 07:21:49</t>
         </is>
       </c>
       <c r="D49" s="15" t="inlineStr">
         <is>
-          <t>-33.088266,-71.5422</t>
+          <t>-32.635806,-71.232128</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>96.59999999999999</v>
+        <v>100.2</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>124119.2</v>
+        <v>113809.2</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>331.2</v>
+        <v>334.5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>GLP SKDX-44 V VIAL</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B50" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>2026/08/11 01:18:36</t>
+          <t>2026/08/19 07:22:09</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>-33.031585,-71.631541</t>
+          <t>-32.630921,-71.230883</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>109.2</v>
+        <v>100.3</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>148436.9</v>
+        <v>113809.8</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>44.9</v>
+        <v>353</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>GLP SKDX-44 V VIAL</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B51" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>2026/08/11 01:22:16</t>
+          <t>2026/08/19 07:23:08</t>
         </is>
       </c>
       <c r="D51" s="15" t="inlineStr">
         <is>
-          <t>-33.031585,-71.631541</t>
+          <t>-32.616636,-71.229754</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>109.2</v>
+        <v>101.3</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>148436.9</v>
+        <v>113811.5</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>44.9</v>
+        <v>385.9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>GLP SKDX-44 V VIAL</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B52" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>2026/08/11 01:22:22</t>
+          <t>2026/08/19 07:24:12</t>
         </is>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>-33.031872,-71.6299</t>
+          <t>-32.616636,-71.229754</t>
         </is>
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>6.2</v>
+        <v>101.3</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>148437.1</v>
+        <v>113811.5</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>12</v>
+        <v>385.9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>GLP SKDX-44 V VIAL</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B53" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>2026/08/12 12:27:11</t>
+          <t>2026/08/19 07:25:09</t>
         </is>
       </c>
       <c r="D53" s="15" t="inlineStr">
         <is>
-          <t>-33.113036,-71.560164</t>
+          <t>-32.589536,-71.245251</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>103.8</v>
+        <v>99.2</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>148506.5</v>
+        <v>113814.8</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>338.1</v>
+        <v>265</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>GLP SKDX-44 V VIAL</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B54" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>2026/08/12 12:27:50</t>
+          <t>2026/08/19 07:26:09</t>
         </is>
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>-33.121189,-71.561416</t>
+          <t>-32.577264,-71.255286</t>
         </is>
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>33.5</v>
+        <v>100.2</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>148507.3</v>
+        <v>113816.5</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>352.7</v>
+        <v>171.1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>GC TSVS-89 M AEDO</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B55" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>2026/08/14 19:10:37</t>
+          <t>2026/08/19 07:27:09</t>
         </is>
       </c>
       <c r="D55" s="15" t="inlineStr">
         <is>
-          <t>-33.053836,-71.334523</t>
+          <t>-32.563325,-71.261645</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>103.6</v>
+        <v>100.2</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>119886.3</v>
+        <v>113818.2</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>191.8</v>
+        <v>122.3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>GC TSVS-89 M AEDO</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B56" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>2026/08/14 19:11:38</t>
+          <t>2026/08/19 07:28:09</t>
         </is>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>-33.063285,-71.348089</t>
+          <t>-32.549474,-71.268194</t>
         </is>
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>94.8</v>
+        <v>100</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>119887.9</v>
+        <v>113819.8</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>201.8</v>
+        <v>108.6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>GC TSVS-89 M AEDO</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B57" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>2026/08/14 19:12:38</t>
+          <t>2026/08/20 07:07:09</t>
         </is>
       </c>
       <c r="D57" s="15" t="inlineStr">
         <is>
-          <t>-33.06932,-71.363576</t>
+          <t>-32.799799,-71.206358</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Autopista Los Andes, Calera, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>101.3</v>
+        <v>100.3</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>119889.5</v>
+        <v>114071.7</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>191.9</v>
+        <v>200.4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>GC TSVS-89 M AEDO</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B58" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>2026/08/14 19:13:38</t>
+          <t>2026/08/20 07:08:10</t>
         </is>
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>-33.067875,-71.380877</t>
+          <t>-32.791891,-71.191591</t>
         </is>
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Autopista Los Andes, Calera, Quillota, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>95.5</v>
+        <v>88</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>119891.2</v>
+        <v>114073.3</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>181.5</v>
+        <v>219.1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>JAC  LYTS-17 G GALEA</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B59" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>2026/08/13 11:57:49</t>
+          <t>2026/08/20 07:11:10</t>
         </is>
       </c>
       <c r="D59" s="15" t="inlineStr">
         <is>
-          <t>-33.285524,-71.411366</t>
+          <t>-32.781931,-71.175729</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-852, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta 5 Norte, Calera, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>107.6</v>
+        <v>100.1</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>227898.2</v>
+        <v>114077.4</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>261.6</v>
+        <v>222.2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>JAC  LYTS-17 G GALEA</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B60" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>2026/08/13 11:58:27</t>
+          <t>2026/08/20 07:12:10</t>
         </is>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>-33.279484,-71.413704</t>
+          <t>-32.771449,-71.188487</t>
         </is>
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-852, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>s/n, Calera, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>64.5</v>
+        <v>100.1</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>227898.9</v>
+        <v>114079.1</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>297.5</v>
+        <v>213.6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B61" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>2026/08/11 17:10:00</t>
+          <t>2026/08/20 07:13:10</t>
         </is>
       </c>
       <c r="D61" s="15" t="inlineStr">
         <is>
-          <t>-32.798908,-71.440814</t>
+          <t>-32.758091,-71.19483</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-190, Quintero, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>107.1</v>
+        <v>100</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>281024.7</v>
+        <v>114080.7</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>30.5</v>
+        <v>207.3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B62" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>2026/08/11 17:11:00</t>
+          <t>2026/08/20 07:20:09</t>
         </is>
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>-32.810983,-71.441434</t>
+          <t>-32.657495,-71.220065</t>
         </is>
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-190, Quintero, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>56.4</v>
+        <v>100.8</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>281026.1</v>
+        <v>114092.2</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>13</v>
+        <v>253.3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B63" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>2026/08/11 17:31:29</t>
+          <t>2026/08/20 07:21:10</t>
         </is>
       </c>
       <c r="D63" s="15" t="inlineStr">
         <is>
-          <t>-32.942137,-71.482014</t>
+          <t>-32.644382,-71.229461</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Ruta 64, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>104</v>
+        <v>99.2</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>281045</v>
+        <v>114093.9</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>68.5</v>
+        <v>279.8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B64" s="12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>2026/08/11 17:32:08</t>
+          <t>2026/08/20 07:22:10</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>-32.9487,-71.483747</t>
+          <t>-32.630176,-71.230736</t>
         </is>
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>Ruta 64, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>62.9</v>
+        <v>101.4</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>281045.7</v>
+        <v>114095.6</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>109.1</v>
+        <v>351.7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B65" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>2026/08/12 11:16:15</t>
+          <t>2026/08/20 07:23:07</t>
         </is>
       </c>
       <c r="D65" s="15" t="inlineStr">
         <is>
-          <t>-33.38297,-71.391372</t>
+          <t>-32.616292,-71.229904</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-74-G, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>102.1</v>
+        <v>102.7</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>281111.9</v>
+        <v>114097.2</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>246.1</v>
+        <v>383</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B66" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>2026/08/12 11:17:01</t>
+          <t>2026/08/20 07:24:12</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>-33.393885,-71.395297</t>
+          <t>-32.616292,-71.229904</t>
         </is>
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-74-G, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>102.1</v>
+        <v>102.7</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>281113.2</v>
+        <v>114097.2</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>262.5</v>
+        <v>383</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B67" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>2026/08/12 11:17:15</t>
+          <t>2026/08/20 07:25:10</t>
         </is>
       </c>
       <c r="D67" s="15" t="inlineStr">
         <is>
-          <t>-33.396877,-71.394671</t>
+          <t>-32.588579,-71.245847</t>
         </is>
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-74-G, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>77.2</v>
+        <v>101.2</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>281113.5</v>
+        <v>114100.6</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>271.2</v>
+        <v>256.8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B68" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>2026/08/12 15:55:12</t>
+          <t>2026/08/20 07:26:10</t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>-33.376179,-71.386332</t>
+          <t>-32.576203,-71.255976</t>
         </is>
       </c>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-74-G, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>102.6</v>
+        <v>100.6</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>281121.8</v>
+        <v>114102.3</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>254</v>
+        <v>159.9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B69" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>2026/08/12 15:55:25</t>
+          <t>2026/08/20 07:27:09</t>
         </is>
       </c>
       <c r="D69" s="15" t="inlineStr">
         <is>
-          <t>-33.373618,-71.385271</t>
+          <t>-32.56233,-71.262126</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-74-G, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>82.90000000000001</v>
+        <v>100.6</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>281122.1</v>
+        <v>114104</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>265.3</v>
+        <v>117.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B70" s="12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>2026/08/12 16:13:58</t>
+          <t>2026/08/20 07:28:09</t>
         </is>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>-33.305002,-71.411287</t>
+          <t>-32.548299,-71.267953</t>
         </is>
       </c>
       <c r="E70" s="12" t="inlineStr">
         <is>
-          <t>s/n, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>105.9</v>
+        <v>100.2</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>281132.6</v>
+        <v>114105.7</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>256.6</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B71" s="12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>2026/08/12 16:14:58</t>
+          <t>2026/08/20 07:29:10</t>
         </is>
       </c>
       <c r="D71" s="15" t="inlineStr">
         <is>
-          <t>-33.292213,-71.422649</t>
+          <t>-32.53323,-71.26438</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>108.6</v>
+        <v>100.7</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>281134.4</v>
+        <v>114107.4</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>287.9</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B72" s="12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>2026/08/12 16:15:57</t>
+          <t>2026/08/20 07:30:10</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>-33.277849,-71.428907</t>
+          <t>-32.518409,-71.260858</t>
         </is>
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>98.8</v>
+        <v>100.5</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>281136.1</v>
+        <v>114109.1</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>309.8</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B73" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>2026/08/12 17:29:08</t>
+          <t>2026/08/20 07:31:10</t>
         </is>
       </c>
       <c r="D73" s="15" t="inlineStr">
         <is>
-          <t>-32.982117,-71.500227</t>
+          <t>-32.503336,-71.259429</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Camino Internacional Valparaíso - Mendoza, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>107</v>
+        <v>100.6</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>281187.3</v>
+        <v>114110.7</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>128</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B74" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>2026/08/12 17:29:59</t>
+          <t>2026/08/20 07:32:09</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>-32.970275,-71.5001</t>
+          <t>-32.488665,-71.258352</t>
         </is>
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
-          <t>Ruta E-30-F, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>s/n, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>86.59999999999999</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>281188.6</v>
+        <v>114112.4</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>173.6</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B75" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>2026/08/12 17:32:09</t>
+          <t>2026/08/20 16:56:33</t>
         </is>
       </c>
       <c r="D75" s="15" t="inlineStr">
         <is>
-          <t>-32.943489,-71.513534</t>
+          <t>-32.454363,-71.100068</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Ruta E-35, Cabildo, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>110.7</v>
+        <v>101.1</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>281192</v>
+        <v>114183.4</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>118.9</v>
+        <v>150.2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B76" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>2026/08/12 17:33:09</t>
+          <t>2026/08/20 16:57:33</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>-32.929667,-71.512068</t>
+          <t>-32.461252,-71.106287</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Ruta E-35, Cabildo, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>90.59999999999999</v>
+        <v>15.3</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>281193.6</v>
+        <v>114184.4</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>41.7</v>
+        <v>148.4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B77" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>2026/08/13 09:24:35</t>
+          <t>2026/08/21 07:05:04</t>
         </is>
       </c>
       <c r="D77" s="15" t="inlineStr">
         <is>
-          <t>-32.985661,-71.500562</t>
+          <t>-32.817143,-71.223555</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Camino Internacional Valparaíso - Mendoza, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>107.7</v>
+        <v>101.2</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>281301.3</v>
+        <v>114302.4</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>132.1</v>
+        <v>185.2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B78" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 07:05:59</t>
+        </is>
+      </c>
+      <c r="D78" s="15" t="inlineStr">
+        <is>
+          <t>-32.804745,-71.217531</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F78" s="12" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="G78" s="12" t="n">
+        <v>114303.9</v>
+      </c>
+      <c r="H78" s="12" t="n">
+        <v>188.7</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 07:07:05</t>
+        </is>
+      </c>
+      <c r="D79" s="15" t="inlineStr">
+        <is>
+          <t>-32.797402,-71.200269</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Calera, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F79" s="12" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="G79" s="12" t="n">
+        <v>114305.7</v>
+      </c>
+      <c r="H79" s="12" t="n">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="C80" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 07:08:01</t>
+        </is>
+      </c>
+      <c r="D80" s="15" t="inlineStr">
+        <is>
+          <t>-32.79047,-71.188293</t>
+        </is>
+      </c>
+      <c r="E80" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Calera, Quillota, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="F80" s="12" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="G80" s="12" t="n">
+        <v>114307.1</v>
+      </c>
+      <c r="H80" s="12" t="n">
+        <v>223.7</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B81" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 07:12:04</t>
+        </is>
+      </c>
+      <c r="D81" s="15" t="inlineStr">
+        <is>
+          <t>-32.76685,-71.193175</t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Calera, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F81" s="12" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="G81" s="12" t="n">
+        <v>114313.2</v>
+      </c>
+      <c r="H81" s="12" t="n">
+        <v>208.1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B82" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 07:13:04</t>
+        </is>
+      </c>
+      <c r="D82" s="15" t="inlineStr">
+        <is>
+          <t>-32.752011,-71.19595</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F82" s="12" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="G82" s="12" t="n">
+        <v>114314.8</v>
+      </c>
+      <c r="H82" s="12" t="n">
+        <v>213.9</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B83" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 07:14:04</t>
+        </is>
+      </c>
+      <c r="D83" s="15" t="inlineStr">
+        <is>
+          <t>-32.737222,-71.199115</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F83" s="12" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="G83" s="12" t="n">
+        <v>114316.5</v>
+      </c>
+      <c r="H83" s="12" t="n">
+        <v>226.8</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B84" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 07:15:05</t>
+        </is>
+      </c>
+      <c r="D84" s="15" t="inlineStr">
+        <is>
+          <t>-32.722409,-71.203591</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>114318.2</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>225.1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B85" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 07:16:04</t>
+        </is>
+      </c>
+      <c r="D85" s="15" t="inlineStr">
+        <is>
+          <t>-32.707723,-71.205703</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F85" s="12" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="G85" s="12" t="n">
+        <v>114319.9</v>
+      </c>
+      <c r="H85" s="12" t="n">
+        <v>231.1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B86" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="C86" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 07:17:04</t>
+        </is>
+      </c>
+      <c r="D86" s="15" t="inlineStr">
+        <is>
+          <t>-32.69285,-71.208249</t>
+        </is>
+      </c>
+      <c r="E86" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F86" s="12" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="G86" s="12" t="n">
+        <v>114321.5</v>
+      </c>
+      <c r="H86" s="12" t="n">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B87" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="C87" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 07:18:04</t>
+        </is>
+      </c>
+      <c r="D87" s="15" t="inlineStr">
+        <is>
+          <t>-32.678094,-71.211653</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F87" s="12" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="G87" s="12" t="n">
+        <v>114323.2</v>
+      </c>
+      <c r="H87" s="12" t="n">
+        <v>242.5</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B88" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 07:22:23</t>
+        </is>
+      </c>
+      <c r="D88" s="15" t="inlineStr">
+        <is>
+          <t>-32.617989,-71.229113</t>
+        </is>
+      </c>
+      <c r="E88" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F88" s="12" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="G88" s="12" t="n">
+        <v>114330.4</v>
+      </c>
+      <c r="H88" s="12" t="n">
+        <v>382.5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B89" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="C89" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 07:23:07</t>
+        </is>
+      </c>
+      <c r="D89" s="15" t="inlineStr">
+        <is>
+          <t>-32.617989,-71.229113</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F89" s="12" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="G89" s="12" t="n">
+        <v>114330.6</v>
+      </c>
+      <c r="H89" s="12" t="n">
+        <v>382.5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B90" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="C90" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 07:24:07</t>
+        </is>
+      </c>
+      <c r="D90" s="15" t="inlineStr">
+        <is>
+          <t>-32.617989,-71.229113</t>
+        </is>
+      </c>
+      <c r="E90" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F90" s="12" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="G90" s="12" t="n">
+        <v>114330.6</v>
+      </c>
+      <c r="H90" s="12" t="n">
+        <v>382.5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B91" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="C91" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 07:25:04</t>
+        </is>
+      </c>
+      <c r="D91" s="15" t="inlineStr">
+        <is>
+          <t>-32.583989,-71.249226</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F91" s="12" t="n">
+        <v>101</v>
+      </c>
+      <c r="G91" s="12" t="n">
+        <v>114334.7</v>
+      </c>
+      <c r="H91" s="12" t="n">
+        <v>221.2</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B92" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="C92" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 07:26:04</t>
+        </is>
+      </c>
+      <c r="D92" s="15" t="inlineStr">
+        <is>
+          <t>-32.571113,-71.257823</t>
+        </is>
+      </c>
+      <c r="E92" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F92" s="12" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="G92" s="12" t="n">
+        <v>114336.3</v>
+      </c>
+      <c r="H92" s="12" t="n">
+        <v>138.2</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B93" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 07:30:04</t>
+        </is>
+      </c>
+      <c r="D93" s="15" t="inlineStr">
+        <is>
+          <t>-32.513499,-71.260158</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F93" s="12" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="G93" s="12" t="n">
+        <v>114343</v>
+      </c>
+      <c r="H93" s="12" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B94" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 07:31:04</t>
+        </is>
+      </c>
+      <c r="D94" s="15" t="inlineStr">
+        <is>
+          <t>-32.499411,-71.259165</t>
+        </is>
+      </c>
+      <c r="E94" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F94" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="G94" s="12" t="n">
+        <v>114344.6</v>
+      </c>
+      <c r="H94" s="12" t="n">
+        <v>69.7</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B95" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C95" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 10:51:46</t>
+        </is>
+      </c>
+      <c r="D95" s="15" t="inlineStr">
+        <is>
+          <t>-32.509631,-71.260064</t>
+        </is>
+      </c>
+      <c r="E95" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F95" s="12" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="G95" s="12" t="n">
+        <v>114432.8</v>
+      </c>
+      <c r="H95" s="12" t="n">
+        <v>79.40000000000001</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B96" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 10:52:45</t>
+        </is>
+      </c>
+      <c r="D96" s="15" t="inlineStr">
+        <is>
+          <t>-32.524293,-71.26245</t>
+        </is>
+      </c>
+      <c r="E96" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F96" s="12" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="G96" s="12" t="n">
+        <v>114434.5</v>
+      </c>
+      <c r="H96" s="12" t="n">
+        <v>105.6</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B97" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C97" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 10:53:46</t>
+        </is>
+      </c>
+      <c r="D97" s="15" t="inlineStr">
+        <is>
+          <t>-32.539407,-71.266028</t>
+        </is>
+      </c>
+      <c r="E97" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F97" s="12" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="G97" s="12" t="n">
+        <v>114436.2</v>
+      </c>
+      <c r="H97" s="12" t="n">
+        <v>113.5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B98" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C98" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 10:54:46</t>
+        </is>
+      </c>
+      <c r="D98" s="15" t="inlineStr">
+        <is>
+          <t>-32.553877,-71.266773</t>
+        </is>
+      </c>
+      <c r="E98" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F98" s="12" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="G98" s="12" t="n">
+        <v>114437.9</v>
+      </c>
+      <c r="H98" s="12" t="n">
+        <v>111.7</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B99" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="C99" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 10:55:46</t>
+        </is>
+      </c>
+      <c r="D99" s="15" t="inlineStr">
+        <is>
+          <t>-32.567495,-71.25956</t>
+        </is>
+      </c>
+      <c r="E99" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F99" s="12" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="G99" s="12" t="n">
+        <v>114439.5</v>
+      </c>
+      <c r="H99" s="12" t="n">
+        <v>130.3</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B100" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="C100" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 10:56:45</t>
+        </is>
+      </c>
+      <c r="D100" s="15" t="inlineStr">
+        <is>
+          <t>-32.580441,-71.251731</t>
+        </is>
+      </c>
+      <c r="E100" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F100" s="12" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="G100" s="12" t="n">
+        <v>114441.2</v>
+      </c>
+      <c r="H100" s="12" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B101" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 10:57:42</t>
+        </is>
+      </c>
+      <c r="D101" s="15" t="inlineStr">
+        <is>
+          <t>-32.592534,-71.243801</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="F101" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="G101" s="12" t="n">
+        <v>114442.7</v>
+      </c>
+      <c r="H101" s="12" t="n">
+        <v>281.7</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B102" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="C102" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:01:46</t>
+        </is>
+      </c>
+      <c r="D102" s="15" t="inlineStr">
+        <is>
+          <t>-32.630672,-71.230994</t>
+        </is>
+      </c>
+      <c r="E102" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="F102" s="12" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="G102" s="12" t="n">
+        <v>114447.5</v>
+      </c>
+      <c r="H102" s="12" t="n">
+        <v>351.3</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:02:46</t>
+        </is>
+      </c>
+      <c r="D103" s="15" t="inlineStr">
+        <is>
+          <t>-32.645001,-71.22917</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F103" s="12" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="G103" s="12" t="n">
+        <v>114449.2</v>
+      </c>
+      <c r="H103" s="12" t="n">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B104" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:03:46</t>
+        </is>
+      </c>
+      <c r="D104" s="15" t="inlineStr">
+        <is>
+          <t>-32.657987,-71.219943</t>
+        </is>
+      </c>
+      <c r="E104" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F104" s="12" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="G104" s="12" t="n">
+        <v>114450.9</v>
+      </c>
+      <c r="H104" s="12" t="n">
+        <v>255.4</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:04:46</t>
+        </is>
+      </c>
+      <c r="D105" s="15" t="inlineStr">
+        <is>
+          <t>-32.672,-71.213217</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F105" s="12" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="G105" s="12" t="n">
+        <v>114452.5</v>
+      </c>
+      <c r="H105" s="12" t="n">
+        <v>245.7</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B106" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="C106" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:05:46</t>
+        </is>
+      </c>
+      <c r="D106" s="15" t="inlineStr">
+        <is>
+          <t>-32.686857,-71.209718</t>
+        </is>
+      </c>
+      <c r="E106" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F106" s="12" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="G106" s="12" t="n">
+        <v>114454.2</v>
+      </c>
+      <c r="H106" s="12" t="n">
+        <v>240.9</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B107" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="C107" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:06:46</t>
+        </is>
+      </c>
+      <c r="D107" s="15" t="inlineStr">
+        <is>
+          <t>-32.701804,-71.206652</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F107" s="12" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="G107" s="12" t="n">
+        <v>114455.9</v>
+      </c>
+      <c r="H107" s="12" t="n">
+        <v>231.4</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B108" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="C108" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:07:46</t>
+        </is>
+      </c>
+      <c r="D108" s="15" t="inlineStr">
+        <is>
+          <t>-32.716872,-71.204538</t>
+        </is>
+      </c>
+      <c r="E108" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F108" s="12" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="G108" s="12" t="n">
+        <v>114457.6</v>
+      </c>
+      <c r="H108" s="12" t="n">
+        <v>224.6</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:08:45</t>
+        </is>
+      </c>
+      <c r="D109" s="15" t="inlineStr">
+        <is>
+          <t>-32.731461,-71.20107</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F109" s="12" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="G109" s="12" t="n">
+        <v>114459.3</v>
+      </c>
+      <c r="H109" s="12" t="n">
+        <v>220.6</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B110" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="C110" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:09:46</t>
+        </is>
+      </c>
+      <c r="D110" s="15" t="inlineStr">
+        <is>
+          <t>-32.746504,-71.197175</t>
+        </is>
+      </c>
+      <c r="E110" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F110" s="12" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="G110" s="12" t="n">
+        <v>114461</v>
+      </c>
+      <c r="H110" s="12" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B111" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:10:46</t>
+        </is>
+      </c>
+      <c r="D111" s="15" t="inlineStr">
+        <is>
+          <t>-32.761483,-71.194312</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F111" s="12" t="n">
+        <v>101</v>
+      </c>
+      <c r="G111" s="12" t="n">
+        <v>114462.7</v>
+      </c>
+      <c r="H111" s="12" t="n">
+        <v>206.7</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B112" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="C112" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:11:46</t>
+        </is>
+      </c>
+      <c r="D112" s="15" t="inlineStr">
+        <is>
+          <t>-32.771829,-71.189922</t>
+        </is>
+      </c>
+      <c r="E112" s="12" t="inlineStr">
+        <is>
+          <t>s/n, Calera, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F112" s="12" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="G112" s="12" t="n">
+        <v>114463.9</v>
+      </c>
+      <c r="H112" s="12" t="n">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B113" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="C113" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:28:46</t>
+        </is>
+      </c>
+      <c r="D113" s="15" t="inlineStr">
+        <is>
+          <t>-32.799702,-71.206422</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Calera, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F113" s="12" t="n">
+        <v>101</v>
+      </c>
+      <c r="G113" s="12" t="n">
+        <v>114471.3</v>
+      </c>
+      <c r="H113" s="12" t="n">
+        <v>199.8</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B114" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="C114" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:29:46</t>
+        </is>
+      </c>
+      <c r="D114" s="15" t="inlineStr">
+        <is>
+          <t>-32.808391,-71.220336</t>
+        </is>
+      </c>
+      <c r="E114" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F114" s="12" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="G114" s="12" t="n">
+        <v>114473</v>
+      </c>
+      <c r="H114" s="12" t="n">
+        <v>185.3</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B115" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="C115" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:30:34</t>
+        </is>
+      </c>
+      <c r="D115" s="15" t="inlineStr">
+        <is>
+          <t>-32.819704,-71.223271</t>
+        </is>
+      </c>
+      <c r="E115" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="F115" s="12" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="G115" s="12" t="n">
+        <v>114474.3</v>
+      </c>
+      <c r="H115" s="12" t="n">
+        <v>190.8</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B116" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="C116" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:30:46</t>
+        </is>
+      </c>
+      <c r="D116" s="15" t="inlineStr">
+        <is>
+          <t>-32.822655,-71.223108</t>
+        </is>
+      </c>
+      <c r="E116" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="F116" s="12" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="G116" s="12" t="n">
+        <v>114474.7</v>
+      </c>
+      <c r="H116" s="12" t="n">
+        <v>191.5</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B117" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:31:46</t>
+        </is>
+      </c>
+      <c r="D117" s="15" t="inlineStr">
+        <is>
+          <t>-32.836586,-71.221254</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F117" s="12" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="G117" s="12" t="n">
+        <v>114476.3</v>
+      </c>
+      <c r="H117" s="12" t="n">
+        <v>163.7</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B118" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="C118" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:32:45</t>
+        </is>
+      </c>
+      <c r="D118" s="15" t="inlineStr">
+        <is>
+          <t>-32.851149,-71.224474</t>
+        </is>
+      </c>
+      <c r="E118" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F118" s="12" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="G118" s="12" t="n">
+        <v>114477.9</v>
+      </c>
+      <c r="H118" s="12" t="n">
+        <v>145.3</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B119" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:33:46</t>
+        </is>
+      </c>
+      <c r="D119" s="15" t="inlineStr">
+        <is>
+          <t>-32.866108,-71.22795</t>
+        </is>
+      </c>
+      <c r="E119" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F119" s="12" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="G119" s="12" t="n">
+        <v>114479.7</v>
+      </c>
+      <c r="H119" s="12" t="n">
+        <v>135.5</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B120" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="C120" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:34:46</t>
+        </is>
+      </c>
+      <c r="D120" s="15" t="inlineStr">
+        <is>
+          <t>-32.880794,-71.231704</t>
+        </is>
+      </c>
+      <c r="E120" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F120" s="12" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="G120" s="12" t="n">
+        <v>114481.3</v>
+      </c>
+      <c r="H120" s="12" t="n">
+        <v>126.4</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B121" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:35:44</t>
+        </is>
+      </c>
+      <c r="D121" s="15" t="inlineStr">
+        <is>
+          <t>-32.894939,-71.234868</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F121" s="12" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="G121" s="12" t="n">
+        <v>114483</v>
+      </c>
+      <c r="H121" s="12" t="n">
+        <v>115.8</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B122" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="C122" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:35:46</t>
+        </is>
+      </c>
+      <c r="D122" s="15" t="inlineStr">
+        <is>
+          <t>-32.895297,-71.235293</t>
+        </is>
+      </c>
+      <c r="E122" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F122" s="12" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="G122" s="12" t="n">
+        <v>114483</v>
+      </c>
+      <c r="H122" s="12" t="n">
+        <v>116.7</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B123" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="C123" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:36:46</t>
+        </is>
+      </c>
+      <c r="D123" s="15" t="inlineStr">
+        <is>
+          <t>-32.902265,-71.250674</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F123" s="12" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="G123" s="12" t="n">
+        <v>114484.7</v>
+      </c>
+      <c r="H123" s="12" t="n">
+        <v>109.6</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B124" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="C124" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:37:46</t>
+        </is>
+      </c>
+      <c r="D124" s="15" t="inlineStr">
+        <is>
+          <t>-32.908456,-71.267175</t>
+        </is>
+      </c>
+      <c r="E124" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F124" s="12" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="G124" s="12" t="n">
+        <v>114486.4</v>
+      </c>
+      <c r="H124" s="12" t="n">
+        <v>96.40000000000001</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="C125" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:38:46</t>
+        </is>
+      </c>
+      <c r="D125" s="15" t="inlineStr">
+        <is>
+          <t>-32.92049,-71.278113</t>
+        </is>
+      </c>
+      <c r="E125" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F125" s="12" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="G125" s="12" t="n">
+        <v>114488.1</v>
+      </c>
+      <c r="H125" s="12" t="n">
+        <v>86.90000000000001</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B126" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="C126" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:39:46</t>
+        </is>
+      </c>
+      <c r="D126" s="15" t="inlineStr">
+        <is>
+          <t>-32.932324,-71.288644</t>
+        </is>
+      </c>
+      <c r="E126" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F126" s="12" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="G126" s="12" t="n">
+        <v>114489.8</v>
+      </c>
+      <c r="H126" s="12" t="n">
+        <v>79.8</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B127" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="C127" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:42:46</t>
+        </is>
+      </c>
+      <c r="D127" s="15" t="inlineStr">
+        <is>
+          <t>-32.962176,-71.288986</t>
+        </is>
+      </c>
+      <c r="E127" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F127" s="12" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="G127" s="12" t="n">
+        <v>114493.2</v>
+      </c>
+      <c r="H127" s="12" t="n">
+        <v>148.8</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B128" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="C128" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:43:01</t>
+        </is>
+      </c>
+      <c r="D128" s="15" t="inlineStr">
+        <is>
+          <t>-32.96498,-71.291826</t>
+        </is>
+      </c>
+      <c r="E128" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F128" s="12" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="G128" s="12" t="n">
+        <v>114493.6</v>
+      </c>
+      <c r="H128" s="12" t="n">
+        <v>133.7</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B129" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="C129" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:43:46</t>
+        </is>
+      </c>
+      <c r="D129" s="15" t="inlineStr">
+        <is>
+          <t>-32.971848,-71.301426</t>
+        </is>
+      </c>
+      <c r="E129" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F129" s="12" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="G129" s="12" t="n">
+        <v>114494.8</v>
+      </c>
+      <c r="H129" s="12" t="n">
+        <v>80.2</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B130" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="C130" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:44:34</t>
+        </is>
+      </c>
+      <c r="D130" s="15" t="inlineStr">
+        <is>
+          <t>-32.981189,-71.309935</t>
+        </is>
+      </c>
+      <c r="E130" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F130" s="12" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="G130" s="12" t="n">
+        <v>114496.1</v>
+      </c>
+      <c r="H130" s="12" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B131" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="C131" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:44:46</t>
+        </is>
+      </c>
+      <c r="D131" s="15" t="inlineStr">
+        <is>
+          <t>-32.981819,-71.313399</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F131" s="12" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="G131" s="12" t="n">
+        <v>114496.5</v>
+      </c>
+      <c r="H131" s="12" t="n">
+        <v>67.5</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B132" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="C132" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:45:04</t>
+        </is>
+      </c>
+      <c r="D132" s="15" t="inlineStr">
+        <is>
+          <t>-32.983966,-71.317872</t>
+        </is>
+      </c>
+      <c r="E132" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F132" s="12" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="G132" s="12" t="n">
+        <v>114497</v>
+      </c>
+      <c r="H132" s="12" t="n">
+        <v>75.40000000000001</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B133" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="C133" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:45:46</t>
+        </is>
+      </c>
+      <c r="D133" s="15" t="inlineStr">
+        <is>
+          <t>-32.990023,-71.327423</t>
+        </is>
+      </c>
+      <c r="E133" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F133" s="12" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="G133" s="12" t="n">
+        <v>114498.2</v>
+      </c>
+      <c r="H133" s="12" t="n">
+        <v>72.3</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B134" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="C134" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:46:46</t>
+        </is>
+      </c>
+      <c r="D134" s="15" t="inlineStr">
+        <is>
+          <t>-33.004446,-71.328509</t>
+        </is>
+      </c>
+      <c r="E134" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F134" s="12" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="G134" s="12" t="n">
+        <v>114499.8</v>
+      </c>
+      <c r="H134" s="12" t="n">
+        <v>95.2</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B135" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="C135" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:47:46</t>
+        </is>
+      </c>
+      <c r="D135" s="15" t="inlineStr">
+        <is>
+          <t>-33.017425,-71.319856</t>
+        </is>
+      </c>
+      <c r="E135" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F135" s="12" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="G135" s="12" t="n">
+        <v>114501.5</v>
+      </c>
+      <c r="H135" s="12" t="n">
+        <v>108.8</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B136" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="C136" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:48:46</t>
+        </is>
+      </c>
+      <c r="D136" s="15" t="inlineStr">
+        <is>
+          <t>-33.032106,-71.31984</t>
+        </is>
+      </c>
+      <c r="E136" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F136" s="12" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="G136" s="12" t="n">
+        <v>114503.2</v>
+      </c>
+      <c r="H136" s="12" t="n">
+        <v>149.6</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B137" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="C137" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:49:29</t>
+        </is>
+      </c>
+      <c r="D137" s="15" t="inlineStr">
+        <is>
+          <t>-33.04256,-71.319453</t>
+        </is>
+      </c>
+      <c r="E137" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F137" s="12" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="G137" s="12" t="n">
+        <v>114504.3</v>
+      </c>
+      <c r="H137" s="12" t="n">
+        <v>180.2</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B138" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="C138" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:49:46</t>
+        </is>
+      </c>
+      <c r="D138" s="15" t="inlineStr">
+        <is>
+          <t>-33.044888,-71.323532</t>
+        </is>
+      </c>
+      <c r="E138" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="F138" s="12" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="G138" s="12" t="n">
+        <v>114504.8</v>
+      </c>
+      <c r="H138" s="12" t="n">
+        <v>192.1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B139" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="C139" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:52:33</t>
+        </is>
+      </c>
+      <c r="D139" s="15" t="inlineStr">
+        <is>
+          <t>-33.069343,-71.362224</t>
+        </is>
+      </c>
+      <c r="E139" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F139" s="12" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="G139" s="12" t="n">
+        <v>114509.4</v>
+      </c>
+      <c r="H139" s="12" t="n">
+        <v>194.5</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B140" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="C140" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:52:46</t>
+        </is>
+      </c>
+      <c r="D140" s="15" t="inlineStr">
+        <is>
+          <t>-33.069099,-71.366073</t>
+        </is>
+      </c>
+      <c r="E140" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F140" s="12" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="G140" s="12" t="n">
+        <v>114509.8</v>
+      </c>
+      <c r="H140" s="12" t="n">
+        <v>182.6</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B141" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="C141" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:53:46</t>
+        </is>
+      </c>
+      <c r="D141" s="15" t="inlineStr">
+        <is>
+          <t>-33.067592,-71.383795</t>
+        </is>
+      </c>
+      <c r="E141" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F141" s="12" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="G141" s="12" t="n">
+        <v>114511.5</v>
+      </c>
+      <c r="H141" s="12" t="n">
+        <v>179.7</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B142" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="C142" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:54:46</t>
+        </is>
+      </c>
+      <c r="D142" s="15" t="inlineStr">
+        <is>
+          <t>-33.065767,-71.401506</t>
+        </is>
+      </c>
+      <c r="E142" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Quilpué, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F142" s="12" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="G142" s="12" t="n">
+        <v>114513.1</v>
+      </c>
+      <c r="H142" s="12" t="n">
+        <v>164.3</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B143" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="C143" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:55:46</t>
+        </is>
+      </c>
+      <c r="D143" s="15" t="inlineStr">
+        <is>
+          <t>-33.064605,-71.419237</t>
+        </is>
+      </c>
+      <c r="E143" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Quilpué, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F143" s="12" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="G143" s="12" t="n">
+        <v>114514.8</v>
+      </c>
+      <c r="H143" s="12" t="n">
+        <v>166.5</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B144" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="C144" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:56:46</t>
+        </is>
+      </c>
+      <c r="D144" s="15" t="inlineStr">
+        <is>
+          <t>-33.062787,-71.436909</t>
+        </is>
+      </c>
+      <c r="E144" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Quilpué, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F144" s="12" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="G144" s="12" t="n">
+        <v>114516.5</v>
+      </c>
+      <c r="H144" s="12" t="n">
+        <v>172.7</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B145" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="C145" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:57:45</t>
+        </is>
+      </c>
+      <c r="D145" s="15" t="inlineStr">
+        <is>
+          <t>-33.062516,-71.454299</t>
+        </is>
+      </c>
+      <c r="E145" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Quilpué, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F145" s="12" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="G145" s="12" t="n">
+        <v>114518.1</v>
+      </c>
+      <c r="H145" s="12" t="n">
+        <v>182.2</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B146" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="C146" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:58:17</t>
+        </is>
+      </c>
+      <c r="D146" s="15" t="inlineStr">
+        <is>
+          <t>-33.061032,-71.463302</t>
+        </is>
+      </c>
+      <c r="E146" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Quilpué, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F146" s="12" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="G146" s="12" t="n">
+        <v>114519</v>
+      </c>
+      <c r="H146" s="12" t="n">
+        <v>147.1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B147" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="C147" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 11:59:46</t>
+        </is>
+      </c>
+      <c r="D147" s="15" t="inlineStr">
+        <is>
+          <t>-33.061569,-71.486547</t>
+        </is>
+      </c>
+      <c r="E147" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F147" s="12" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="G147" s="12" t="n">
+        <v>114521.4</v>
+      </c>
+      <c r="H147" s="12" t="n">
+        <v>53.5</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B148" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="C148" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 12:00:46</t>
+        </is>
+      </c>
+      <c r="D148" s="15" t="inlineStr">
+        <is>
+          <t>-33.05298,-71.497836</t>
+        </is>
+      </c>
+      <c r="E148" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F148" s="12" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="G148" s="12" t="n">
+        <v>114522.9</v>
+      </c>
+      <c r="H148" s="12" t="n">
+        <v>17.4</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B149" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C149" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/20 09:01:07</t>
+        </is>
+      </c>
+      <c r="D149" s="15" t="inlineStr">
+        <is>
+          <t>-32.931996,-71.478943</t>
+        </is>
+      </c>
+      <c r="E149" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 64, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="F149" s="12" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="G149" s="12" t="n">
+        <v>120871.9</v>
+      </c>
+      <c r="H149" s="12" t="n">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B150" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/20 09:01:23</t>
+        </is>
+      </c>
+      <c r="D150" s="15" t="inlineStr">
+        <is>
+          <t>-32.935124,-71.481164</t>
+        </is>
+      </c>
+      <c r="E150" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 64, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="F150" s="12" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="G150" s="12" t="n">
+        <v>120872.3</v>
+      </c>
+      <c r="H150" s="12" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B151" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C151" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/20 10:50:54</t>
+        </is>
+      </c>
+      <c r="D151" s="15" t="inlineStr">
+        <is>
+          <t>-33.352393,-71.375785</t>
+        </is>
+      </c>
+      <c r="E151" s="12" t="inlineStr">
+        <is>
+          <t>Ruta F-90-G, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F151" s="12" t="n">
+        <v>117</v>
+      </c>
+      <c r="G151" s="12" t="n">
+        <v>120956.4</v>
+      </c>
+      <c r="H151" s="12" t="n">
+        <v>271.6</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B152" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C152" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/20 10:51:54</t>
+        </is>
+      </c>
+      <c r="D152" s="15" t="inlineStr">
+        <is>
+          <t>-33.342378,-71.363904</t>
+        </is>
+      </c>
+      <c r="E152" s="12" t="inlineStr">
+        <is>
+          <t>Ruta F-90-G, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="F152" s="12" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="G152" s="12" t="n">
+        <v>120958</v>
+      </c>
+      <c r="H152" s="12" t="n">
+        <v>278.5</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B153" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C153" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/20 10:52:54</t>
+        </is>
+      </c>
+      <c r="D153" s="15" t="inlineStr">
+        <is>
+          <t>-33.337902,-71.372132</t>
+        </is>
+      </c>
+      <c r="E153" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F153" s="12" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="G153" s="12" t="n">
+        <v>120959.4</v>
+      </c>
+      <c r="H153" s="12" t="n">
+        <v>265.1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B154" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C154" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/20 10:53:55</t>
+        </is>
+      </c>
+      <c r="D154" s="15" t="inlineStr">
+        <is>
+          <t>-33.331425,-71.386417</t>
+        </is>
+      </c>
+      <c r="E154" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F154" s="12" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="G154" s="12" t="n">
+        <v>120960.9</v>
+      </c>
+      <c r="H154" s="12" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B155" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C155" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/20 10:54:54</t>
+        </is>
+      </c>
+      <c r="D155" s="15" t="inlineStr">
+        <is>
+          <t>-33.319175,-71.396951</t>
+        </is>
+      </c>
+      <c r="E155" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F155" s="12" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="G155" s="12" t="n">
+        <v>120962.6</v>
+      </c>
+      <c r="H155" s="12" t="n">
+        <v>269.3</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B156" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C156" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/20 10:55:54</t>
+        </is>
+      </c>
+      <c r="D156" s="15" t="inlineStr">
+        <is>
+          <t>-33.307794,-71.40857</t>
+        </is>
+      </c>
+      <c r="E156" s="12" t="inlineStr">
+        <is>
+          <t>s/n, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F156" s="12" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="G156" s="12" t="n">
+        <v>120964.3</v>
+      </c>
+      <c r="H156" s="12" t="n">
+        <v>260.7</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B157" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C157" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/20 10:57:54</t>
+        </is>
+      </c>
+      <c r="D157" s="15" t="inlineStr">
+        <is>
+          <t>-33.283395,-71.411513</t>
+        </is>
+      </c>
+      <c r="E157" s="12" t="inlineStr">
+        <is>
+          <t>Ruta F-852, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F157" s="12" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="G157" s="12" t="n">
+        <v>120967.1</v>
+      </c>
+      <c r="H157" s="12" t="n">
+        <v>272.1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B158" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C158" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/20 10:58:13</t>
+        </is>
+      </c>
+      <c r="D158" s="15" t="inlineStr">
+        <is>
+          <t>-33.279461,-71.413734</t>
+        </is>
+      </c>
+      <c r="E158" s="12" t="inlineStr">
+        <is>
+          <t>Ruta F-852, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F158" s="12" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="G158" s="12" t="n">
+        <v>120967.5</v>
+      </c>
+      <c r="H158" s="12" t="n">
+        <v>302.3</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B159" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C159" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/20 10:58:56</t>
+        </is>
+      </c>
+      <c r="D159" s="15" t="inlineStr">
+        <is>
+          <t>-33.275198,-71.4257</t>
+        </is>
+      </c>
+      <c r="E159" s="12" t="inlineStr">
+        <is>
+          <t>Ruta F-852, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F159" s="12" t="n">
+        <v>121.7</v>
+      </c>
+      <c r="G159" s="12" t="n">
+        <v>120968.8</v>
+      </c>
+      <c r="H159" s="12" t="n">
+        <v>289.1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B160" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C160" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/20 10:59:27</t>
+        </is>
+      </c>
+      <c r="D160" s="15" t="inlineStr">
+        <is>
+          <t>-33.268717,-71.430666</t>
+        </is>
+      </c>
+      <c r="E160" s="12" t="inlineStr">
+        <is>
+          <t>Ruta F-852, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F160" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="G160" s="12" t="n">
+        <v>120969.6</v>
+      </c>
+      <c r="H160" s="12" t="n">
+        <v>284.5</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B161" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C161" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/20 11:42:35</t>
+        </is>
+      </c>
+      <c r="D161" s="15" t="inlineStr">
+        <is>
+          <t>-33.286247,-71.411266</t>
+        </is>
+      </c>
+      <c r="E161" s="12" t="inlineStr">
+        <is>
+          <t>Ruta F-852, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F161" s="12" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="G161" s="12" t="n">
+        <v>120972.7</v>
+      </c>
+      <c r="H161" s="12" t="n">
+        <v>263.4</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B162" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C162" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/20 11:43:35</t>
+        </is>
+      </c>
+      <c r="D162" s="15" t="inlineStr">
+        <is>
+          <t>-33.30091,-71.41017</t>
+        </is>
+      </c>
+      <c r="E162" s="12" t="inlineStr">
+        <is>
+          <t>Ruta F-852, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F162" s="12" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="G162" s="12" t="n">
+        <v>120974.3</v>
+      </c>
+      <c r="H162" s="12" t="n">
+        <v>260.4</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B163" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="C78" s="12" t="inlineStr">
-        <is>
-          <t>2026/08/13 09:25:32</t>
-        </is>
-      </c>
-      <c r="D78" s="15" t="inlineStr">
-        <is>
-          <t>-32.998254,-71.502383</t>
-        </is>
-      </c>
-      <c r="E78" s="12" t="inlineStr">
-        <is>
-          <t>Camino Internacional Valparaíso - Mendoza, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F78" s="12" t="n">
-        <v>86.90000000000001</v>
-      </c>
-      <c r="G78" s="12" t="n">
-        <v>281302.7</v>
-      </c>
-      <c r="H78" s="12" t="n">
-        <v>158.4</v>
+      <c r="C163" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/20 11:53:35</t>
+        </is>
+      </c>
+      <c r="D163" s="15" t="inlineStr">
+        <is>
+          <t>-33.327825,-71.394773</t>
+        </is>
+      </c>
+      <c r="E163" s="12" t="inlineStr">
+        <is>
+          <t>Avenida Diego Portales, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F163" s="12" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="G163" s="12" t="n">
+        <v>120979.1</v>
+      </c>
+      <c r="H163" s="12" t="n">
+        <v>258.9</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B164" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C164" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/20 11:54:16</t>
+        </is>
+      </c>
+      <c r="D164" s="15" t="inlineStr">
+        <is>
+          <t>-33.325557,-71.400218</t>
+        </is>
+      </c>
+      <c r="E164" s="12" t="inlineStr">
+        <is>
+          <t>Melipilla, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F164" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="G164" s="12" t="n">
+        <v>120979.7</v>
+      </c>
+      <c r="H164" s="12" t="n">
+        <v>257.4</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B165" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="C165" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/20 11:59:36</t>
+        </is>
+      </c>
+      <c r="D165" s="15" t="inlineStr">
+        <is>
+          <t>-33.376217,-71.386345</t>
+        </is>
+      </c>
+      <c r="E165" s="12" t="inlineStr">
+        <is>
+          <t>Ruta F-74-G, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="F165" s="12" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="G165" s="12" t="n">
+        <v>120985.8</v>
+      </c>
+      <c r="H165" s="12" t="n">
+        <v>258.6</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B166" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="C166" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/20 12:00:36</t>
+        </is>
+      </c>
+      <c r="D166" s="15" t="inlineStr">
+        <is>
+          <t>-33.389996,-71.395401</t>
+        </is>
+      </c>
+      <c r="E166" s="12" t="inlineStr">
+        <is>
+          <t>Ruta F-74-G, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="F166" s="12" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="G166" s="12" t="n">
+        <v>120987.6</v>
+      </c>
+      <c r="H166" s="12" t="n">
+        <v>253.2</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B167" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C167" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 17:37:45</t>
+        </is>
+      </c>
+      <c r="D167" s="15" t="inlineStr">
+        <is>
+          <t>-33.254758,-71.44134</t>
+        </is>
+      </c>
+      <c r="E167" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F167" s="12" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="G167" s="12" t="n">
+        <v>121264.8</v>
+      </c>
+      <c r="H167" s="12" t="n">
+        <v>267.4</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B168" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C168" s="12" t="inlineStr">
+        <is>
+          <t>2026/08/21 17:38:31</t>
+        </is>
+      </c>
+      <c r="D168" s="15" t="inlineStr">
+        <is>
+          <t>-33.245884,-71.447565</t>
+        </is>
+      </c>
+      <c r="E168" s="12" t="inlineStr">
+        <is>
+          <t>s/n, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F168" s="12" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="G168" s="12" t="n">
+        <v>121265.9</v>
+      </c>
+      <c r="H168" s="12" t="n">
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -16323,12 +21441,102 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId163"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="default" paperSize="1" scale="100" pageOrder="downThenOver" blackAndWhite="0" draft="0" errors="displayed"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId74"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId164"/>
   </tableParts>
 </worksheet>
 </file>